--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2072,13 +2072,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.514497372686</v>
+        <v>46162.68116403936</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.711231319445</v>
+        <v>46175.87789798611</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.711242743055</v>
+        <v>46175.877909409726</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2125,13 +2125,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.51460834491</v>
+        <v>46162.68127501158</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71120528935</v>
+        <v>46175.87787195602</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.711231469904</v>
+        <v>46175.877898136576</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2190,13 +2190,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.51461189815</v>
+        <v>46162.681278564814</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711205949076</v>
+        <v>46175.87787261574</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71123170139</v>
+        <v>46175.87789836805</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2255,13 +2255,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.51461583334</v>
+        <v>46162.6812825</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71120636574</v>
+        <v>46175.87787303241</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71123180556</v>
+        <v>46175.87789847222</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2320,13 +2320,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.51461923611</v>
+        <v>46162.68128590278</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71120680556</v>
+        <v>46175.87787347222</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71123256945</v>
+        <v>46175.87789923611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2385,13 +2385,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.5146228588</v>
+        <v>46162.68128952546</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.71120755787</v>
+        <v>46175.877874224534</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.7112331713</v>
+        <v>46175.877899837964</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2450,11 +2450,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.51450131944</v>
+        <v>46162.68116798611</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46162.52296707176</v>
+        <v>46162.689633738424</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2497,11 +2497,11 @@
         <v>48</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.51462636574</v>
+        <v>46162.68129303241</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.711229293986</v>
+        <v>46175.87789596065</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2560,11 +2560,11 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.51463159722</v>
+        <v>46162.68129826389</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46175.71122922454</v>
+        <v>46175.8778958912</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2623,11 +2623,11 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.51463680556</v>
+        <v>46162.68130347222</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.71122994213</v>
+        <v>46175.8778966088</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2686,11 +2686,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.514641863425</v>
+        <v>46162.6813085301</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.59364871528</v>
+        <v>46162.760315381944</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2749,11 +2749,11 @@
         <v>68</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.51450521991</v>
+        <v>46162.68117188658</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46162.52323704861</v>
+        <v>46162.689903715276</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2796,11 +2796,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.514649363424</v>
+        <v>46162.681316030095</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.71009886574</v>
+        <v>46169.876765532405</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2859,11 +2859,11 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.51465442129</v>
+        <v>46162.68132108796</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.71010894676</v>
+        <v>46169.876775613426</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2922,11 +2922,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.51466033565</v>
+        <v>46162.68132700231</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46169.71012320602</v>
+        <v>46169.87678987268</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2985,11 +2985,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.51466597222</v>
+        <v>46162.68133263889</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46182.01362844907</v>
+        <v>46182.180295115744</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -3048,11 +3048,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.51467096065</v>
+        <v>46162.68133762731</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46185.004170520835</v>
+        <v>46185.1708371875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -3111,11 +3111,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.51467452546</v>
+        <v>46162.68134119213</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46182.01362846065</v>
+        <v>46182.18029512731</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -3174,11 +3174,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.51467802083</v>
+        <v>46162.6813446875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.013628437504</v>
+        <v>46182.18029510417</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -3237,11 +3237,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.514509120374</v>
+        <v>46162.68117578704</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46162.534388518514</v>
+        <v>46162.701055185185</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -3284,11 +3284,11 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.51468197917</v>
+        <v>46162.681348645834</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.7099952662</v>
+        <v>46169.87666193287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3347,11 +3347,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.51468634259</v>
+        <v>46162.68135300926</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.71025925926</v>
+        <v>46169.87692592593</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3406,11 +3406,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.51469081019</v>
+        <v>46162.68135747685</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.71027026621</v>
+        <v>46169.876936932866</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3465,11 +3465,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.51469575231</v>
+        <v>46162.68136241898</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.71001829861</v>
+        <v>46169.876684965275</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3528,11 +3528,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.51470047454</v>
+        <v>46162.6813671412</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.71031487269</v>
+        <v>46169.87698153935</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3587,11 +3587,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.514705520836</v>
+        <v>46162.6813721875</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.71032918982</v>
+        <v>46169.87699585648</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3646,11 +3646,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.514710393516</v>
+        <v>46162.68137706019</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.71002853009</v>
+        <v>46169.876695196755</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3709,11 +3709,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.51471541666</v>
+        <v>46162.681382083334</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.71035778935</v>
+        <v>46169.877024456015</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3768,11 +3768,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.51472085648</v>
+        <v>46162.681387523146</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.710368113425</v>
+        <v>46169.87703478009</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3827,11 +3827,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.5147255787</v>
+        <v>46162.68139224537</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46175.0037055787</v>
+        <v>46175.17037224537</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3886,11 +3886,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.514730324074</v>
+        <v>46162.68139699074</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71004505787</v>
+        <v>46169.87671172454</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3949,11 +3949,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.51473513889</v>
+        <v>46162.68140180556</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.71041488426</v>
+        <v>46169.87708155093</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -4008,11 +4008,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.51474012731</v>
+        <v>46162.681406793985</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.71043666667</v>
+        <v>46169.87710333333</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -4063,11 +4063,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.51479568287</v>
+        <v>46162.68146234954</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.710054675925</v>
+        <v>46169.87672134259</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>144</v>
@@ -4126,11 +4126,11 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.51480118056</v>
+        <v>46162.68146784722</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.710467372686</v>
+        <v>46169.87713403935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>90</v>
@@ -4179,11 +4179,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.51480631944</v>
+        <v>46162.68147298611</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.71048034722</v>
+        <v>46169.87714701389</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -4232,11 +4232,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.51481050926</v>
+        <v>46162.681477175924</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.710068333334</v>
+        <v>46169.876735</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4295,11 +4295,11 @@
         <v>156</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.51481383102</v>
+        <v>46162.68148049769</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.71051924769</v>
+        <v>46169.87718591435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>96</v>
@@ -4348,11 +4348,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.51481820602</v>
+        <v>46162.681484872686</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.71053196759</v>
+        <v>46169.87719863426</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4401,11 +4401,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.51482258102</v>
+        <v>46162.68148924768</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71054472223</v>
+        <v>46169.877211388884</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4454,11 +4454,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.514825659724</v>
+        <v>46162.68149232639</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.71008885417</v>
+        <v>46169.87675552083</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4517,11 +4517,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.51482921296</v>
+        <v>46162.68149587963</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.71059298611</v>
+        <v>46169.87725965278</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>93</v>
@@ -4570,11 +4570,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.51483364584</v>
+        <v>46162.6815003125</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.71061253472</v>
+        <v>46169.87727920139</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4623,11 +4623,11 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.51451271991</v>
+        <v>46162.68117938658</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46162.53969820602</v>
+        <v>46162.70636487268</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4670,11 +4670,11 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.51483840278</v>
+        <v>46162.68150506944</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46168.00079423611</v>
+        <v>46168.16746090278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4733,11 +4733,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.51484361111</v>
+        <v>46162.68151027778</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46185.01586172453</v>
+        <v>46185.182528391204</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4796,11 +4796,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.51484989583</v>
+        <v>46162.6815165625</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46185.00417555556</v>
+        <v>46185.17084222222</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>85</v>
@@ -4859,11 +4859,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.5148634838</v>
+        <v>46162.68153015046</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46162.59563628472</v>
+        <v>46162.76230295139</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4920,11 +4920,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.514866875004</v>
+        <v>46162.68153354166</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46162.59563131945</v>
+        <v>46162.76229798611</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4971,11 +4971,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.514870694446</v>
+        <v>46162.68153736111</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46162.59562782408</v>
+        <v>46162.76229449074</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>193</v>
@@ -5022,11 +5022,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.514874768516</v>
+        <v>46162.68154143519</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.59562479166</v>
+        <v>46162.76229145833</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -5073,11 +5073,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.51487774306</v>
+        <v>46162.68154440972</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46162.595622106484</v>
+        <v>46162.76228877315</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>193</v>
@@ -5124,11 +5124,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.51488074074</v>
+        <v>46162.68154740741</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.59561929398</v>
+        <v>46162.76228596065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>193</v>
@@ -5175,11 +5175,11 @@
         <v>199</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.514883807875</v>
+        <v>46162.68155047453</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46162.595616203704</v>
+        <v>46162.762282870375</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>193</v>
@@ -5226,11 +5226,11 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.51488609954</v>
+        <v>46162.681552766204</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.59561251158</v>
+        <v>46162.76227917824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>193</v>
@@ -5277,11 +5277,11 @@
         <v>201</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.51488849537</v>
+        <v>46162.68155516204</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46162.595609675926</v>
+        <v>46162.76227634259</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>193</v>
@@ -5328,11 +5328,11 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.51489078703</v>
+        <v>46162.6815574537</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46162.59560234954</v>
+        <v>46162.7622690162</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>193</v>
@@ -5379,11 +5379,11 @@
         <v>203</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.514892858795</v>
+        <v>46162.68155952546</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46162.59560172453</v>
+        <v>46162.762268391205</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>193</v>
@@ -5430,11 +5430,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.5149321412</v>
+        <v>46162.681598807874</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46162.54069429398</v>
+        <v>46162.707360960645</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5477,11 +5477,11 @@
         <v>207</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.51493607639</v>
+        <v>46162.681602743054</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.59635743056</v>
+        <v>46162.76302409722</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>208</v>
@@ -5538,11 +5538,11 @@
         <v>212</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.51494170139</v>
+        <v>46162.68160836806</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46162.59647108796</v>
+        <v>46162.763137754635</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5599,11 +5599,11 @@
         <v>216</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.51494854166</v>
+        <v>46162.681615208334</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46162.5963546412</v>
+        <v>46162.76302130787</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>217</v>
@@ -5660,11 +5660,11 @@
         <v>219</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.51495402778</v>
+        <v>46162.68162069445</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46162.59646792824</v>
+        <v>46162.763134594905</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>220</v>
@@ -5721,11 +5721,11 @@
         <v>222</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.51495931713</v>
+        <v>46162.681625983794</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46162.596350127315</v>
+        <v>46162.76301679398</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5782,11 +5782,11 @@
         <v>225</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.51496408565</v>
+        <v>46162.68163075231</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.59646457176</v>
+        <v>46162.763131238426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>224</v>
@@ -5843,11 +5843,11 @@
         <v>226</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.51496944444</v>
+        <v>46162.68163611111</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46162.596656724534</v>
+        <v>46162.763323391206</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5890,11 +5890,11 @@
         <v>229</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.51497234954</v>
+        <v>46162.6816390162</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.59666891204</v>
+        <v>46162.763335578704</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>230</v>
@@ -5953,11 +5953,11 @@
         <v>234</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.5149772338</v>
+        <v>46162.68164390046</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.59665186342</v>
+        <v>46162.763318530095</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>193</v>
@@ -6006,11 +6006,11 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.51498453703</v>
+        <v>46162.681651203704</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.596648935185</v>
+        <v>46162.76331560186</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>193</v>
@@ -6059,11 +6059,11 @@
         <v>239</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.5149906713</v>
+        <v>46162.68165733796</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.596646053236</v>
+        <v>46162.76331271991</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>193</v>
@@ -6112,11 +6112,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.514996701386</v>
+        <v>46162.68166336806</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.59664304398</v>
+        <v>46162.763309710645</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>193</v>
@@ -6165,11 +6165,11 @@
         <v>243</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.515002685184</v>
+        <v>46162.68166935185</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.5966400926</v>
+        <v>46162.763306759254</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>193</v>
@@ -6218,11 +6218,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.51500905093</v>
+        <v>46162.68167571759</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.59663693287</v>
+        <v>46162.76330359954</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>193</v>
@@ -6271,11 +6271,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.515014432865</v>
+        <v>46162.68168109954</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.59663400463</v>
+        <v>46162.7633006713</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>193</v>
@@ -6324,11 +6324,11 @@
         <v>247</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.5150196412</v>
+        <v>46162.68168630787</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.59663071759</v>
+        <v>46162.763297384256</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6377,11 +6377,11 @@
         <v>248</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.51502527778</v>
+        <v>46162.68169194444</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.596624224534</v>
+        <v>46162.763290891206</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>193</v>
@@ -6430,11 +6430,11 @@
         <v>249</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.5150315625</v>
+        <v>46162.681698229164</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.59662357639</v>
+        <v>46162.763290243056</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6483,11 +6483,11 @@
         <v>250</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.515047650464</v>
+        <v>46162.68171431713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.59694990741</v>
+        <v>46162.76361657407</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>251</v>
@@ -6546,11 +6546,11 @@
         <v>252</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.515052268514</v>
+        <v>46162.681718935186</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.59693472223</v>
+        <v>46162.763601388884</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>193</v>
@@ -6599,11 +6599,11 @@
         <v>255</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.5150584838</v>
+        <v>46162.68172515046</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.59693162037</v>
+        <v>46162.76359828704</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>193</v>
@@ -6652,11 +6652,11 @@
         <v>256</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.515064074076</v>
+        <v>46162.68173074074</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.59692876157</v>
+        <v>46162.763595428245</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6705,11 +6705,11 @@
         <v>257</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.51506952546</v>
+        <v>46162.68173619213</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46162.59692599537</v>
+        <v>46162.76359266204</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>193</v>
@@ -6758,11 +6758,11 @@
         <v>258</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.51507508101</v>
+        <v>46162.681741747685</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46162.59692311342</v>
+        <v>46162.763589780094</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6811,11 +6811,11 @@
         <v>259</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.51511611111</v>
+        <v>46162.68178277778</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46162.59691972222</v>
+        <v>46162.763586388886</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6864,11 +6864,11 @@
         <v>260</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.5151200463</v>
+        <v>46162.68178671296</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46162.59691699074</v>
+        <v>46162.763583657405</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>193</v>
@@ -6917,11 +6917,11 @@
         <v>261</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.51512310185</v>
+        <v>46162.68178976852</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.596914317124</v>
+        <v>46162.763580983796</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6970,11 +6970,11 @@
         <v>262</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.515126342594</v>
+        <v>46162.68179300926</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.59690751157</v>
+        <v>46162.76357417824</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>193</v>
@@ -7023,11 +7023,11 @@
         <v>263</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.515129583335</v>
+        <v>46162.68179625</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.59690686343</v>
+        <v>46162.763573530094</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>193</v>
@@ -7076,11 +7076,11 @@
         <v>264</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.51514020833</v>
+        <v>46162.681806875</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.59717238426</v>
+        <v>46162.763839050924</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>265</v>
@@ -7139,11 +7139,11 @@
         <v>266</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.51514509259</v>
+        <v>46162.68181175926</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.597131574075</v>
+        <v>46162.76379824074</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -7192,11 +7192,11 @@
         <v>268</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.515150844905</v>
+        <v>46162.68181751158</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.597128124995</v>
+        <v>46162.76379479167</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>193</v>
@@ -7245,11 +7245,11 @@
         <v>269</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.51515636574</v>
+        <v>46162.681823032406</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.59712489584</v>
+        <v>46162.763791562495</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>193</v>
@@ -7298,11 +7298,11 @@
         <v>271</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.51516170139</v>
+        <v>46162.681828368055</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.597121956016</v>
+        <v>46162.76378862269</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>193</v>
@@ -7351,11 +7351,11 @@
         <v>272</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.51516733796</v>
+        <v>46162.68183400463</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.597118680555</v>
+        <v>46162.763785347226</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>193</v>
@@ -7404,11 +7404,11 @@
         <v>274</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.51517239583</v>
+        <v>46162.6818390625</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46162.59711548611</v>
+        <v>46162.763782152775</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>193</v>
@@ -7457,11 +7457,11 @@
         <v>275</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.515175416665</v>
+        <v>46162.68184208333</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.59711282408</v>
+        <v>46162.76377949074</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>193</v>
@@ -7510,11 +7510,11 @@
         <v>277</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.51517922454</v>
+        <v>46162.6818458912</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46162.59710596065</v>
+        <v>46162.76377262731</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>193</v>
@@ -7563,11 +7563,11 @@
         <v>278</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.51518270833</v>
+        <v>46162.681849375</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46162.597105312496</v>
+        <v>46162.76377197917</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>193</v>
@@ -7616,11 +7616,11 @@
         <v>279</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.51518592593</v>
+        <v>46162.68185259259</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.59710462963</v>
+        <v>46162.7637712963</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>193</v>
@@ -7669,11 +7669,11 @@
         <v>280</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.5151958912</v>
+        <v>46162.681862557874</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.54193150463</v>
+        <v>46162.708598171295</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>205</v>
@@ -7716,11 +7716,11 @@
         <v>282</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.515199340276</v>
+        <v>46162.68186600694</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.59731405093</v>
+        <v>46162.76398071759</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>283</v>
@@ -7777,11 +7777,11 @@
         <v>285</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.51520620371</v>
+        <v>46162.681872870366</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46162.59731125</v>
+        <v>46162.763977916664</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>286</v>
@@ -7838,11 +7838,11 @@
         <v>288</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.51521326389</v>
+        <v>46162.681879930555</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.59730825231</v>
+        <v>46162.763974918984</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7899,11 +7899,11 @@
         <v>291</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.51521974537</v>
+        <v>46162.681886412036</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.59730359954</v>
+        <v>46162.763970266205</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>292</v>
@@ -7960,11 +7960,11 @@
         <v>294</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.51522420139</v>
+        <v>46162.68189086806</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.5441978125</v>
+        <v>46162.710864479166</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>295</v>
@@ -8007,11 +8007,11 @@
         <v>297</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.515227094904</v>
+        <v>46162.681893761575</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.59758981482</v>
+        <v>46162.76425648148</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8070,11 +8070,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.515240277775</v>
+        <v>46162.68190694445</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.59758659722</v>
+        <v>46162.764253263886</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>193</v>
@@ -8123,11 +8123,11 @@
         <v>302</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.515244375</v>
+        <v>46162.68191104167</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46162.59758336806</v>
+        <v>46162.76425003472</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>193</v>
@@ -8176,11 +8176,11 @@
         <v>303</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.51524849537</v>
+        <v>46162.68191516204</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.59757960648</v>
+        <v>46162.764246273146</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>193</v>
@@ -8229,11 +8229,11 @@
         <v>305</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.5152528125</v>
+        <v>46162.68191947917</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46162.59757637732</v>
+        <v>46162.76424304398</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>193</v>
@@ -8282,11 +8282,11 @@
         <v>307</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.51525704861</v>
+        <v>46162.68192371528</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.59757341435</v>
+        <v>46162.764240081015</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>193</v>
@@ -8335,11 +8335,11 @@
         <v>308</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.51526049769</v>
+        <v>46162.68192716435</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.5975703125</v>
+        <v>46162.76423697917</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>193</v>
@@ -8388,11 +8388,11 @@
         <v>309</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.51526369213</v>
+        <v>46162.6819303588</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.59756756945</v>
+        <v>46162.76423423611</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>193</v>
@@ -8441,11 +8441,11 @@
         <v>310</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.51526677083</v>
+        <v>46162.6819334375</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.59756486111</v>
+        <v>46162.76423152778</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>193</v>
@@ -8494,11 +8494,11 @@
         <v>311</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.5152699537</v>
+        <v>46162.68193662037</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.5975578125</v>
+        <v>46162.764224479164</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>193</v>
@@ -8547,11 +8547,11 @@
         <v>312</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.51527310185</v>
+        <v>46162.68193976852</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.59755723379</v>
+        <v>46162.76422390046</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>193</v>
@@ -8600,11 +8600,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.51532694444</v>
+        <v>46162.68199361111</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.59778599537</v>
+        <v>46162.76445266204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>314</v>
@@ -8663,11 +8663,11 @@
         <v>315</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.51533206018</v>
+        <v>46162.68199872685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.59775847222</v>
+        <v>46162.764425138885</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>193</v>
@@ -8716,11 +8716,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.51533766204</v>
+        <v>46162.6820043287</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.59775552084</v>
+        <v>46162.7644221875</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>193</v>
@@ -8769,11 +8769,11 @@
         <v>320</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.51534278935</v>
+        <v>46162.68200945602</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46162.59775206019</v>
+        <v>46162.76441872685</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>193</v>
@@ -8822,11 +8822,11 @@
         <v>323</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.51534923611</v>
+        <v>46162.68201590278</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.59774861111</v>
+        <v>46162.76441527778</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>193</v>
@@ -8875,11 +8875,11 @@
         <v>324</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.515355509255</v>
+        <v>46162.682022175926</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46162.59774576389</v>
+        <v>46162.76441243055</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>193</v>
@@ -8928,11 +8928,11 @@
         <v>325</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.51535997685</v>
+        <v>46162.68202664352</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46162.59774262732</v>
+        <v>46162.76440929398</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>193</v>
@@ -8981,11 +8981,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.51536520833</v>
+        <v>46162.682031874996</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46162.5977397338</v>
+        <v>46162.76440640046</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>193</v>
@@ -9034,11 +9034,11 @@
         <v>329</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.51537046296</v>
+        <v>46162.682037129634</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46162.59773709491</v>
+        <v>46162.764403761576</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>193</v>
@@ -9087,11 +9087,11 @@
         <v>330</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.5153756713</v>
+        <v>46162.68204233796</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.59772972223</v>
+        <v>46162.764396388884</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>193</v>
@@ -9140,11 +9140,11 @@
         <v>331</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.515380868055</v>
+        <v>46162.68204753472</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46162.597729016205</v>
+        <v>46162.76439568287</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>193</v>
@@ -9193,11 +9193,11 @@
         <v>332</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.51539451389</v>
+        <v>46162.68206118056</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46162.59795079861</v>
+        <v>46162.76461746528</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>333</v>
@@ -9256,11 +9256,11 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.51539876158</v>
+        <v>46162.68206542824</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46162.59794666666</v>
+        <v>46162.76461333333</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>193</v>
@@ -9309,11 +9309,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.515404756945</v>
+        <v>46162.68207142361</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46162.597943773144</v>
+        <v>46162.764610439815</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>193</v>
@@ -9362,11 +9362,11 @@
         <v>338</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.51541633102</v>
+        <v>46162.682082997686</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46162.59794086806</v>
+        <v>46162.76460753472</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>193</v>
@@ -9415,11 +9415,11 @@
         <v>340</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.51542265047</v>
+        <v>46162.682089317124</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46162.59793777778</v>
+        <v>46162.76460444444</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>193</v>
@@ -9468,11 +9468,11 @@
         <v>343</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.51542899305</v>
+        <v>46162.68209565972</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46162.59793458333</v>
+        <v>46162.764601250004</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>193</v>
@@ -9521,11 +9521,11 @@
         <v>345</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.51543327546</v>
+        <v>46162.68209994213</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46162.59793099537</v>
+        <v>46162.76459766204</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>193</v>
@@ -9574,11 +9574,11 @@
         <v>347</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.51543752315</v>
+        <v>46162.682104189815</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46162.59792822917</v>
+        <v>46162.76459489584</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>193</v>
@@ -9627,11 +9627,11 @@
         <v>348</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.5154406713</v>
+        <v>46162.68210733796</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46162.59792023148</v>
+        <v>46162.76458689815</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>193</v>
@@ -9680,11 +9680,11 @@
         <v>349</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.51544488426</v>
+        <v>46162.68211155092</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.597919548614</v>
+        <v>46162.76458621528</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>193</v>
@@ -9733,11 +9733,11 @@
         <v>350</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.515449212966</v>
+        <v>46162.68211587963</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.59791885417</v>
+        <v>46162.76458552083</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>193</v>
@@ -9786,11 +9786,11 @@
         <v>351</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.515461504634</v>
+        <v>46162.68212817129</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.598105</v>
+        <v>46162.76477166667</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>352</v>
@@ -9849,11 +9849,11 @@
         <v>353</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.5154656713</v>
+        <v>46162.68213233796</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46162.59810696759</v>
+        <v>46162.76477363426</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>193</v>
@@ -9902,11 +9902,11 @@
         <v>356</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.51547121527</v>
+        <v>46162.682137881944</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46162.59810405092</v>
+        <v>46162.76477071759</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>193</v>
@@ -9955,11 +9955,11 @@
         <v>357</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.515476608794</v>
+        <v>46162.682143275466</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46162.59810047454</v>
+        <v>46162.764767141205</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>193</v>
@@ -10008,11 +10008,11 @@
         <v>359</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.51548292824</v>
+        <v>46162.68214959491</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46162.598097372684</v>
+        <v>46162.764764039355</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>193</v>
@@ -10061,11 +10061,11 @@
         <v>361</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.515531365745</v>
+        <v>46162.6821980324</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.59809424769</v>
+        <v>46162.76476091435</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>193</v>
@@ -10114,11 +10114,11 @@
         <v>363</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.51553788195</v>
+        <v>46162.68220454861</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.598091064814</v>
+        <v>46162.76475773148</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>193</v>
@@ -10167,11 +10167,11 @@
         <v>366</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.51554462963</v>
+        <v>46162.6822112963</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.5980878588</v>
+        <v>46162.76475452546</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>193</v>
@@ -10220,11 +10220,11 @@
         <v>367</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.515549386575</v>
+        <v>46162.68221605324</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.59808292824</v>
+        <v>46162.764749594906</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>193</v>
@@ -10273,11 +10273,11 @@
         <v>368</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.515555335645</v>
+        <v>46162.68222200232</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.5980762963</v>
+        <v>46162.76474296296</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>193</v>
@@ -10326,11 +10326,11 @@
         <v>370</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.51556148149</v>
+        <v>46162.68222814814</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.59807547454</v>
+        <v>46162.764742141204</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>193</v>
@@ -10379,11 +10379,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.51557831018</v>
+        <v>46162.68224497685</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.598281921295</v>
+        <v>46162.76494858797</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>372</v>
@@ -10442,11 +10442,11 @@
         <v>373</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.51558331019</v>
+        <v>46162.68224997685</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.59826834491</v>
+        <v>46162.764935011575</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>193</v>
@@ -10495,11 +10495,11 @@
         <v>375</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.51558917824</v>
+        <v>46162.682255844906</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.598265127315</v>
+        <v>46162.76493179398</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>193</v>
@@ -10548,11 +10548,11 @@
         <v>376</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.5155946875</v>
+        <v>46162.682261354166</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46162.598262025465</v>
+        <v>46162.76492869213</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>193</v>
@@ -10601,11 +10601,11 @@
         <v>377</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.515600266204</v>
+        <v>46162.68226693287</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46162.59825894676</v>
+        <v>46162.764925613425</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>193</v>
@@ -10654,11 +10654,11 @@
         <v>379</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.515605625</v>
+        <v>46162.68227229167</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46162.59825605324</v>
+        <v>46162.76492271991</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>193</v>
@@ -10707,11 +10707,11 @@
         <v>380</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.51561096065</v>
+        <v>46162.68227762732</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46162.59825277778</v>
+        <v>46162.764919444446</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>193</v>
@@ -10760,11 +10760,11 @@
         <v>381</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.51561365741</v>
+        <v>46162.68228032408</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.598249710645</v>
+        <v>46162.76491637732</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>193</v>
@@ -10813,11 +10813,11 @@
         <v>382</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.51561780093</v>
+        <v>46162.68228446759</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.598247002315</v>
+        <v>46162.76491366898</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>193</v>
@@ -10866,11 +10866,11 @@
         <v>383</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.5156205324</v>
+        <v>46162.68228719907</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.5982405324</v>
+        <v>46162.764907199075</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>193</v>
@@ -10919,11 +10919,11 @@
         <v>384</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.515623495376</v>
+        <v>46162.68229016203</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.598239756946</v>
+        <v>46162.76490642361</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>193</v>
@@ -10972,11 +10972,11 @@
         <v>385</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.51563335648</v>
+        <v>46162.68230002315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.598489317126</v>
+        <v>46162.7651559838</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>386</v>
@@ -11035,11 +11035,11 @@
         <v>388</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.51564283565</v>
+        <v>46162.682309502314</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.59846577546</v>
+        <v>46162.76513244213</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>193</v>
@@ -11086,11 +11086,11 @@
         <v>390</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.51564708333</v>
+        <v>46162.68231375</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.59846291666</v>
+        <v>46162.765129583335</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>193</v>
@@ -11137,11 +11137,11 @@
         <v>391</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.515651435184</v>
+        <v>46162.682318101855</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.59845991898</v>
+        <v>46162.76512658565</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>193</v>
@@ -11188,11 +11188,11 @@
         <v>392</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.515655763884</v>
+        <v>46162.682322430555</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.598457025466</v>
+        <v>46162.76512369213</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>193</v>
@@ -11239,11 +11239,11 @@
         <v>393</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.51566009259</v>
+        <v>46162.682326759255</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.598454085644</v>
+        <v>46162.765120752316</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>193</v>
@@ -11290,11 +11290,11 @@
         <v>395</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.51569572916</v>
+        <v>46162.68236239583</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.598450798614</v>
+        <v>46162.76511746528</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>193</v>
@@ -11341,11 +11341,11 @@
         <v>396</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.51569929398</v>
+        <v>46162.682365960645</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.59844327546</v>
+        <v>46162.765109942135</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>193</v>
@@ -11392,11 +11392,11 @@
         <v>397</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.515702777775</v>
+        <v>46162.68236944445</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.59844033565</v>
+        <v>46162.76510700231</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>193</v>
@@ -11443,11 +11443,11 @@
         <v>398</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.51570592592</v>
+        <v>46162.68237259259</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.59843385417</v>
+        <v>46162.76510052083</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>193</v>
@@ -11494,11 +11494,11 @@
         <v>399</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.51570923611</v>
+        <v>46162.682375902776</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.598433356485</v>
+        <v>46162.76510002315</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>193</v>
@@ -11545,11 +11545,11 @@
         <v>400</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.51571943287</v>
+        <v>46162.682386099536</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.5451181713</v>
+        <v>46162.711784837964</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>401</v>
@@ -11592,11 +11592,11 @@
         <v>403</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.51572258102</v>
+        <v>46162.68238924768</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.598708715275</v>
+        <v>46162.76537538195</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>404</v>
@@ -11655,11 +11655,11 @@
         <v>408</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.515727997685</v>
+        <v>46162.682394664356</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.59869457176</v>
+        <v>46162.76536123843</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>193</v>
@@ -11708,11 +11708,11 @@
         <v>410</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.51573236111</v>
+        <v>46162.68239902778</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.59869135417</v>
+        <v>46162.76535802083</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>193</v>
@@ -11761,11 +11761,11 @@
         <v>411</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.51573665509</v>
+        <v>46162.682403321756</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.59868791667</v>
+        <v>46162.76535458333</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>193</v>
@@ -11814,11 +11814,11 @@
         <v>412</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.515740891205</v>
+        <v>46162.68240755787</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.5986849537</v>
+        <v>46162.76535162037</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>193</v>
@@ -11867,11 +11867,11 @@
         <v>414</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.51574541666</v>
+        <v>46162.68241208333</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.598682129625</v>
+        <v>46162.765348796296</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>193</v>
@@ -11920,11 +11920,11 @@
         <v>415</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.51574973379</v>
+        <v>46162.682416400465</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.59867831018</v>
+        <v>46162.765344976855</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>193</v>
@@ -11973,11 +11973,11 @@
         <v>416</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.515752858795</v>
+        <v>46162.68241952546</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.59867409722</v>
+        <v>46162.765340763886</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>193</v>
@@ -12026,11 +12026,11 @@
         <v>417</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.51575556713</v>
+        <v>46162.6824222338</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.59867082176</v>
+        <v>46162.765337488425</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>193</v>
@@ -12079,11 +12079,11 @@
         <v>418</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.51575847222</v>
+        <v>46162.68242513889</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.59866390046</v>
+        <v>46162.76533056713</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>193</v>
@@ -12132,11 +12132,11 @@
         <v>419</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.51576145833</v>
+        <v>46162.682428125</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.598663240744</v>
+        <v>46162.76532990741</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>193</v>
@@ -12185,11 +12185,11 @@
         <v>420</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.51577021991</v>
+        <v>46162.68243688658</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.59967365741</v>
+        <v>46162.76634032407</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>421</v>
@@ -12248,11 +12248,11 @@
         <v>422</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.51577402778</v>
+        <v>46162.68244069444</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.59965137731</v>
+        <v>46162.766318043985</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>193</v>
@@ -12301,11 +12301,11 @@
         <v>424</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.51577790509</v>
+        <v>46162.68244457176</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.5996480787</v>
+        <v>46162.76631474537</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>193</v>
@@ -12354,11 +12354,11 @@
         <v>425</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.51578178241</v>
+        <v>46162.68244844908</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.59964526621</v>
+        <v>46162.76631193287</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>193</v>
@@ -12407,11 +12407,11 @@
         <v>427</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.51578554398</v>
+        <v>46162.68245221065</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.59964231482</v>
+        <v>46162.76630898148</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>193</v>
@@ -12460,11 +12460,11 @@
         <v>428</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.51578986111</v>
+        <v>46162.68245652778</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.59963861111</v>
+        <v>46162.76630527778</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>193</v>
@@ -12513,11 +12513,11 @@
         <v>429</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.515793831015</v>
+        <v>46162.68246049769</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.59963546296</v>
+        <v>46162.76630212963</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>193</v>
@@ -12566,11 +12566,11 @@
         <v>430</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.51579651621</v>
+        <v>46162.68246318287</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.59963251157</v>
+        <v>46162.76629917824</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>193</v>
@@ -12619,11 +12619,11 @@
         <v>431</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.51579935185</v>
+        <v>46162.68246601852</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.59962894676</v>
+        <v>46162.76629561343</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>193</v>
@@ -12672,11 +12672,11 @@
         <v>432</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.515802152775</v>
+        <v>46162.68246881945</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.59962233796</v>
+        <v>46162.766289004634</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>193</v>
@@ -12725,11 +12725,11 @@
         <v>433</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.51580491898</v>
+        <v>46162.68247158565</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.59962168982</v>
+        <v>46162.76628835648</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>193</v>
@@ -12778,11 +12778,11 @@
         <v>434</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.515813460646</v>
+        <v>46162.68248012732</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.59986376157</v>
+        <v>46162.76653042824</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>435</v>
@@ -12841,11 +12841,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.51585783565</v>
+        <v>46162.682524502314</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.59984879629</v>
+        <v>46162.766515462965</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>193</v>
@@ -12894,11 +12894,11 @@
         <v>438</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.51586636574</v>
+        <v>46162.682533032406</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.599846157405</v>
+        <v>46162.76651282408</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>193</v>
@@ -12947,11 +12947,11 @@
         <v>439</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.51587216435</v>
+        <v>46162.68253883102</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.599843564814</v>
+        <v>46162.76651023148</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>193</v>
@@ -13000,11 +13000,11 @@
         <v>441</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.51587701389</v>
+        <v>46162.68254368055</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.59984106482</v>
+        <v>46162.76650773148</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>193</v>
@@ -13053,11 +13053,11 @@
         <v>442</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.515887430556</v>
+        <v>46162.68255409722</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.59983741898</v>
+        <v>46162.76650408565</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>193</v>
@@ -13106,11 +13106,11 @@
         <v>444</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.51589239584</v>
+        <v>46162.6825590625</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.59983439815</v>
+        <v>46162.76650106482</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>193</v>
@@ -13159,11 +13159,11 @@
         <v>445</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.51589594907</v>
+        <v>46162.68256261574</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.599831747684</v>
+        <v>46162.76649841435</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>193</v>
@@ -13212,11 +13212,11 @@
         <v>446</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.51589934027</v>
+        <v>46162.682566006944</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.599827893515</v>
+        <v>46162.76649456019</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>193</v>
@@ -13265,11 +13265,11 @@
         <v>447</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.51590271991</v>
+        <v>46162.682569386576</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.59982238426</v>
+        <v>46162.766489050926</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>193</v>
@@ -13318,11 +13318,11 @@
         <v>448</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.51590612269</v>
+        <v>46162.68257278935</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.599821724536</v>
+        <v>46162.76648839121</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>193</v>
@@ -13371,11 +13371,11 @@
         <v>449</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.51591664352</v>
+        <v>46162.68258331019</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.60004421296</v>
+        <v>46162.76671087963</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>450</v>
@@ -13434,11 +13434,11 @@
         <v>452</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.51592248843</v>
+        <v>46162.6825891551</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.60003350694</v>
+        <v>46162.76670017361</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>193</v>
@@ -13487,11 +13487,11 @@
         <v>453</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.5159266088</v>
+        <v>46162.68259327546</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.600030138885</v>
+        <v>46162.76669680556</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>193</v>
@@ -13540,11 +13540,11 @@
         <v>454</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.51593083334</v>
+        <v>46162.682597499996</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.600027430555</v>
+        <v>46162.76669409723</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>193</v>
@@ -13593,11 +13593,11 @@
         <v>455</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.51593502315</v>
+        <v>46162.68260168981</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.60002471065</v>
+        <v>46162.766691377314</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>193</v>
@@ -13646,11 +13646,11 @@
         <v>456</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.51593949074</v>
+        <v>46162.68260615741</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.60002099537</v>
+        <v>46162.766687662035</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>193</v>
@@ -13699,11 +13699,11 @@
         <v>457</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.515943900464</v>
+        <v>46162.68261056713</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.60001805556</v>
+        <v>46162.76668472222</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>193</v>
@@ -13752,11 +13752,11 @@
         <v>458</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.515946898144</v>
+        <v>46162.682613564815</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.600015069445</v>
+        <v>46162.76668173611</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>193</v>
@@ -13805,11 +13805,11 @@
         <v>459</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.51595</v>
+        <v>46162.682616666665</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.60000615741</v>
+        <v>46162.76667282407</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>193</v>
@@ -13858,11 +13858,11 @@
         <v>460</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.51595291667</v>
+        <v>46162.682619583335</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.60000546296</v>
+        <v>46162.76667212963</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>193</v>
@@ -13911,11 +13911,11 @@
         <v>461</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.515955995375</v>
+        <v>46162.68262266203</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.60000474537</v>
+        <v>46162.76667141204</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>193</v>
@@ -13964,11 +13964,11 @@
         <v>462</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.51599895833</v>
+        <v>46162.682665625005</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.59338501157</v>
+        <v>46162.76005167824</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>463</v>
@@ -14011,11 +14011,11 @@
         <v>465</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.51600283565</v>
+        <v>46162.68266950232</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.60010122685</v>
+        <v>46162.76676789352</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>466</v>
@@ -14074,11 +14074,11 @@
         <v>469</v>
       </c>
       <c r="B222" s="5">
-        <v>46162.51600824074</v>
+        <v>46162.68267490741</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.600161608796</v>
+        <v>46162.76682827546</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>470</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -4800,7 +4800,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46185.17084222222</v>
+        <v>46186.16887460648</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>85</v>
@@ -4844,8 +4844,8 @@
       <c r="R50" s="5">
         <v>46185</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>87</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.876695196755</v>
+        <v>46188.19885825232</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3694,8 +3694,8 @@
       <c r="R30" s="5">
         <v>46195</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>54</v>
+      <c r="S30" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46182.180295115744</v>
+        <v>46189.16936103009</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46182.18029512731</v>
+        <v>46189.16936292824</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46182.18029510417</v>
+        <v>46189.16936435185</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.87713403935</v>
+        <v>46189.16936783565</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>90</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.763974918984</v>
+        <v>46189.1766387963</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7884,8 +7884,8 @@
       <c r="R106" s="5">
         <v>46196</v>
       </c>
-      <c r="S106" s="7" t="s">
-        <v>54</v>
+      <c r="S106" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -293,112 +293,112 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT4327</t>
   </si>
   <si>
+    <t>1214977075717403</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT4327</t>
+  </si>
+  <si>
+    <t>1214977075717413</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732911</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT4327</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT4327</t>
+  </si>
+  <si>
+    <t>1214969047720958</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe OT4327,Motor OT4327,rodete OT4327,Materiales corte Laser OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732921</t>
+  </si>
+  <si>
+    <t>Alabe OT4327</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT4327,Fabricación Alabe OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732936</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT4327</t>
+  </si>
+  <si>
+    <t>Alabe OT4327,Fabricación Alabe OT4327</t>
+  </si>
+  <si>
+    <t>1214977316760264</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT4327</t>
+  </si>
+  <si>
+    <t>Alabe OT4327,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214977533931641</t>
+  </si>
+  <si>
+    <t>rodete OT4327</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT4327,Generación OC Rodete OT4327</t>
+  </si>
+  <si>
+    <t>1214977533931656</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT4327</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT4327,rodete OT4327</t>
+  </si>
+  <si>
+    <t>1214977075779516</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT4327</t>
+  </si>
+  <si>
+    <t>rodete OT4327,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214977075779534</t>
+  </si>
+  <si>
+    <t>Motor OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT4327,Fabricación motor OT4327,Planos motor proveedor OT4327</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977075717403</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT4327</t>
-  </si>
-  <si>
-    <t>1214977075717413</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732911</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT4327</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT4327</t>
-  </si>
-  <si>
-    <t>1214969047720958</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe OT4327,Motor OT4327,rodete OT4327,Materiales corte Laser OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732921</t>
-  </si>
-  <si>
-    <t>Alabe OT4327</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT4327,Fabricación Alabe OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732936</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT4327</t>
-  </si>
-  <si>
-    <t>Alabe OT4327,Fabricación Alabe OT4327</t>
-  </si>
-  <si>
-    <t>1214977316760264</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT4327</t>
-  </si>
-  <si>
-    <t>Alabe OT4327,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214977533931641</t>
-  </si>
-  <si>
-    <t>rodete OT4327</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT4327,Generación OC Rodete OT4327</t>
-  </si>
-  <si>
-    <t>1214977533931656</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT4327</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT4327,rodete OT4327</t>
-  </si>
-  <si>
-    <t>1214977075779516</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT4327</t>
-  </si>
-  <si>
-    <t>rodete OT4327,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214977075779534</t>
-  </si>
-  <si>
-    <t>Motor OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT4327,Fabricación motor OT4327,Planos motor proveedor OT4327</t>
   </si>
   <si>
     <t>1214977075791024</t>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.16936103009</v>
+        <v>46190.17346704861</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -3033,8 +3033,8 @@
       <c r="R19" s="9">
         <v>46189</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>87</v>
+      <c r="S19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -3045,17 +3045,17 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46162.68133762731</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46185.1708371875</v>
+        <v>46190.17346712963</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3088,7 +3088,7 @@
         <v>85</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3096,8 +3096,8 @@
       <c r="R20" s="5">
         <v>46189</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>87</v>
+      <c r="S20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
@@ -3108,17 +3108,17 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46162.68134119213</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.16936292824</v>
+        <v>46190.17346684028</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3151,7 +3151,7 @@
         <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3159,8 +3159,8 @@
       <c r="R21" s="9">
         <v>46189</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>87</v>
+      <c r="S21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -3171,17 +3171,17 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46162.6813446875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46189.16936435185</v>
+        <v>46190.1734668287</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3214,7 +3214,7 @@
         <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46188</v>
@@ -3222,8 +3222,8 @@
       <c r="R22" s="5">
         <v>46189</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>87</v>
+      <c r="S22" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46162.68117578704</v>
@@ -3244,7 +3244,7 @@
         <v>46162.701055185185</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3268,7 +3268,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3281,7 +3281,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46162.681348645834</v>
@@ -3291,16 +3291,16 @@
         <v>46169.87666193287</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3318,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46155</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46162.68135300926</v>
@@ -3354,16 +3354,16 @@
         <v>46169.87692592593</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3381,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46162.68135747685</v>
@@ -3413,16 +3413,16 @@
         <v>46169.876936932866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3440,13 +3440,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46162.68136241898</v>
@@ -3472,16 +3472,16 @@
         <v>46169.876684965275</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3499,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q27" s="9">
         <v>46155</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46162.6813671412</v>
@@ -3535,16 +3535,16 @@
         <v>46169.87698153935</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3562,13 +3562,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46162.6813721875</v>
@@ -3594,16 +3594,16 @@
         <v>46169.87699585648</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3621,13 +3621,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46162.68137706019</v>
@@ -3653,16 +3653,16 @@
         <v>46188.19885825232</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3680,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q30" s="5">
         <v>46155</v>
@@ -3695,7 +3695,7 @@
         <v>46195</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3722,10 +3722,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="I31" s="9">
         <v>46155</v>
@@ -3743,7 +3743,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>72</v>
@@ -3781,10 +3781,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3802,7 +3802,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>124</v>
@@ -3840,10 +3840,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="I33" s="9">
         <v>46167</v>
@@ -3861,7 +3861,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>124</v>
@@ -3920,13 +3920,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q34" s="5">
         <v>46190</v>
@@ -4097,7 +4097,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>145</v>
@@ -4133,7 +4133,7 @@
         <v>46189.16936783565</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4163,7 +4163,7 @@
         <v>144</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>147</v>
@@ -4216,7 +4216,7 @@
         <v>144</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>150</v>
@@ -4266,7 +4266,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>155</v>
@@ -4302,7 +4302,7 @@
         <v>46169.87718591435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4332,7 +4332,7 @@
         <v>152</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>157</v>
@@ -4385,7 +4385,7 @@
         <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>160</v>
@@ -4488,7 +4488,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>167</v>
@@ -4524,7 +4524,7 @@
         <v>46169.87725965278</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4554,7 +4554,7 @@
         <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>169</v>
@@ -4607,7 +4607,7 @@
         <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>172</v>
@@ -7751,7 +7751,7 @@
         <v>205</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>284</v>
@@ -7812,7 +7812,7 @@
         <v>205</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>287</v>
@@ -7885,7 +7885,7 @@
         <v>46196</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.87708155093</v>
+        <v>46191.169341932866</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87725965278</v>
+        <v>46191.1693375926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>92</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.876684965275</v>
+        <v>46191.8521162963</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.19885825232</v>
+        <v>46191.85166767361</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46191.8521162963</v>
+        <v>46192.853174930555</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46191.85166767361</v>
+        <v>46192.85321752315</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.85321752315</v>
+        <v>46195.16987429398</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.87703478009</v>
+        <v>46195.16987640046</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.87671172454</v>
+        <v>46195.19788605324</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3934,8 +3934,8 @@
       <c r="R34" s="5">
         <v>46202</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>54</v>
+      <c r="S34" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.87672134259</v>
+        <v>46195.19788600694</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>144</v>
@@ -4111,8 +4111,8 @@
       <c r="R37" s="9">
         <v>46202</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>54</v>
+      <c r="S37" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.87675552083</v>
+        <v>46195.197886145834</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4502,8 +4502,8 @@
       <c r="R44" s="5">
         <v>46202</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>54</v>
+      <c r="S44" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.87789596065</v>
+        <v>46195.59170534722</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -398,49 +398,49 @@
     <t>Generación OC motor OT4327,Fabricación motor OT4327,Planos motor proveedor OT4327</t>
   </si>
   <si>
+    <t>1214977075791024</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT4327</t>
+  </si>
+  <si>
+    <t>Motor OT4327,Fabricación motor OT4327,Planos motor proveedor OT4327</t>
+  </si>
+  <si>
+    <t>1214977075791042</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT4327</t>
+  </si>
+  <si>
+    <t>Motor OT4327,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214977075795359</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT4327</t>
+  </si>
+  <si>
+    <t>Motor OT4327,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977075795377</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT4327</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser OT4327,Fabricacion Corte Lase OT4327 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977075791024</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT4327</t>
-  </si>
-  <si>
-    <t>Motor OT4327,Fabricación motor OT4327,Planos motor proveedor OT4327</t>
-  </si>
-  <si>
-    <t>1214977075791042</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT4327</t>
-  </si>
-  <si>
-    <t>Motor OT4327,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214977075795359</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT4327</t>
-  </si>
-  <si>
-    <t>Motor OT4327,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977075795377</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT4327</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser OT4327,Fabricacion Corte Lase OT4327 </t>
   </si>
   <si>
     <t>1214977533942291</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.16987429398</v>
+        <v>46196.1721819213</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3694,8 +3694,8 @@
       <c r="R30" s="5">
         <v>46195</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>122</v>
+      <c r="S30" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46162.681382083334</v>
@@ -3716,7 +3716,7 @@
         <v>46169.877024456015</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3749,7 +3749,7 @@
         <v>72</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3765,7 +3765,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46162.681387523146</v>
@@ -3775,7 +3775,7 @@
         <v>46195.16987640046</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3805,10 +3805,10 @@
         <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46162.68139224537</v>
@@ -3834,7 +3834,7 @@
         <v>46175.17037224537</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3864,10 +3864,10 @@
         <v>120</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46162.68139699074</v>
@@ -3893,16 +3893,16 @@
         <v>46195.19788605324</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I34" s="5">
         <v>46190</v>
@@ -3923,7 +3923,7 @@
         <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>97</v>
@@ -3935,7 +3935,7 @@
         <v>46202</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46190</v>
@@ -3983,7 +3983,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>82</v>
@@ -4021,10 +4021,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
@@ -4038,7 +4038,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>138</v>
@@ -4076,10 +4076,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46190</v>
@@ -4112,7 +4112,7 @@
         <v>46202</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
@@ -4139,10 +4139,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46188</v>
@@ -4192,10 +4192,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46192</v>
@@ -4467,10 +4467,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I44" s="5">
         <v>46190</v>
@@ -4503,7 +4503,7 @@
         <v>46202</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4530,10 +4530,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I45" s="9">
         <v>46190</v>
@@ -4583,10 +4583,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I46" s="5">
         <v>46192</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46162.76302409722</v>
+        <v>46196.168763634254</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>208</v>
@@ -5523,8 +5523,8 @@
       <c r="R63" s="9">
         <v>46203</v>
       </c>
-      <c r="S63" s="7" t="s">
-        <v>54</v>
+      <c r="S63" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46162.76302130787</v>
+        <v>46196.16876357639</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>217</v>
@@ -5645,8 +5645,8 @@
       <c r="R65" s="9">
         <v>46203</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>54</v>
+      <c r="S65" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46162.76301679398</v>
+        <v>46196.16876371528</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5767,8 +5767,8 @@
       <c r="R67" s="9">
         <v>46203</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>54</v>
+      <c r="S67" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46189.1766387963</v>
+        <v>46196.16910078704</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7873,7 +7873,7 @@
         <v>205</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>290</v>
@@ -7885,7 +7885,7 @@
         <v>46196</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46195.59170534722</v>
+        <v>46196.60177111111</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -860,7 +860,7 @@
     <t>1214977317069425</t>
   </si>
   <si>
-    <t xml:space="preserve">OT7 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214977317069435</t>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46162.763137754635</v>
+        <v>46197.17514756945</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5584,8 +5584,8 @@
       <c r="R64" s="5">
         <v>46204</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>54</v>
+      <c r="S64" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46162.763134594905</v>
+        <v>46197.175148090275</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>220</v>
@@ -5706,8 +5706,8 @@
       <c r="R66" s="5">
         <v>46204</v>
       </c>
-      <c r="S66" s="7" t="s">
-        <v>54</v>
+      <c r="S66" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.763131238426</v>
+        <v>46197.17514795139</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>224</v>
@@ -5828,8 +5828,8 @@
       <c r="R68" s="5">
         <v>46204</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>54</v>
+      <c r="S68" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46196.16910078704</v>
+        <v>46197.17676240741</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7884,8 +7884,8 @@
       <c r="R106" s="5">
         <v>46196</v>
       </c>
-      <c r="S106" s="12" t="s">
-        <v>136</v>
+      <c r="S106" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46162.689903715276</v>
+        <v>46197.587885057874</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2924,9 +2924,11 @@
       <c r="B18" s="5">
         <v>46162.68132700231</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46197.587876516205</v>
+      </c>
       <c r="D18" s="5">
-        <v>46169.87678987268</v>
+        <v>46197.587896655095</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2974,10 +2976,10 @@
         <v>54</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3532,7 +3534,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.87698153935</v>
+        <v>46197.58788623843</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="473">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -182,7 +182,9 @@
     <t>cperez@zitron.com</t>
   </si>
   <si>
-    <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
+    <t xml:space="preserve">MOTOR
+        OT 4327 — ZVN 2-9-103/2 -- MOTOR 103 KW Doble eje, 280 S/M, 2 Polos, 60 Hz, 460 v
+</t>
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor OT4327</t>
@@ -191,34 +193,46 @@
     <t>Baja</t>
   </si>
   <si>
+    <t>1214977075698289</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Rodete:
+        OT 4327 Ventilador ZVN 2-9-103/2 --- COD. ALABES: 300000
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta alabes OT4327,propuesta nucleo rodete OT4327</t>
+  </si>
+  <si>
+    <t>1214977075699571</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P.1553
+        OT 4327: 10 ventiladores ZVN 2-9-103/2
+    Planos para:
+        Ventilador ZVN 2-9-103/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 90/100 + VENT + FAR 90/100 + TIPO A
+        Alcance Chile: TOBERA + REJILLA + VENT
+        Alcance Colombia: FAR + DIFUSOR
+    Rodete:
+        Ventilador ZVN 1-12-55/4 --- ALABES: 300004
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        440V, 60HZ, IP55, IE-3, 1000 MSNM.
+        Incluye: Sensor de vibraciones VKV 021 y Graseras automáticas con protección mecánica.
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214977075698289</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta alabes OT4327,propuesta nucleo rodete OT4327</t>
-  </si>
-  <si>
-    <t>1214977075699571</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
   </si>
   <si>
     <t>1214977316716053</t>
@@ -2454,7 +2468,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46162.689633738424</v>
+        <v>46197.669773472226</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2499,9 +2513,11 @@
       <c r="B11" s="9">
         <v>46162.68129303241</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46197.66700505787</v>
+      </c>
       <c r="D11" s="9">
-        <v>46196.60177111111</v>
+        <v>46197.66702116898</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>49</v>
@@ -2549,25 +2565,27 @@
         <v>54</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46162.68129826389</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.66976853009</v>
+      </c>
       <c r="D12" s="5">
-        <v>46175.8778958912</v>
+        <v>46197.66978386574</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2588,7 +2606,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2600,7 +2618,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2612,25 +2630,25 @@
         <v>54</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46162.68130347222</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46175.8778966088</v>
+        <v>46197.670623125</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2651,7 +2669,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2678,22 +2696,22 @@
         <v>0</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46162.6813085301</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46162.760315381944</v>
+        <v>46197.669773981484</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2723,10 +2741,10 @@
         <v>46</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="5">
         <v>46149</v>
@@ -2741,12 +2759,12 @@
         <v>0</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="9">
         <v>46162.68117188658</v>
@@ -2756,7 +2774,7 @@
         <v>46197.587885057874</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>25</v>
@@ -2780,7 +2798,7 @@
         <v>26</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>26</v>
@@ -2793,17 +2811,17 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5">
         <v>46162.681316030095</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46169.876765532405</v>
+        <v>46197.66702332176</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2830,13 +2848,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46153</v>
@@ -2850,23 +2868,23 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="11" t="s">
-        <v>67</v>
+      <c r="U16" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="9">
         <v>46162.68132108796</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46169.876775613426</v>
+        <v>46197.66978644676</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2893,13 +2911,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46153</v>
@@ -2913,13 +2931,13 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>67</v>
+      <c r="U17" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46162.68132700231</v>
@@ -2928,19 +2946,19 @@
         <v>46197.587876516205</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.587896655095</v>
+        <v>46197.66978645833</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I18" s="5">
         <v>46153</v>
@@ -2958,13 +2976,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46153</v>
@@ -2978,13 +2996,13 @@
       <c r="T18" s="6">
         <v>1</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>27</v>
+      <c r="U18" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46162.68133263889</v>
@@ -2994,16 +3012,16 @@
         <v>46190.17346704861</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I19" s="9">
         <v>46188</v>
@@ -3021,13 +3039,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="9">
         <v>46188</v>
@@ -3042,12 +3060,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
         <v>46162.68133762731</v>
@@ -3057,16 +3075,16 @@
         <v>46190.17346712963</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I20" s="5">
         <v>46184</v>
@@ -3084,13 +3102,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3105,12 +3123,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" s="9">
         <v>46162.68134119213</v>
@@ -3120,16 +3138,16 @@
         <v>46190.17346684028</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="9">
         <v>46188</v>
@@ -3147,13 +3165,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3168,12 +3186,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46162.6813446875</v>
@@ -3183,16 +3201,16 @@
         <v>46190.1734668287</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46188</v>
@@ -3210,13 +3228,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="5">
         <v>46188</v>
@@ -3231,12 +3249,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46162.68117578704</v>
@@ -3246,7 +3264,7 @@
         <v>46162.701055185185</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3270,7 +3288,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3283,7 +3301,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46162.681348645834</v>
@@ -3293,16 +3311,16 @@
         <v>46169.87666193287</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3320,13 +3338,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46155</v>
@@ -3341,12 +3359,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46162.68135300926</v>
@@ -3356,16 +3374,16 @@
         <v>46169.87692592593</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I25" s="9">
         <v>46155</v>
@@ -3383,13 +3401,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3400,12 +3418,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46162.68135747685</v>
@@ -3415,16 +3433,16 @@
         <v>46169.876936932866</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3442,13 +3460,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3459,12 +3477,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46162.68136241898</v>
@@ -3474,16 +3492,16 @@
         <v>46192.853174930555</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3501,13 +3519,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="9">
         <v>46155</v>
@@ -3522,12 +3540,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46162.6813671412</v>
@@ -3537,16 +3555,16 @@
         <v>46197.58788623843</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3564,13 +3582,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3581,12 +3599,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46162.6813721875</v>
@@ -3596,16 +3614,16 @@
         <v>46169.87699585648</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3623,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3640,12 +3658,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46162.68137706019</v>
@@ -3655,16 +3673,16 @@
         <v>46196.1721819213</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3682,13 +3700,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="5">
         <v>46155</v>
@@ -3703,12 +3721,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46162.681382083334</v>
@@ -3718,16 +3736,16 @@
         <v>46169.877024456015</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" s="9">
         <v>46155</v>
@@ -3745,13 +3763,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3762,12 +3780,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46162.681387523146</v>
@@ -3777,16 +3795,16 @@
         <v>46195.16987640046</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3804,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3821,12 +3839,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46162.68139224537</v>
@@ -3836,16 +3854,16 @@
         <v>46175.17037224537</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I33" s="9">
         <v>46167</v>
@@ -3863,13 +3881,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3880,12 +3898,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46162.68139699074</v>
@@ -3895,16 +3913,16 @@
         <v>46195.19788605324</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I34" s="5">
         <v>46190</v>
@@ -3922,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q34" s="5">
         <v>46190</v>
@@ -3937,18 +3955,18 @@
         <v>46202</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46162.68140180556</v>
@@ -3958,16 +3976,16 @@
         <v>46191.169341932866</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46190</v>
@@ -3985,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4002,12 +4020,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46162.681406793985</v>
@@ -4017,16 +4035,16 @@
         <v>46169.87710333333</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
@@ -4040,13 +4058,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -4057,12 +4075,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46162.68146234954</v>
@@ -4072,16 +4090,16 @@
         <v>46195.19788600694</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46190</v>
@@ -4099,10 +4117,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4114,18 +4132,18 @@
         <v>46202</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46162.68146784722</v>
@@ -4135,16 +4153,16 @@
         <v>46189.16936783565</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46188</v>
@@ -4162,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4178,7 +4196,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.68147298611</v>
@@ -4188,16 +4206,16 @@
         <v>46169.87714701389</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46192</v>
@@ -4215,13 +4233,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4231,7 +4249,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46162.681477175924</v>
@@ -4241,16 +4259,16 @@
         <v>46169.876735</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I40" s="5">
         <v>46190</v>
@@ -4268,10 +4286,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -4289,12 +4307,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="9">
         <v>46162.68148049769</v>
@@ -4304,16 +4322,16 @@
         <v>46169.87718591435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I41" s="9">
         <v>46190</v>
@@ -4331,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4347,7 +4365,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.681484872686</v>
@@ -4357,16 +4375,16 @@
         <v>46169.87719863426</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46199</v>
@@ -4384,13 +4402,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4400,7 +4418,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46162.68148924768</v>
@@ -4410,16 +4428,16 @@
         <v>46169.877211388884</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I43" s="9">
         <v>46230</v>
@@ -4437,10 +4455,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4453,7 +4471,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46162.68149232639</v>
@@ -4463,16 +4481,16 @@
         <v>46195.197886145834</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I44" s="5">
         <v>46190</v>
@@ -4490,10 +4508,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4505,18 +4523,18 @@
         <v>46202</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" s="9">
         <v>46162.68149587963</v>
@@ -4526,16 +4544,16 @@
         <v>46191.1693375926</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I45" s="9">
         <v>46190</v>
@@ -4553,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4569,7 +4587,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46162.6815003125</v>
@@ -4579,16 +4597,16 @@
         <v>46169.87727920139</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5">
         <v>46192</v>
@@ -4606,13 +4624,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4622,7 +4640,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.68117938658</v>
@@ -4632,7 +4650,7 @@
         <v>46162.70636487268</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4656,7 +4674,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4669,7 +4687,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46162.68150506944</v>
@@ -4679,16 +4697,16 @@
         <v>46168.16746090278</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46160</v>
@@ -4706,13 +4724,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46160</v>
@@ -4727,12 +4745,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46162.68151027778</v>
@@ -4742,16 +4760,16 @@
         <v>46185.182528391204</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I49" s="9">
         <v>46176</v>
@@ -4769,13 +4787,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46176</v>
@@ -4790,12 +4808,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46162.6815165625</v>
@@ -4805,16 +4823,16 @@
         <v>46186.16887460648</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I50" s="5">
         <v>46185</v>
@@ -4832,13 +4850,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46185</v>
@@ -4853,12 +4871,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46162.68153015046</v>
@@ -4868,16 +4886,16 @@
         <v>46162.76230295139</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4893,10 +4911,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4914,12 +4932,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46162.68153354166</v>
@@ -4929,16 +4947,16 @@
         <v>46162.76229798611</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4954,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4970,7 +4988,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46162.68153736111</v>
@@ -4980,16 +4998,16 @@
         <v>46162.76229449074</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5005,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5021,7 +5039,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46162.68154143519</v>
@@ -5031,16 +5049,16 @@
         <v>46162.76229145833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5056,13 +5074,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5072,7 +5090,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46162.68154440972</v>
@@ -5082,16 +5100,16 @@
         <v>46162.76228877315</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5107,13 +5125,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5123,7 +5141,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46162.68154740741</v>
@@ -5133,16 +5151,16 @@
         <v>46162.76228596065</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5158,13 +5176,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5174,7 +5192,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="9">
         <v>46162.68155047453</v>
@@ -5184,16 +5202,16 @@
         <v>46162.762282870375</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5209,10 +5227,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5225,7 +5243,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46162.681552766204</v>
@@ -5235,16 +5253,16 @@
         <v>46162.76227917824</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5260,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5276,7 +5294,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46162.68155516204</v>
@@ -5286,16 +5304,16 @@
         <v>46162.76227634259</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5311,13 +5329,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5327,7 +5345,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46162.6815574537</v>
@@ -5337,16 +5355,16 @@
         <v>46162.7622690162</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5362,10 +5380,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5378,7 +5396,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46162.68155952546</v>
@@ -5388,16 +5406,16 @@
         <v>46162.762268391205</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5413,10 +5431,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5429,7 +5447,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46162.681598807874</v>
@@ -5439,7 +5457,7 @@
         <v>46162.707360960645</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5463,7 +5481,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5476,7 +5494,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" s="9">
         <v>46162.681602743054</v>
@@ -5486,16 +5504,16 @@
         <v>46196.168763634254</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5511,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="9">
         <v>46203</v>
@@ -5526,18 +5544,18 @@
         <v>46203</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
         <v>46162.68160836806</v>
@@ -5547,16 +5565,16 @@
         <v>46197.17514756945</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5572,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46204</v>
@@ -5587,18 +5605,18 @@
         <v>46204</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46162.681615208334</v>
@@ -5608,16 +5626,16 @@
         <v>46196.16876357639</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="9">
@@ -5633,13 +5651,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46203</v>
@@ -5648,18 +5666,18 @@
         <v>46203</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46162.68162069445</v>
@@ -5669,16 +5687,16 @@
         <v>46197.175148090275</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5694,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="5">
         <v>46204</v>
@@ -5709,18 +5727,18 @@
         <v>46204</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B67" s="9">
         <v>46162.681625983794</v>
@@ -5730,16 +5748,16 @@
         <v>46196.16876371528</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5755,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67" s="9">
         <v>46203</v>
@@ -5770,18 +5788,18 @@
         <v>46203</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
         <v>46162.68163075231</v>
@@ -5791,16 +5809,16 @@
         <v>46197.17514795139</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5816,13 +5834,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46204</v>
@@ -5831,18 +5849,18 @@
         <v>46204</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B69" s="9">
         <v>46162.68163611111</v>
@@ -5852,7 +5870,7 @@
         <v>46162.763323391206</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5876,7 +5894,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5889,7 +5907,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46162.6816390162</v>
@@ -5899,16 +5917,16 @@
         <v>46162.763335578704</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I70" s="5">
         <v>46205</v>
@@ -5926,13 +5944,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q70" s="5">
         <v>46205</v>
@@ -5947,12 +5965,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46162.68164390046</v>
@@ -5962,16 +5980,16 @@
         <v>46162.763318530095</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -5989,13 +6007,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6005,7 +6023,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.681651203704</v>
@@ -6015,16 +6033,16 @@
         <v>46162.76331560186</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6042,13 +6060,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6058,7 +6076,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.68165733796</v>
@@ -6068,16 +6086,16 @@
         <v>46162.76331271991</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6095,13 +6113,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6111,7 +6129,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.68166336806</v>
@@ -6121,16 +6139,16 @@
         <v>46162.763309710645</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6148,13 +6166,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6164,7 +6182,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.68166935185</v>
@@ -6174,16 +6192,16 @@
         <v>46162.763306759254</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6201,13 +6219,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6217,7 +6235,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46162.68167571759</v>
@@ -6227,16 +6245,16 @@
         <v>46162.76330359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6254,13 +6272,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6270,7 +6288,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.68168109954</v>
@@ -6280,16 +6298,16 @@
         <v>46162.7633006713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6307,13 +6325,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6323,7 +6341,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46162.68168630787</v>
@@ -6333,16 +6351,16 @@
         <v>46162.763297384256</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6360,13 +6378,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6376,7 +6394,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
         <v>46162.68169194444</v>
@@ -6386,16 +6404,16 @@
         <v>46162.763290891206</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6413,13 +6431,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6429,7 +6447,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
         <v>46162.681698229164</v>
@@ -6439,16 +6457,16 @@
         <v>46162.763290243056</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6466,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6482,7 +6500,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B81" s="9">
         <v>46162.68171431713</v>
@@ -6492,16 +6510,16 @@
         <v>46162.76361657407</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I81" s="9">
         <v>46210</v>
@@ -6519,13 +6537,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q81" s="9">
         <v>46210</v>
@@ -6540,12 +6558,12 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46162.681718935186</v>
@@ -6555,16 +6573,16 @@
         <v>46162.763601388884</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I82" s="5">
         <v>46210</v>
@@ -6582,13 +6600,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6598,7 +6616,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="9">
         <v>46162.68172515046</v>
@@ -6608,16 +6626,16 @@
         <v>46162.76359828704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I83" s="9">
         <v>46210</v>
@@ -6635,13 +6653,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6651,7 +6669,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46162.68173074074</v>
@@ -6661,16 +6679,16 @@
         <v>46162.763595428245</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6688,13 +6706,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6704,7 +6722,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46162.68173619213</v>
@@ -6714,16 +6732,16 @@
         <v>46162.76359266204</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6741,13 +6759,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6757,7 +6775,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B86" s="5">
         <v>46162.681741747685</v>
@@ -6767,16 +6785,16 @@
         <v>46162.763589780094</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6794,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6810,7 +6828,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B87" s="9">
         <v>46162.68178277778</v>
@@ -6820,16 +6838,16 @@
         <v>46162.763586388886</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -6847,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6863,7 +6881,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B88" s="5">
         <v>46162.68178671296</v>
@@ -6873,16 +6891,16 @@
         <v>46162.763583657405</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -6900,10 +6918,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6916,7 +6934,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B89" s="9">
         <v>46162.68178976852</v>
@@ -6926,16 +6944,16 @@
         <v>46162.763580983796</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -6953,13 +6971,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6969,7 +6987,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B90" s="5">
         <v>46162.68179300926</v>
@@ -6979,16 +6997,16 @@
         <v>46162.76357417824</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7006,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7022,7 +7040,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B91" s="9">
         <v>46162.68179625</v>
@@ -7032,16 +7050,16 @@
         <v>46162.763573530094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7059,13 +7077,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7075,7 +7093,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B92" s="5">
         <v>46162.681806875</v>
@@ -7085,16 +7103,16 @@
         <v>46162.763839050924</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I92" s="5">
         <v>46217</v>
@@ -7112,13 +7130,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q92" s="5">
         <v>46217</v>
@@ -7133,12 +7151,12 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B93" s="9">
         <v>46162.68181175926</v>
@@ -7148,16 +7166,16 @@
         <v>46162.76379824074</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I93" s="9">
         <v>46217</v>
@@ -7175,13 +7193,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7191,7 +7209,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="5">
         <v>46162.68181751158</v>
@@ -7201,16 +7219,16 @@
         <v>46162.76379479167</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I94" s="5">
         <v>46217</v>
@@ -7228,13 +7246,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7244,7 +7262,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B95" s="9">
         <v>46162.681823032406</v>
@@ -7254,16 +7272,16 @@
         <v>46162.763791562495</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I95" s="9">
         <v>46217</v>
@@ -7281,13 +7299,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7297,7 +7315,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46162.681828368055</v>
@@ -7307,16 +7325,16 @@
         <v>46162.76378862269</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I96" s="5">
         <v>46217</v>
@@ -7334,13 +7352,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7350,7 +7368,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46162.68183400463</v>
@@ -7360,16 +7378,16 @@
         <v>46162.763785347226</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7387,13 +7405,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7403,7 +7421,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B98" s="5">
         <v>46162.6818390625</v>
@@ -7413,16 +7431,16 @@
         <v>46162.763782152775</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7440,13 +7458,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7456,7 +7474,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B99" s="9">
         <v>46162.68184208333</v>
@@ -7466,16 +7484,16 @@
         <v>46162.76377949074</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7493,13 +7511,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7509,7 +7527,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B100" s="5">
         <v>46162.6818458912</v>
@@ -7519,16 +7537,16 @@
         <v>46162.76377262731</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7546,13 +7564,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7562,7 +7580,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B101" s="9">
         <v>46162.681849375</v>
@@ -7572,16 +7590,16 @@
         <v>46162.76377197917</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7599,13 +7617,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7615,7 +7633,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B102" s="5">
         <v>46162.68185259259</v>
@@ -7625,16 +7643,16 @@
         <v>46162.7637712963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I102" s="5">
         <v>46217</v>
@@ -7652,13 +7670,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7668,7 +7686,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B103" s="9">
         <v>46162.681862557874</v>
@@ -7678,7 +7696,7 @@
         <v>46162.708598171295</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7702,7 +7720,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7715,7 +7733,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B104" s="5">
         <v>46162.68186600694</v>
@@ -7725,16 +7743,16 @@
         <v>46162.76398071759</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7750,13 +7768,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="5">
         <v>46161</v>
@@ -7771,12 +7789,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46162.681872870366</v>
@@ -7786,16 +7804,16 @@
         <v>46162.763977916664</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7811,13 +7829,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q105" s="9">
         <v>46161</v>
@@ -7832,12 +7850,12 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46162.681879930555</v>
@@ -7847,16 +7865,16 @@
         <v>46197.17676240741</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7872,13 +7890,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46196</v>
@@ -7893,12 +7911,12 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46162.681886412036</v>
@@ -7908,16 +7926,16 @@
         <v>46162.763970266205</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7933,13 +7951,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q107" s="9">
         <v>46232</v>
@@ -7954,12 +7972,12 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46162.68189086806</v>
@@ -7969,7 +7987,7 @@
         <v>46162.710864479166</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>25</v>
@@ -7993,7 +8011,7 @@
         <v>26</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8006,7 +8024,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B109" s="9">
         <v>46162.681893761575</v>
@@ -8016,16 +8034,16 @@
         <v>46162.76425648148</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I109" s="9">
         <v>46218</v>
@@ -8043,13 +8061,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q109" s="9">
         <v>46218</v>
@@ -8064,12 +8082,12 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B110" s="5">
         <v>46162.68190694445</v>
@@ -8079,16 +8097,16 @@
         <v>46162.764253263886</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I110" s="5">
         <v>46218</v>
@@ -8106,10 +8124,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8122,7 +8140,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B111" s="9">
         <v>46162.68191104167</v>
@@ -8132,16 +8150,16 @@
         <v>46162.76425003472</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I111" s="9">
         <v>46218</v>
@@ -8159,10 +8177,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8175,7 +8193,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B112" s="5">
         <v>46162.68191516204</v>
@@ -8185,16 +8203,16 @@
         <v>46162.764246273146</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I112" s="5">
         <v>46218</v>
@@ -8212,13 +8230,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8228,7 +8246,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B113" s="9">
         <v>46162.68191947917</v>
@@ -8238,16 +8256,16 @@
         <v>46162.76424304398</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I113" s="9">
         <v>46218</v>
@@ -8265,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8281,7 +8299,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B114" s="5">
         <v>46162.68192371528</v>
@@ -8291,16 +8309,16 @@
         <v>46162.764240081015</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I114" s="5">
         <v>46218</v>
@@ -8318,13 +8336,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8334,7 +8352,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B115" s="9">
         <v>46162.68192716435</v>
@@ -8344,16 +8362,16 @@
         <v>46162.76423697917</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I115" s="9">
         <v>46218</v>
@@ -8371,13 +8389,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8387,7 +8405,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B116" s="5">
         <v>46162.6819303588</v>
@@ -8397,16 +8415,16 @@
         <v>46162.76423423611</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I116" s="5">
         <v>46218</v>
@@ -8424,13 +8442,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8440,7 +8458,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B117" s="9">
         <v>46162.6819334375</v>
@@ -8450,16 +8468,16 @@
         <v>46162.76423152778</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I117" s="9">
         <v>46218</v>
@@ -8477,13 +8495,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8493,7 +8511,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B118" s="5">
         <v>46162.68193662037</v>
@@ -8503,16 +8521,16 @@
         <v>46162.764224479164</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I118" s="5">
         <v>46218</v>
@@ -8530,13 +8548,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8546,7 +8564,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B119" s="9">
         <v>46162.68193976852</v>
@@ -8556,16 +8574,16 @@
         <v>46162.76422390046</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I119" s="9">
         <v>46218</v>
@@ -8583,13 +8601,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8599,7 +8617,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B120" s="5">
         <v>46162.68199361111</v>
@@ -8609,16 +8627,16 @@
         <v>46162.76445266204</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I120" s="5">
         <v>46219</v>
@@ -8636,13 +8654,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q120" s="5">
         <v>46219</v>
@@ -8657,12 +8675,12 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B121" s="9">
         <v>46162.68199872685</v>
@@ -8672,16 +8690,16 @@
         <v>46162.764425138885</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I121" s="9">
         <v>46219</v>
@@ -8699,13 +8717,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8715,7 +8733,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46162.6820043287</v>
@@ -8725,16 +8743,16 @@
         <v>46162.7644221875</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I122" s="5">
         <v>46219</v>
@@ -8752,13 +8770,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8768,7 +8786,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B123" s="9">
         <v>46162.68200945602</v>
@@ -8778,16 +8796,16 @@
         <v>46162.76441872685</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I123" s="9">
         <v>46219</v>
@@ -8805,13 +8823,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8821,7 +8839,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B124" s="5">
         <v>46162.68201590278</v>
@@ -8831,16 +8849,16 @@
         <v>46162.76441527778</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I124" s="5">
         <v>46219</v>
@@ -8858,13 +8876,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8874,7 +8892,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46162.682022175926</v>
@@ -8884,16 +8902,16 @@
         <v>46162.76441243055</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I125" s="9">
         <v>46219</v>
@@ -8911,13 +8929,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8927,7 +8945,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B126" s="5">
         <v>46162.68202664352</v>
@@ -8937,16 +8955,16 @@
         <v>46162.76440929398</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I126" s="5">
         <v>46219</v>
@@ -8964,13 +8982,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8980,7 +8998,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B127" s="9">
         <v>46162.682031874996</v>
@@ -8990,16 +9008,16 @@
         <v>46162.76440640046</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I127" s="9">
         <v>46219</v>
@@ -9017,13 +9035,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9033,7 +9051,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B128" s="5">
         <v>46162.682037129634</v>
@@ -9043,16 +9061,16 @@
         <v>46162.764403761576</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I128" s="5">
         <v>46219</v>
@@ -9070,13 +9088,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9086,7 +9104,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B129" s="9">
         <v>46162.68204233796</v>
@@ -9096,16 +9114,16 @@
         <v>46162.764396388884</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I129" s="9">
         <v>46219</v>
@@ -9123,13 +9141,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9139,7 +9157,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B130" s="5">
         <v>46162.68204753472</v>
@@ -9149,16 +9167,16 @@
         <v>46162.76439568287</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I130" s="5">
         <v>46219</v>
@@ -9176,13 +9194,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9192,7 +9210,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B131" s="9">
         <v>46162.68206118056</v>
@@ -9202,16 +9220,16 @@
         <v>46162.76461746528</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I131" s="9">
         <v>46220</v>
@@ -9229,13 +9247,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q131" s="9">
         <v>46220</v>
@@ -9250,12 +9268,12 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B132" s="5">
         <v>46162.68206542824</v>
@@ -9265,16 +9283,16 @@
         <v>46162.76461333333</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I132" s="5">
         <v>46220</v>
@@ -9292,13 +9310,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9308,7 +9326,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B133" s="9">
         <v>46162.68207142361</v>
@@ -9318,16 +9336,16 @@
         <v>46162.764610439815</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I133" s="9">
         <v>46220</v>
@@ -9345,13 +9363,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9361,7 +9379,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46162.682082997686</v>
@@ -9371,16 +9389,16 @@
         <v>46162.76460753472</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I134" s="5">
         <v>46220</v>
@@ -9398,13 +9416,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9414,7 +9432,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B135" s="9">
         <v>46162.682089317124</v>
@@ -9424,16 +9442,16 @@
         <v>46162.76460444444</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I135" s="9">
         <v>46220</v>
@@ -9451,13 +9469,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9467,7 +9485,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B136" s="5">
         <v>46162.68209565972</v>
@@ -9477,16 +9495,16 @@
         <v>46162.764601250004</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I136" s="5">
         <v>46220</v>
@@ -9504,13 +9522,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9520,7 +9538,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B137" s="9">
         <v>46162.68209994213</v>
@@ -9530,16 +9548,16 @@
         <v>46162.76459766204</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I137" s="9">
         <v>46220</v>
@@ -9557,13 +9575,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9573,7 +9591,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B138" s="5">
         <v>46162.682104189815</v>
@@ -9583,16 +9601,16 @@
         <v>46162.76459489584</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I138" s="5">
         <v>46220</v>
@@ -9610,13 +9628,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9626,7 +9644,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B139" s="9">
         <v>46162.68210733796</v>
@@ -9636,16 +9654,16 @@
         <v>46162.76458689815</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I139" s="9">
         <v>46220</v>
@@ -9663,13 +9681,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9679,7 +9697,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B140" s="5">
         <v>46162.68211155092</v>
@@ -9689,16 +9707,16 @@
         <v>46162.76458621528</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I140" s="5">
         <v>46220</v>
@@ -9716,13 +9734,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9732,7 +9750,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B141" s="9">
         <v>46162.68211587963</v>
@@ -9742,16 +9760,16 @@
         <v>46162.76458552083</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I141" s="9">
         <v>46220</v>
@@ -9769,13 +9787,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9785,7 +9803,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B142" s="5">
         <v>46162.68212817129</v>
@@ -9795,16 +9813,16 @@
         <v>46162.76477166667</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I142" s="5">
         <v>46223</v>
@@ -9822,13 +9840,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q142" s="5">
         <v>46223</v>
@@ -9843,12 +9861,12 @@
         <v>0</v>
       </c>
       <c r="U142" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B143" s="9">
         <v>46162.68213233796</v>
@@ -9858,16 +9876,16 @@
         <v>46162.76477363426</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I143" s="9">
         <v>46223</v>
@@ -9885,13 +9903,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9901,7 +9919,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B144" s="5">
         <v>46162.682137881944</v>
@@ -9911,16 +9929,16 @@
         <v>46162.76477071759</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I144" s="5">
         <v>46223</v>
@@ -9938,13 +9956,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9954,7 +9972,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B145" s="9">
         <v>46162.682143275466</v>
@@ -9964,16 +9982,16 @@
         <v>46162.764767141205</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I145" s="9">
         <v>46223</v>
@@ -9991,13 +10009,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10007,7 +10025,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B146" s="5">
         <v>46162.68214959491</v>
@@ -10017,16 +10035,16 @@
         <v>46162.764764039355</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I146" s="5">
         <v>46223</v>
@@ -10044,13 +10062,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10060,7 +10078,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B147" s="9">
         <v>46162.6821980324</v>
@@ -10070,16 +10088,16 @@
         <v>46162.76476091435</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I147" s="9">
         <v>46223</v>
@@ -10097,13 +10115,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10113,7 +10131,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B148" s="5">
         <v>46162.68220454861</v>
@@ -10123,16 +10141,16 @@
         <v>46162.76475773148</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I148" s="5">
         <v>46223</v>
@@ -10150,13 +10168,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10166,7 +10184,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B149" s="9">
         <v>46162.6822112963</v>
@@ -10176,16 +10194,16 @@
         <v>46162.76475452546</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I149" s="9">
         <v>46223</v>
@@ -10203,13 +10221,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10219,7 +10237,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B150" s="5">
         <v>46162.68221605324</v>
@@ -10229,16 +10247,16 @@
         <v>46162.764749594906</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I150" s="5">
         <v>46223</v>
@@ -10256,13 +10274,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10272,7 +10290,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B151" s="9">
         <v>46162.68222200232</v>
@@ -10282,16 +10300,16 @@
         <v>46162.76474296296</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I151" s="9">
         <v>46223</v>
@@ -10309,13 +10327,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10325,7 +10343,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B152" s="5">
         <v>46162.68222814814</v>
@@ -10335,16 +10353,16 @@
         <v>46162.764742141204</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I152" s="5">
         <v>46223</v>
@@ -10362,13 +10380,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10378,7 +10396,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B153" s="9">
         <v>46162.68224497685</v>
@@ -10388,16 +10406,16 @@
         <v>46162.76494858797</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I153" s="9">
         <v>46224</v>
@@ -10415,13 +10433,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q153" s="9">
         <v>46224</v>
@@ -10436,12 +10454,12 @@
         <v>0</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B154" s="5">
         <v>46162.68224997685</v>
@@ -10451,16 +10469,16 @@
         <v>46162.764935011575</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I154" s="5">
         <v>46224</v>
@@ -10478,13 +10496,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10494,7 +10512,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B155" s="9">
         <v>46162.682255844906</v>
@@ -10504,16 +10522,16 @@
         <v>46162.76493179398</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I155" s="9">
         <v>46224</v>
@@ -10531,13 +10549,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10547,7 +10565,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B156" s="5">
         <v>46162.682261354166</v>
@@ -10557,16 +10575,16 @@
         <v>46162.76492869213</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I156" s="5">
         <v>46224</v>
@@ -10584,13 +10602,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10600,7 +10618,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B157" s="9">
         <v>46162.68226693287</v>
@@ -10610,16 +10628,16 @@
         <v>46162.764925613425</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I157" s="9">
         <v>46224</v>
@@ -10637,13 +10655,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10653,7 +10671,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B158" s="5">
         <v>46162.68227229167</v>
@@ -10663,16 +10681,16 @@
         <v>46162.76492271991</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I158" s="5">
         <v>46224</v>
@@ -10690,13 +10708,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10706,7 +10724,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B159" s="9">
         <v>46162.68227762732</v>
@@ -10716,16 +10734,16 @@
         <v>46162.764919444446</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I159" s="9">
         <v>46224</v>
@@ -10743,10 +10761,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10759,7 +10777,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B160" s="5">
         <v>46162.68228032408</v>
@@ -10769,16 +10787,16 @@
         <v>46162.76491637732</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I160" s="5">
         <v>46224</v>
@@ -10796,13 +10814,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10812,7 +10830,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B161" s="9">
         <v>46162.68228446759</v>
@@ -10822,16 +10840,16 @@
         <v>46162.76491366898</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I161" s="9">
         <v>46224</v>
@@ -10849,10 +10867,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10865,7 +10883,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B162" s="5">
         <v>46162.68228719907</v>
@@ -10875,16 +10893,16 @@
         <v>46162.764907199075</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I162" s="5">
         <v>46224</v>
@@ -10902,10 +10920,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>26</v>
@@ -10918,7 +10936,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B163" s="9">
         <v>46162.68229016203</v>
@@ -10928,16 +10946,16 @@
         <v>46162.76490642361</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I163" s="9">
         <v>46224</v>
@@ -10955,10 +10973,10 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P163" s="10" t="s">
         <v>26</v>
@@ -10971,7 +10989,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B164" s="5">
         <v>46162.68230002315</v>
@@ -10981,16 +10999,16 @@
         <v>46162.7651559838</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I164" s="5">
         <v>46226</v>
@@ -11008,13 +11026,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q164" s="5">
         <v>46226</v>
@@ -11029,12 +11047,12 @@
         <v>0</v>
       </c>
       <c r="U164" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B165" s="9">
         <v>46162.682309502314</v>
@@ -11044,16 +11062,16 @@
         <v>46162.76513244213</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I165" s="10"/>
       <c r="J165" s="9">
@@ -11069,13 +11087,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11085,7 +11103,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B166" s="5">
         <v>46162.68231375</v>
@@ -11095,16 +11113,16 @@
         <v>46162.765129583335</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11120,13 +11138,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11136,7 +11154,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B167" s="9">
         <v>46162.682318101855</v>
@@ -11146,16 +11164,16 @@
         <v>46162.76512658565</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I167" s="10"/>
       <c r="J167" s="9">
@@ -11171,13 +11189,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11187,7 +11205,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B168" s="5">
         <v>46162.682322430555</v>
@@ -11197,16 +11215,16 @@
         <v>46162.76512369213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11222,13 +11240,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11238,7 +11256,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B169" s="9">
         <v>46162.682326759255</v>
@@ -11248,16 +11266,16 @@
         <v>46162.765120752316</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I169" s="10"/>
       <c r="J169" s="9">
@@ -11273,13 +11291,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11289,7 +11307,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B170" s="5">
         <v>46162.68236239583</v>
@@ -11299,16 +11317,16 @@
         <v>46162.76511746528</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11324,10 +11342,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11340,7 +11358,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B171" s="9">
         <v>46162.682365960645</v>
@@ -11350,16 +11368,16 @@
         <v>46162.765109942135</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I171" s="10"/>
       <c r="J171" s="9">
@@ -11375,13 +11393,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11391,7 +11409,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B172" s="5">
         <v>46162.68236944445</v>
@@ -11401,16 +11419,16 @@
         <v>46162.76510700231</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11426,13 +11444,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11442,7 +11460,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B173" s="9">
         <v>46162.68237259259</v>
@@ -11452,16 +11470,16 @@
         <v>46162.76510052083</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I173" s="10"/>
       <c r="J173" s="9">
@@ -11477,13 +11495,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11493,7 +11511,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B174" s="5">
         <v>46162.682375902776</v>
@@ -11503,16 +11521,16 @@
         <v>46162.76510002315</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
@@ -11528,13 +11546,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11544,7 +11562,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B175" s="9">
         <v>46162.682386099536</v>
@@ -11554,7 +11572,7 @@
         <v>46162.711784837964</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>25</v>
@@ -11578,7 +11596,7 @@
         <v>26</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11591,7 +11609,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B176" s="5">
         <v>46162.68238924768</v>
@@ -11601,16 +11619,16 @@
         <v>46162.76537538195</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I176" s="5">
         <v>46227</v>
@@ -11628,13 +11646,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q176" s="5">
         <v>46227</v>
@@ -11649,12 +11667,12 @@
         <v>0</v>
       </c>
       <c r="U176" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B177" s="9">
         <v>46162.682394664356</v>
@@ -11664,16 +11682,16 @@
         <v>46162.76536123843</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I177" s="9">
         <v>46227</v>
@@ -11691,13 +11709,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11707,7 +11725,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B178" s="5">
         <v>46162.68239902778</v>
@@ -11717,16 +11735,16 @@
         <v>46162.76535802083</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I178" s="5">
         <v>46227</v>
@@ -11744,13 +11762,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11760,7 +11778,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B179" s="9">
         <v>46162.682403321756</v>
@@ -11770,16 +11788,16 @@
         <v>46162.76535458333</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I179" s="9">
         <v>46227</v>
@@ -11797,13 +11815,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11813,7 +11831,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B180" s="5">
         <v>46162.68240755787</v>
@@ -11823,16 +11841,16 @@
         <v>46162.76535162037</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I180" s="5">
         <v>46227</v>
@@ -11850,13 +11868,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11866,7 +11884,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B181" s="9">
         <v>46162.68241208333</v>
@@ -11876,16 +11894,16 @@
         <v>46162.765348796296</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I181" s="9">
         <v>46227</v>
@@ -11903,13 +11921,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11919,7 +11937,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B182" s="5">
         <v>46162.682416400465</v>
@@ -11929,16 +11947,16 @@
         <v>46162.765344976855</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I182" s="5">
         <v>46227</v>
@@ -11956,13 +11974,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11972,7 +11990,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B183" s="9">
         <v>46162.68241952546</v>
@@ -11982,16 +12000,16 @@
         <v>46162.765340763886</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I183" s="9">
         <v>46227</v>
@@ -12009,10 +12027,10 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P183" s="10" t="s">
         <v>26</v>
@@ -12025,7 +12043,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B184" s="5">
         <v>46162.6824222338</v>
@@ -12035,16 +12053,16 @@
         <v>46162.765337488425</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I184" s="5">
         <v>46227</v>
@@ -12062,13 +12080,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12078,7 +12096,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B185" s="9">
         <v>46162.68242513889</v>
@@ -12088,16 +12106,16 @@
         <v>46162.76533056713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I185" s="9">
         <v>46227</v>
@@ -12115,13 +12133,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12131,7 +12149,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B186" s="5">
         <v>46162.682428125</v>
@@ -12141,16 +12159,16 @@
         <v>46162.76532990741</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I186" s="5">
         <v>46227</v>
@@ -12168,13 +12186,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12184,7 +12202,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B187" s="9">
         <v>46162.68243688658</v>
@@ -12194,16 +12212,16 @@
         <v>46162.76634032407</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I187" s="9">
         <v>46230</v>
@@ -12221,13 +12239,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q187" s="9">
         <v>46230</v>
@@ -12242,12 +12260,12 @@
         <v>0</v>
       </c>
       <c r="U187" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B188" s="5">
         <v>46162.68244069444</v>
@@ -12257,16 +12275,16 @@
         <v>46162.766318043985</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I188" s="5">
         <v>46230</v>
@@ -12284,13 +12302,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12300,7 +12318,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B189" s="9">
         <v>46162.68244457176</v>
@@ -12310,16 +12328,16 @@
         <v>46162.76631474537</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I189" s="9">
         <v>46230</v>
@@ -12337,13 +12355,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12353,7 +12371,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B190" s="5">
         <v>46162.68244844908</v>
@@ -12363,16 +12381,16 @@
         <v>46162.76631193287</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I190" s="5">
         <v>46230</v>
@@ -12390,13 +12408,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12406,7 +12424,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B191" s="9">
         <v>46162.68245221065</v>
@@ -12416,16 +12434,16 @@
         <v>46162.76630898148</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I191" s="9">
         <v>46230</v>
@@ -12443,13 +12461,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12459,7 +12477,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B192" s="5">
         <v>46162.68245652778</v>
@@ -12469,16 +12487,16 @@
         <v>46162.76630527778</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I192" s="5">
         <v>46230</v>
@@ -12496,13 +12514,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12512,7 +12530,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B193" s="9">
         <v>46162.68246049769</v>
@@ -12522,16 +12540,16 @@
         <v>46162.76630212963</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I193" s="9">
         <v>46230</v>
@@ -12549,10 +12567,10 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P193" s="10" t="s">
         <v>26</v>
@@ -12565,7 +12583,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B194" s="5">
         <v>46162.68246318287</v>
@@ -12575,16 +12593,16 @@
         <v>46162.76629917824</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I194" s="5">
         <v>46230</v>
@@ -12602,13 +12620,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12618,7 +12636,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B195" s="9">
         <v>46162.68246601852</v>
@@ -12628,16 +12646,16 @@
         <v>46162.76629561343</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I195" s="9">
         <v>46230</v>
@@ -12655,13 +12673,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12671,7 +12689,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="5">
         <v>46162.68246881945</v>
@@ -12681,16 +12699,16 @@
         <v>46162.766289004634</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I196" s="5">
         <v>46230</v>
@@ -12708,13 +12726,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12724,7 +12742,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B197" s="9">
         <v>46162.68247158565</v>
@@ -12734,16 +12752,16 @@
         <v>46162.76628835648</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I197" s="9">
         <v>46230</v>
@@ -12761,13 +12779,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12777,7 +12795,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B198" s="5">
         <v>46162.68248012732</v>
@@ -12787,16 +12805,16 @@
         <v>46162.76653042824</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I198" s="5">
         <v>46231</v>
@@ -12814,13 +12832,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q198" s="5">
         <v>46231</v>
@@ -12835,12 +12853,12 @@
         <v>0</v>
       </c>
       <c r="U198" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B199" s="9">
         <v>46162.682524502314</v>
@@ -12850,16 +12868,16 @@
         <v>46162.766515462965</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I199" s="9">
         <v>46231</v>
@@ -12877,13 +12895,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12893,7 +12911,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B200" s="5">
         <v>46162.682533032406</v>
@@ -12903,16 +12921,16 @@
         <v>46162.76651282408</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I200" s="5">
         <v>46231</v>
@@ -12930,13 +12948,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12946,7 +12964,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B201" s="9">
         <v>46162.68253883102</v>
@@ -12956,16 +12974,16 @@
         <v>46162.76651023148</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I201" s="9">
         <v>46231</v>
@@ -12983,13 +13001,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -12999,7 +13017,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B202" s="5">
         <v>46162.68254368055</v>
@@ -13009,16 +13027,16 @@
         <v>46162.76650773148</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I202" s="5">
         <v>46231</v>
@@ -13036,13 +13054,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13052,7 +13070,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B203" s="9">
         <v>46162.68255409722</v>
@@ -13062,16 +13080,16 @@
         <v>46162.76650408565</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I203" s="9">
         <v>46231</v>
@@ -13089,13 +13107,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13105,7 +13123,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B204" s="5">
         <v>46162.6825590625</v>
@@ -13115,16 +13133,16 @@
         <v>46162.76650106482</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I204" s="5">
         <v>46231</v>
@@ -13142,13 +13160,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13158,7 +13176,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B205" s="9">
         <v>46162.68256261574</v>
@@ -13168,16 +13186,16 @@
         <v>46162.76649841435</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I205" s="9">
         <v>46231</v>
@@ -13195,13 +13213,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13211,7 +13229,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B206" s="5">
         <v>46162.682566006944</v>
@@ -13221,16 +13239,16 @@
         <v>46162.76649456019</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I206" s="5">
         <v>46231</v>
@@ -13248,13 +13266,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13264,7 +13282,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B207" s="9">
         <v>46162.682569386576</v>
@@ -13274,16 +13292,16 @@
         <v>46162.766489050926</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I207" s="9">
         <v>46231</v>
@@ -13301,13 +13319,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13317,7 +13335,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B208" s="5">
         <v>46162.68257278935</v>
@@ -13327,16 +13345,16 @@
         <v>46162.76648839121</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I208" s="5">
         <v>46231</v>
@@ -13354,13 +13372,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13370,7 +13388,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B209" s="9">
         <v>46162.68258331019</v>
@@ -13380,16 +13398,16 @@
         <v>46162.76671087963</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I209" s="9">
         <v>46232</v>
@@ -13407,13 +13425,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q209" s="9">
         <v>46232</v>
@@ -13428,12 +13446,12 @@
         <v>0</v>
       </c>
       <c r="U209" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B210" s="5">
         <v>46162.6825891551</v>
@@ -13443,16 +13461,16 @@
         <v>46162.76670017361</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I210" s="5">
         <v>46232</v>
@@ -13470,13 +13488,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13486,7 +13504,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B211" s="9">
         <v>46162.68259327546</v>
@@ -13496,16 +13514,16 @@
         <v>46162.76669680556</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I211" s="9">
         <v>46232</v>
@@ -13523,13 +13541,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13539,7 +13557,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B212" s="5">
         <v>46162.682597499996</v>
@@ -13549,16 +13567,16 @@
         <v>46162.76669409723</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I212" s="5">
         <v>46232</v>
@@ -13576,13 +13594,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13592,7 +13610,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B213" s="9">
         <v>46162.68260168981</v>
@@ -13602,16 +13620,16 @@
         <v>46162.766691377314</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I213" s="9">
         <v>46232</v>
@@ -13629,13 +13647,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13645,7 +13663,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B214" s="5">
         <v>46162.68260615741</v>
@@ -13655,16 +13673,16 @@
         <v>46162.766687662035</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I214" s="5">
         <v>46232</v>
@@ -13682,13 +13700,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13698,7 +13716,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B215" s="9">
         <v>46162.68261056713</v>
@@ -13708,16 +13726,16 @@
         <v>46162.76668472222</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I215" s="9">
         <v>46232</v>
@@ -13735,10 +13753,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13751,7 +13769,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B216" s="5">
         <v>46162.682613564815</v>
@@ -13761,16 +13779,16 @@
         <v>46162.76668173611</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I216" s="5">
         <v>46232</v>
@@ -13788,10 +13806,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13804,7 +13822,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B217" s="9">
         <v>46162.682616666665</v>
@@ -13814,16 +13832,16 @@
         <v>46162.76667282407</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I217" s="9">
         <v>46232</v>
@@ -13841,10 +13859,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13857,7 +13875,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B218" s="5">
         <v>46162.682619583335</v>
@@ -13867,16 +13885,16 @@
         <v>46162.76667212963</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I218" s="5">
         <v>46232</v>
@@ -13894,10 +13912,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13910,7 +13928,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B219" s="9">
         <v>46162.68262266203</v>
@@ -13920,16 +13938,16 @@
         <v>46162.76667141204</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I219" s="9">
         <v>46232</v>
@@ -13947,10 +13965,10 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13963,7 +13981,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B220" s="5">
         <v>46162.682665625005</v>
@@ -13973,7 +13991,7 @@
         <v>46162.76005167824</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>25</v>
@@ -13997,7 +14015,7 @@
         <v>26</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>26</v>
@@ -14010,7 +14028,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B221" s="9">
         <v>46162.68266950232</v>
@@ -14020,16 +14038,16 @@
         <v>46162.76676789352</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I221" s="9">
         <v>46233</v>
@@ -14047,13 +14065,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q221" s="9">
         <v>46233</v>
@@ -14068,12 +14086,12 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B222" s="5">
         <v>46162.68267490741</v>
@@ -14083,7 +14101,7 @@
         <v>46162.76682827546</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14110,13 +14128,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q222" s="5">
         <v>46233</v>
@@ -14131,7 +14149,7 @@
         <v>0</v>
       </c>
       <c r="U222" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -218,9 +218,9 @@
     Planos para:
         Ventilador ZVN 2-9-103/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 90/100 + VENT + FAR 90/100 + TIPO A
         Alcance Chile: TOBERA + REJILLA + VENT
-        Alcance Colombia: FAR + DIFUSOR
+        Alcance Colombia: FAR + TIPO A
     Rodete:
-        Ventilador ZVN 1-12-55/4 --- ALABES: 300004
+        Ventilador ZVN 2-9-103/2 --- ALABES: 300000
     Tratamiento superficial:
         Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
     Datos eléctricos para el motor:
@@ -232,79 +232,79 @@
     <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
   </si>
   <si>
+    <t>1214977316716053</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214977316716053</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>1214969047720956</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT4327,propuesta motor OT4327,propuesta alabes OT4327,propuesta nucleo rodete OT4327</t>
+  </si>
+  <si>
+    <t>1214977316726320</t>
+  </si>
+  <si>
+    <t>propuesta motor OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT4327,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214977316726340</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT4327,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214977533910216</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT4327</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT4327</t>
+  </si>
+  <si>
+    <t>1214977075717388</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT4327</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT4327</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969047720956</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT4327,propuesta motor OT4327,propuesta alabes OT4327,propuesta nucleo rodete OT4327</t>
-  </si>
-  <si>
-    <t>1214977316726320</t>
-  </si>
-  <si>
-    <t>propuesta motor OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT4327,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214977316726340</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT4327,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214977533910216</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT4327</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT4327</t>
-  </si>
-  <si>
-    <t>1214977075717388</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT4327</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT4327</t>
   </si>
   <si>
     <t>1214977075717403</t>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46197.669773472226</v>
+        <v>46197.67116355324</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2643,9 +2643,11 @@
       <c r="B13" s="9">
         <v>46162.68130347222</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46197.671156689816</v>
+      </c>
       <c r="D13" s="9">
-        <v>46197.670623125</v>
+        <v>46197.671174166666</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2693,25 +2695,25 @@
         <v>54</v>
       </c>
       <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>63</v>
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46162.6813085301</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.669773981484</v>
+        <v>46197.67117741898</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2741,10 +2743,10 @@
         <v>46</v>
       </c>
       <c r="O14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="Q14" s="5">
         <v>46149</v>
@@ -2758,13 +2760,13 @@
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="11" t="s">
-        <v>68</v>
+      <c r="U14" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46162.68117188658</v>
@@ -2774,7 +2776,7 @@
         <v>46197.587885057874</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>25</v>
@@ -2798,7 +2800,7 @@
         <v>26</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>26</v>
@@ -2811,7 +2813,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46162.681316030095</v>
@@ -2821,7 +2823,7 @@
         <v>46197.66702332176</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2848,13 +2850,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46153</v>
@@ -2869,12 +2871,12 @@
         <v>0</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46162.68132108796</v>
@@ -2884,7 +2886,7 @@
         <v>46197.66978644676</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2911,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="9">
         <v>46153</v>
@@ -2932,12 +2934,12 @@
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46162.68132700231</v>
@@ -2949,16 +2951,16 @@
         <v>46197.66978645833</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I18" s="5">
         <v>46153</v>
@@ -2976,13 +2978,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46153</v>
@@ -2997,12 +2999,12 @@
         <v>1</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46162.68133263889</v>
@@ -3012,16 +3014,16 @@
         <v>46190.17346704861</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="H19" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I19" s="9">
         <v>46188</v>
@@ -3039,13 +3041,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="Q19" s="9">
         <v>46188</v>
@@ -3060,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3081,10 +3083,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I20" s="5">
         <v>46184</v>
@@ -3102,10 +3104,10 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>90</v>
@@ -3123,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3144,10 +3146,10 @@
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="I21" s="9">
         <v>46188</v>
@@ -3165,10 +3167,10 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>93</v>
@@ -3186,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3207,10 +3209,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46188</v>
@@ -3228,10 +3230,10 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>96</v>
@@ -3249,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3359,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3404,7 +3406,7 @@
         <v>101</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>107</v>
@@ -3418,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3477,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3540,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3585,7 +3587,7 @@
         <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>116</v>
@@ -3599,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3658,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3721,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3766,7 +3768,7 @@
         <v>121</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>125</v>
@@ -3780,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3839,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3898,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3961,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4006,7 +4008,7 @@
         <v>133</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>140</v>
@@ -4020,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4075,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4138,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -4307,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4529,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4694,7 +4696,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46168.16746090278</v>
+        <v>46197.671176655094</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4744,8 +4746,8 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="11" t="s">
-        <v>68</v>
+      <c r="U48" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4808,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4823,7 +4825,7 @@
         <v>46186.16887460648</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4871,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4932,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -5550,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5611,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5672,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5733,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5794,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5855,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5965,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6558,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -7151,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="U92" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7789,7 +7791,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7850,7 +7852,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7911,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7972,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="U107" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8040,10 +8042,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I109" s="9">
         <v>46218</v>
@@ -8082,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8103,10 +8105,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I110" s="5">
         <v>46218</v>
@@ -8156,10 +8158,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I111" s="9">
         <v>46218</v>
@@ -8209,10 +8211,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I112" s="5">
         <v>46218</v>
@@ -8262,10 +8264,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I113" s="9">
         <v>46218</v>
@@ -8315,10 +8317,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I114" s="5">
         <v>46218</v>
@@ -8368,10 +8370,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I115" s="9">
         <v>46218</v>
@@ -8421,10 +8423,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I116" s="5">
         <v>46218</v>
@@ -8474,10 +8476,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I117" s="9">
         <v>46218</v>
@@ -8527,10 +8529,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I118" s="5">
         <v>46218</v>
@@ -8580,10 +8582,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I119" s="9">
         <v>46218</v>
@@ -8633,10 +8635,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I120" s="5">
         <v>46219</v>
@@ -8675,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8696,10 +8698,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I121" s="9">
         <v>46219</v>
@@ -8749,10 +8751,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I122" s="5">
         <v>46219</v>
@@ -8802,10 +8804,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I123" s="9">
         <v>46219</v>
@@ -8855,10 +8857,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I124" s="5">
         <v>46219</v>
@@ -8908,10 +8910,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I125" s="9">
         <v>46219</v>
@@ -8961,10 +8963,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I126" s="5">
         <v>46219</v>
@@ -9014,10 +9016,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I127" s="9">
         <v>46219</v>
@@ -9067,10 +9069,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I128" s="5">
         <v>46219</v>
@@ -9120,10 +9122,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I129" s="9">
         <v>46219</v>
@@ -9173,10 +9175,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I130" s="5">
         <v>46219</v>
@@ -9226,10 +9228,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I131" s="9">
         <v>46220</v>
@@ -9268,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9289,10 +9291,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I132" s="5">
         <v>46220</v>
@@ -9342,10 +9344,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I133" s="9">
         <v>46220</v>
@@ -9395,10 +9397,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I134" s="5">
         <v>46220</v>
@@ -9448,10 +9450,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I135" s="9">
         <v>46220</v>
@@ -9501,10 +9503,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I136" s="5">
         <v>46220</v>
@@ -9554,10 +9556,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I137" s="9">
         <v>46220</v>
@@ -9607,10 +9609,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I138" s="5">
         <v>46220</v>
@@ -9660,10 +9662,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I139" s="9">
         <v>46220</v>
@@ -9713,10 +9715,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I140" s="5">
         <v>46220</v>
@@ -9766,10 +9768,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I141" s="9">
         <v>46220</v>
@@ -9819,10 +9821,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I142" s="5">
         <v>46223</v>
@@ -9861,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="U142" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -9882,10 +9884,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I143" s="9">
         <v>46223</v>
@@ -9935,10 +9937,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I144" s="5">
         <v>46223</v>
@@ -9988,10 +9990,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I145" s="9">
         <v>46223</v>
@@ -10041,10 +10043,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I146" s="5">
         <v>46223</v>
@@ -10094,10 +10096,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I147" s="9">
         <v>46223</v>
@@ -10147,10 +10149,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I148" s="5">
         <v>46223</v>
@@ -10200,10 +10202,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I149" s="9">
         <v>46223</v>
@@ -10253,10 +10255,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I150" s="5">
         <v>46223</v>
@@ -10306,10 +10308,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I151" s="9">
         <v>46223</v>
@@ -10359,10 +10361,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I152" s="5">
         <v>46223</v>
@@ -10412,10 +10414,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I153" s="9">
         <v>46224</v>
@@ -10454,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -10475,10 +10477,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I154" s="5">
         <v>46224</v>
@@ -10528,10 +10530,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I155" s="9">
         <v>46224</v>
@@ -10581,10 +10583,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I156" s="5">
         <v>46224</v>
@@ -10634,10 +10636,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I157" s="9">
         <v>46224</v>
@@ -10687,10 +10689,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I158" s="5">
         <v>46224</v>
@@ -10740,10 +10742,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I159" s="9">
         <v>46224</v>
@@ -10793,10 +10795,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I160" s="5">
         <v>46224</v>
@@ -10846,10 +10848,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I161" s="9">
         <v>46224</v>
@@ -10899,10 +10901,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I162" s="5">
         <v>46224</v>
@@ -10952,10 +10954,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I163" s="9">
         <v>46224</v>
@@ -11005,10 +11007,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I164" s="5">
         <v>46226</v>
@@ -11047,7 +11049,7 @@
         <v>0</v>
       </c>
       <c r="U164" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
@@ -11068,10 +11070,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I165" s="10"/>
       <c r="J165" s="9">
@@ -11119,10 +11121,10 @@
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11170,10 +11172,10 @@
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I167" s="10"/>
       <c r="J167" s="9">
@@ -11221,10 +11223,10 @@
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11272,10 +11274,10 @@
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I169" s="10"/>
       <c r="J169" s="9">
@@ -11323,10 +11325,10 @@
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11374,10 +11376,10 @@
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I171" s="10"/>
       <c r="J171" s="9">
@@ -11425,10 +11427,10 @@
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11476,10 +11478,10 @@
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I173" s="10"/>
       <c r="J173" s="9">
@@ -11527,10 +11529,10 @@
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
@@ -11667,7 +11669,7 @@
         <v>0</v>
       </c>
       <c r="U176" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
@@ -12218,10 +12220,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I187" s="9">
         <v>46230</v>
@@ -12260,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="U187" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
@@ -12281,10 +12283,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I188" s="5">
         <v>46230</v>
@@ -12334,10 +12336,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I189" s="9">
         <v>46230</v>
@@ -12387,10 +12389,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I190" s="5">
         <v>46230</v>
@@ -12440,10 +12442,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I191" s="9">
         <v>46230</v>
@@ -12493,10 +12495,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I192" s="5">
         <v>46230</v>
@@ -12546,10 +12548,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I193" s="9">
         <v>46230</v>
@@ -12599,10 +12601,10 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I194" s="5">
         <v>46230</v>
@@ -12652,10 +12654,10 @@
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I195" s="9">
         <v>46230</v>
@@ -12705,10 +12707,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I196" s="5">
         <v>46230</v>
@@ -12758,10 +12760,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I197" s="9">
         <v>46230</v>
@@ -12853,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="U198" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
@@ -13446,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="U209" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
@@ -14086,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
@@ -14149,7 +14151,7 @@
         <v>0</v>
       </c>
       <c r="U222" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="475">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -580,28 +580,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977521258828</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT4327</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214977521270201</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977521258828</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT4327</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214977521270201</t>
   </si>
   <si>
     <t>Propuesta Corte plasma  OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Propuesta Mecanizado OT4327,Propuesta Fabricación externa  OT4327,propuesta Corte Laser OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
@@ -3853,7 +3859,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46175.17037224537</v>
+        <v>46197.70342619213</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -4649,7 +4655,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46162.70636487268</v>
+        <v>46197.70289550926</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4694,9 +4700,11 @@
       <c r="B48" s="5">
         <v>46162.68150506944</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46197.70288993056</v>
+      </c>
       <c r="D48" s="5">
-        <v>46197.671176655094</v>
+        <v>46197.703074074074</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4744,10 +4752,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4759,7 +4767,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46185.182528391204</v>
+        <v>46197.703094780096</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4831,10 +4839,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46185</v>
@@ -4858,7 +4866,7 @@
         <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46185</v>
@@ -4878,7 +4886,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.68153015046</v>
@@ -4888,16 +4896,16 @@
         <v>46162.76230295139</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4916,7 +4924,7 @@
         <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4939,7 +4947,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46162.68153354166</v>
@@ -4949,16 +4957,16 @@
         <v>46162.76229798611</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4974,13 +4982,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4990,7 +4998,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9">
         <v>46162.68153736111</v>
@@ -5000,16 +5008,16 @@
         <v>46162.76229449074</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5025,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5041,7 +5049,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46162.68154143519</v>
@@ -5051,16 +5059,16 @@
         <v>46162.76229145833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5076,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5092,7 +5100,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46162.68154440972</v>
@@ -5102,16 +5110,16 @@
         <v>46162.76228877315</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5127,13 +5135,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5143,7 +5151,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.68154740741</v>
@@ -5153,16 +5161,16 @@
         <v>46162.76228596065</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5178,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5194,7 +5202,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B57" s="9">
         <v>46162.68155047453</v>
@@ -5204,16 +5212,16 @@
         <v>46162.762282870375</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5229,10 +5237,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5245,7 +5253,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46162.681552766204</v>
@@ -5255,16 +5263,16 @@
         <v>46162.76227917824</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5280,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5296,7 +5304,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B59" s="9">
         <v>46162.68155516204</v>
@@ -5306,16 +5314,16 @@
         <v>46162.76227634259</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5331,13 +5339,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5347,7 +5355,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46162.6815574537</v>
@@ -5357,16 +5365,16 @@
         <v>46162.7622690162</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5382,10 +5390,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5398,7 +5406,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46162.68155952546</v>
@@ -5408,16 +5416,16 @@
         <v>46162.762268391205</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5433,10 +5441,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5449,7 +5457,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46162.681598807874</v>
@@ -5459,7 +5467,7 @@
         <v>46162.707360960645</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5483,7 +5491,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5496,7 +5504,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46162.681602743054</v>
@@ -5506,16 +5514,16 @@
         <v>46196.168763634254</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5531,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46203</v>
@@ -5557,7 +5565,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46162.68160836806</v>
@@ -5567,7 +5575,7 @@
         <v>46197.17514756945</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5592,13 +5600,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46204</v>
@@ -5618,7 +5626,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9">
         <v>46162.681615208334</v>
@@ -5628,16 +5636,16 @@
         <v>46196.16876357639</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="9">
@@ -5653,13 +5661,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9">
         <v>46203</v>
@@ -5679,7 +5687,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46162.68162069445</v>
@@ -5689,7 +5697,7 @@
         <v>46197.175148090275</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5714,13 +5722,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46204</v>
@@ -5740,7 +5748,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46162.681625983794</v>
@@ -5750,16 +5758,16 @@
         <v>46196.16876371528</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5775,13 +5783,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>172</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9">
         <v>46203</v>
@@ -5801,7 +5809,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
         <v>46162.68163075231</v>
@@ -5811,7 +5819,7 @@
         <v>46197.17514795139</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5836,13 +5844,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46204</v>
@@ -5862,7 +5870,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B69" s="9">
         <v>46162.68163611111</v>
@@ -5872,7 +5880,7 @@
         <v>46162.763323391206</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5896,7 +5904,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5909,7 +5917,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46162.6816390162</v>
@@ -5919,16 +5927,16 @@
         <v>46162.763335578704</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I70" s="5">
         <v>46205</v>
@@ -5946,13 +5954,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q70" s="5">
         <v>46205</v>
@@ -5972,7 +5980,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.68164390046</v>
@@ -5982,16 +5990,16 @@
         <v>46162.763318530095</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6009,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6025,7 +6033,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46162.681651203704</v>
@@ -6035,16 +6043,16 @@
         <v>46162.76331560186</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6062,13 +6070,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6078,7 +6086,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46162.68165733796</v>
@@ -6088,16 +6096,16 @@
         <v>46162.76331271991</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6115,13 +6123,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6131,7 +6139,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46162.68166336806</v>
@@ -6141,16 +6149,16 @@
         <v>46162.763309710645</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6168,13 +6176,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6184,7 +6192,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46162.68166935185</v>
@@ -6194,16 +6202,16 @@
         <v>46162.763306759254</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6221,13 +6229,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6237,7 +6245,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.68167571759</v>
@@ -6247,16 +6255,16 @@
         <v>46162.76330359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6274,13 +6282,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6290,7 +6298,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46162.68168109954</v>
@@ -6300,16 +6308,16 @@
         <v>46162.7633006713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6327,13 +6335,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6343,7 +6351,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.68168630787</v>
@@ -6353,16 +6361,16 @@
         <v>46162.763297384256</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6380,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6396,7 +6404,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46162.68169194444</v>
@@ -6406,16 +6414,16 @@
         <v>46162.763290891206</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6433,13 +6441,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6449,7 +6457,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46162.681698229164</v>
@@ -6459,16 +6467,16 @@
         <v>46162.763290243056</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I80" s="5">
         <v>46205</v>
@@ -6486,13 +6494,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6502,7 +6510,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
         <v>46162.68171431713</v>
@@ -6512,16 +6520,16 @@
         <v>46162.76361657407</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I81" s="9">
         <v>46210</v>
@@ -6539,13 +6547,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q81" s="9">
         <v>46210</v>
@@ -6565,7 +6573,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46162.681718935186</v>
@@ -6575,16 +6583,16 @@
         <v>46162.763601388884</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I82" s="5">
         <v>46210</v>
@@ -6602,13 +6610,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6618,7 +6626,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B83" s="9">
         <v>46162.68172515046</v>
@@ -6628,16 +6636,16 @@
         <v>46162.76359828704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I83" s="9">
         <v>46210</v>
@@ -6655,13 +6663,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6671,7 +6679,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B84" s="5">
         <v>46162.68173074074</v>
@@ -6681,16 +6689,16 @@
         <v>46162.763595428245</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6708,13 +6716,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6724,7 +6732,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B85" s="9">
         <v>46162.68173619213</v>
@@ -6734,16 +6742,16 @@
         <v>46162.76359266204</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6761,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6777,7 +6785,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46162.681741747685</v>
@@ -6787,16 +6795,16 @@
         <v>46162.763589780094</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6814,13 +6822,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6830,7 +6838,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B87" s="9">
         <v>46162.68178277778</v>
@@ -6840,16 +6848,16 @@
         <v>46162.763586388886</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -6867,13 +6875,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6883,7 +6891,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B88" s="5">
         <v>46162.68178671296</v>
@@ -6893,16 +6901,16 @@
         <v>46162.763583657405</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -6920,10 +6928,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6936,7 +6944,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B89" s="9">
         <v>46162.68178976852</v>
@@ -6946,16 +6954,16 @@
         <v>46162.763580983796</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -6973,13 +6981,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6989,7 +6997,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B90" s="5">
         <v>46162.68179300926</v>
@@ -6999,16 +7007,16 @@
         <v>46162.76357417824</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7026,13 +7034,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7042,7 +7050,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B91" s="9">
         <v>46162.68179625</v>
@@ -7052,16 +7060,16 @@
         <v>46162.763573530094</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I91" s="9">
         <v>46210</v>
@@ -7079,13 +7087,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7095,7 +7103,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B92" s="5">
         <v>46162.681806875</v>
@@ -7105,7 +7113,7 @@
         <v>46162.763839050924</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7132,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q92" s="5">
         <v>46217</v>
@@ -7158,7 +7166,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B93" s="9">
         <v>46162.68181175926</v>
@@ -7168,7 +7176,7 @@
         <v>46162.76379824074</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7195,13 +7203,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7211,7 +7219,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B94" s="5">
         <v>46162.68181751158</v>
@@ -7221,7 +7229,7 @@
         <v>46162.76379479167</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7248,13 +7256,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7264,7 +7272,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B95" s="9">
         <v>46162.681823032406</v>
@@ -7274,7 +7282,7 @@
         <v>46162.763791562495</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7301,13 +7309,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7317,7 +7325,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B96" s="5">
         <v>46162.681828368055</v>
@@ -7327,7 +7335,7 @@
         <v>46162.76378862269</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7354,13 +7362,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7370,7 +7378,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B97" s="9">
         <v>46162.68183400463</v>
@@ -7380,7 +7388,7 @@
         <v>46162.763785347226</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7407,13 +7415,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7423,7 +7431,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5">
         <v>46162.6818390625</v>
@@ -7433,7 +7441,7 @@
         <v>46162.763782152775</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7460,13 +7468,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7476,7 +7484,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B99" s="9">
         <v>46162.68184208333</v>
@@ -7486,7 +7494,7 @@
         <v>46162.76377949074</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7513,13 +7521,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7529,7 +7537,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B100" s="5">
         <v>46162.6818458912</v>
@@ -7539,7 +7547,7 @@
         <v>46162.76377262731</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7566,13 +7574,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7582,7 +7590,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B101" s="9">
         <v>46162.681849375</v>
@@ -7592,7 +7600,7 @@
         <v>46162.76377197917</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7619,13 +7627,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7635,7 +7643,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B102" s="5">
         <v>46162.68185259259</v>
@@ -7645,7 +7653,7 @@
         <v>46162.7637712963</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7672,13 +7680,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7688,7 +7696,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B103" s="9">
         <v>46162.681862557874</v>
@@ -7698,7 +7706,7 @@
         <v>46162.708598171295</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7722,7 +7730,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7735,7 +7743,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B104" s="5">
         <v>46162.68186600694</v>
@@ -7745,16 +7753,16 @@
         <v>46162.76398071759</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7770,13 +7778,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q104" s="5">
         <v>46161</v>
@@ -7796,7 +7804,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B105" s="9">
         <v>46162.681872870366</v>
@@ -7806,16 +7814,16 @@
         <v>46162.763977916664</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7831,13 +7839,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>109</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q105" s="9">
         <v>46161</v>
@@ -7857,7 +7865,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46162.681879930555</v>
@@ -7867,16 +7875,16 @@
         <v>46197.17676240741</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7892,13 +7900,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q106" s="5">
         <v>46196</v>
@@ -7918,7 +7926,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B107" s="9">
         <v>46162.681886412036</v>
@@ -7928,16 +7936,16 @@
         <v>46162.763970266205</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7953,13 +7961,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>160</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q107" s="9">
         <v>46232</v>
@@ -7979,7 +7987,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B108" s="5">
         <v>46162.68189086806</v>
@@ -7989,7 +7997,7 @@
         <v>46162.710864479166</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>25</v>
@@ -8013,7 +8021,7 @@
         <v>26</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8026,7 +8034,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B109" s="9">
         <v>46162.681893761575</v>
@@ -8036,7 +8044,7 @@
         <v>46162.76425648148</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8063,13 +8071,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q109" s="9">
         <v>46218</v>
@@ -8089,7 +8097,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B110" s="5">
         <v>46162.68190694445</v>
@@ -8099,7 +8107,7 @@
         <v>46162.764253263886</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8126,10 +8134,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8142,7 +8150,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B111" s="9">
         <v>46162.68191104167</v>
@@ -8152,7 +8160,7 @@
         <v>46162.76425003472</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8179,10 +8187,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8195,7 +8203,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B112" s="5">
         <v>46162.68191516204</v>
@@ -8205,7 +8213,7 @@
         <v>46162.764246273146</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8232,13 +8240,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8248,7 +8256,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B113" s="9">
         <v>46162.68191947917</v>
@@ -8258,7 +8266,7 @@
         <v>46162.76424304398</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8285,13 +8293,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8301,7 +8309,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B114" s="5">
         <v>46162.68192371528</v>
@@ -8311,7 +8319,7 @@
         <v>46162.764240081015</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8338,13 +8346,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8354,7 +8362,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B115" s="9">
         <v>46162.68192716435</v>
@@ -8364,7 +8372,7 @@
         <v>46162.76423697917</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8391,13 +8399,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8407,7 +8415,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46162.6819303588</v>
@@ -8417,7 +8425,7 @@
         <v>46162.76423423611</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8444,13 +8452,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8460,7 +8468,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46162.6819334375</v>
@@ -8470,7 +8478,7 @@
         <v>46162.76423152778</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8497,13 +8505,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8513,7 +8521,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46162.68193662037</v>
@@ -8523,7 +8531,7 @@
         <v>46162.764224479164</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8550,13 +8558,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8566,7 +8574,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46162.68193976852</v>
@@ -8576,7 +8584,7 @@
         <v>46162.76422390046</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8603,13 +8611,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8619,7 +8627,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B120" s="5">
         <v>46162.68199361111</v>
@@ -8629,7 +8637,7 @@
         <v>46162.76445266204</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8656,13 +8664,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q120" s="5">
         <v>46219</v>
@@ -8682,7 +8690,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B121" s="9">
         <v>46162.68199872685</v>
@@ -8692,7 +8700,7 @@
         <v>46162.764425138885</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8719,13 +8727,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8735,7 +8743,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B122" s="5">
         <v>46162.6820043287</v>
@@ -8745,7 +8753,7 @@
         <v>46162.7644221875</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8772,13 +8780,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O122" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>320</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>318</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8788,7 +8796,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B123" s="9">
         <v>46162.68200945602</v>
@@ -8798,7 +8806,7 @@
         <v>46162.76441872685</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8825,13 +8833,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8841,7 +8849,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B124" s="5">
         <v>46162.68201590278</v>
@@ -8851,7 +8859,7 @@
         <v>46162.76441527778</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8878,13 +8886,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8894,7 +8902,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B125" s="9">
         <v>46162.682022175926</v>
@@ -8904,7 +8912,7 @@
         <v>46162.76441243055</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8931,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8947,7 +8955,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B126" s="5">
         <v>46162.68202664352</v>
@@ -8957,7 +8965,7 @@
         <v>46162.76440929398</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8984,13 +8992,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9000,7 +9008,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B127" s="9">
         <v>46162.682031874996</v>
@@ -9010,7 +9018,7 @@
         <v>46162.76440640046</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9037,13 +9045,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9053,7 +9061,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B128" s="5">
         <v>46162.682037129634</v>
@@ -9063,7 +9071,7 @@
         <v>46162.764403761576</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9090,13 +9098,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9106,7 +9114,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B129" s="9">
         <v>46162.68204233796</v>
@@ -9116,7 +9124,7 @@
         <v>46162.764396388884</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9143,13 +9151,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9159,7 +9167,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B130" s="5">
         <v>46162.68204753472</v>
@@ -9169,7 +9177,7 @@
         <v>46162.76439568287</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9196,13 +9204,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9212,7 +9220,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B131" s="9">
         <v>46162.68206118056</v>
@@ -9222,7 +9230,7 @@
         <v>46162.76461746528</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9249,13 +9257,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q131" s="9">
         <v>46220</v>
@@ -9275,7 +9283,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B132" s="5">
         <v>46162.68206542824</v>
@@ -9285,7 +9293,7 @@
         <v>46162.76461333333</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9312,13 +9320,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9328,7 +9336,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B133" s="9">
         <v>46162.68207142361</v>
@@ -9338,7 +9346,7 @@
         <v>46162.764610439815</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9365,13 +9373,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9381,7 +9389,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B134" s="5">
         <v>46162.682082997686</v>
@@ -9391,7 +9399,7 @@
         <v>46162.76460753472</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9418,13 +9426,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9434,7 +9442,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B135" s="9">
         <v>46162.682089317124</v>
@@ -9444,7 +9452,7 @@
         <v>46162.76460444444</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9471,13 +9479,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9487,7 +9495,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B136" s="5">
         <v>46162.68209565972</v>
@@ -9497,7 +9505,7 @@
         <v>46162.764601250004</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9524,13 +9532,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9540,7 +9548,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B137" s="9">
         <v>46162.68209994213</v>
@@ -9550,7 +9558,7 @@
         <v>46162.76459766204</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9577,13 +9585,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9593,7 +9601,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B138" s="5">
         <v>46162.682104189815</v>
@@ -9603,7 +9611,7 @@
         <v>46162.76459489584</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9630,13 +9638,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9646,7 +9654,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B139" s="9">
         <v>46162.68210733796</v>
@@ -9656,7 +9664,7 @@
         <v>46162.76458689815</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9683,13 +9691,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9699,7 +9707,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B140" s="5">
         <v>46162.68211155092</v>
@@ -9709,7 +9717,7 @@
         <v>46162.76458621528</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9736,13 +9744,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9752,7 +9760,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B141" s="9">
         <v>46162.68211587963</v>
@@ -9762,7 +9770,7 @@
         <v>46162.76458552083</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9789,13 +9797,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9805,7 +9813,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B142" s="5">
         <v>46162.68212817129</v>
@@ -9815,7 +9823,7 @@
         <v>46162.76477166667</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9842,13 +9850,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q142" s="5">
         <v>46223</v>
@@ -9868,7 +9876,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B143" s="9">
         <v>46162.68213233796</v>
@@ -9878,7 +9886,7 @@
         <v>46162.76477363426</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9905,13 +9913,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9921,7 +9929,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B144" s="5">
         <v>46162.682137881944</v>
@@ -9931,7 +9939,7 @@
         <v>46162.76477071759</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9958,13 +9966,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9974,7 +9982,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B145" s="9">
         <v>46162.682143275466</v>
@@ -9984,7 +9992,7 @@
         <v>46162.764767141205</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10011,13 +10019,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10027,7 +10035,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B146" s="5">
         <v>46162.68214959491</v>
@@ -10037,7 +10045,7 @@
         <v>46162.764764039355</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10064,13 +10072,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10080,7 +10088,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B147" s="9">
         <v>46162.6821980324</v>
@@ -10090,7 +10098,7 @@
         <v>46162.76476091435</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10117,13 +10125,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10133,7 +10141,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B148" s="5">
         <v>46162.68220454861</v>
@@ -10143,7 +10151,7 @@
         <v>46162.76475773148</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10170,13 +10178,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10186,7 +10194,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B149" s="9">
         <v>46162.6822112963</v>
@@ -10196,7 +10204,7 @@
         <v>46162.76475452546</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10223,13 +10231,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10239,7 +10247,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B150" s="5">
         <v>46162.68221605324</v>
@@ -10249,7 +10257,7 @@
         <v>46162.764749594906</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10276,13 +10284,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10292,7 +10300,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B151" s="9">
         <v>46162.68222200232</v>
@@ -10302,7 +10310,7 @@
         <v>46162.76474296296</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10329,13 +10337,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10345,7 +10353,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B152" s="5">
         <v>46162.68222814814</v>
@@ -10355,7 +10363,7 @@
         <v>46162.764742141204</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10382,13 +10390,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10398,7 +10406,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B153" s="9">
         <v>46162.68224497685</v>
@@ -10408,7 +10416,7 @@
         <v>46162.76494858797</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10435,13 +10443,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q153" s="9">
         <v>46224</v>
@@ -10461,7 +10469,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B154" s="5">
         <v>46162.68224997685</v>
@@ -10471,7 +10479,7 @@
         <v>46162.764935011575</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10498,13 +10506,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10514,7 +10522,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B155" s="9">
         <v>46162.682255844906</v>
@@ -10524,7 +10532,7 @@
         <v>46162.76493179398</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10551,13 +10559,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10567,7 +10575,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B156" s="5">
         <v>46162.682261354166</v>
@@ -10577,7 +10585,7 @@
         <v>46162.76492869213</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10604,13 +10612,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10620,7 +10628,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B157" s="9">
         <v>46162.68226693287</v>
@@ -10630,7 +10638,7 @@
         <v>46162.764925613425</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10657,13 +10665,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10673,7 +10681,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B158" s="5">
         <v>46162.68227229167</v>
@@ -10683,7 +10691,7 @@
         <v>46162.76492271991</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10710,13 +10718,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10726,7 +10734,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B159" s="9">
         <v>46162.68227762732</v>
@@ -10736,7 +10744,7 @@
         <v>46162.764919444446</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10763,10 +10771,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>26</v>
@@ -10779,7 +10787,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B160" s="5">
         <v>46162.68228032408</v>
@@ -10789,7 +10797,7 @@
         <v>46162.76491637732</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10816,13 +10824,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10832,7 +10840,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B161" s="9">
         <v>46162.68228446759</v>
@@ -10842,7 +10850,7 @@
         <v>46162.76491366898</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10869,10 +10877,10 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10885,7 +10893,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B162" s="5">
         <v>46162.68228719907</v>
@@ -10895,7 +10903,7 @@
         <v>46162.764907199075</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10922,10 +10930,10 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>26</v>
@@ -10938,7 +10946,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B163" s="9">
         <v>46162.68229016203</v>
@@ -10948,7 +10956,7 @@
         <v>46162.76490642361</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -10975,10 +10983,10 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P163" s="10" t="s">
         <v>26</v>
@@ -10991,7 +10999,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B164" s="5">
         <v>46162.68230002315</v>
@@ -11001,7 +11009,7 @@
         <v>46162.7651559838</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11028,13 +11036,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q164" s="5">
         <v>46226</v>
@@ -11054,7 +11062,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B165" s="9">
         <v>46162.682309502314</v>
@@ -11064,7 +11072,7 @@
         <v>46162.76513244213</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11089,13 +11097,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11105,7 +11113,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B166" s="5">
         <v>46162.68231375</v>
@@ -11115,7 +11123,7 @@
         <v>46162.765129583335</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11140,13 +11148,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11156,7 +11164,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B167" s="9">
         <v>46162.682318101855</v>
@@ -11166,7 +11174,7 @@
         <v>46162.76512658565</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11191,13 +11199,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11207,7 +11215,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B168" s="5">
         <v>46162.682322430555</v>
@@ -11217,7 +11225,7 @@
         <v>46162.76512369213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11242,13 +11250,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11258,7 +11266,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B169" s="9">
         <v>46162.682326759255</v>
@@ -11268,7 +11276,7 @@
         <v>46162.765120752316</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11293,13 +11301,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11309,7 +11317,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B170" s="5">
         <v>46162.68236239583</v>
@@ -11319,7 +11327,7 @@
         <v>46162.76511746528</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11344,10 +11352,10 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>26</v>
@@ -11360,7 +11368,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B171" s="9">
         <v>46162.682365960645</v>
@@ -11370,7 +11378,7 @@
         <v>46162.765109942135</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11395,13 +11403,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="P171" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="P171" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11411,7 +11419,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B172" s="5">
         <v>46162.68236944445</v>
@@ -11421,7 +11429,7 @@
         <v>46162.76510700231</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11446,13 +11454,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11462,7 +11470,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B173" s="9">
         <v>46162.68237259259</v>
@@ -11472,7 +11480,7 @@
         <v>46162.76510052083</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11497,13 +11505,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11513,7 +11521,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B174" s="5">
         <v>46162.682375902776</v>
@@ -11523,7 +11531,7 @@
         <v>46162.76510002315</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11548,13 +11556,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11564,7 +11572,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B175" s="9">
         <v>46162.682386099536</v>
@@ -11574,7 +11582,7 @@
         <v>46162.711784837964</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>25</v>
@@ -11598,7 +11606,7 @@
         <v>26</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P175" s="10" t="s">
         <v>26</v>
@@ -11611,7 +11619,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B176" s="5">
         <v>46162.68238924768</v>
@@ -11621,16 +11629,16 @@
         <v>46162.76537538195</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I176" s="5">
         <v>46227</v>
@@ -11648,13 +11656,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q176" s="5">
         <v>46227</v>
@@ -11674,7 +11682,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B177" s="9">
         <v>46162.682394664356</v>
@@ -11684,16 +11692,16 @@
         <v>46162.76536123843</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I177" s="9">
         <v>46227</v>
@@ -11711,13 +11719,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11727,7 +11735,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B178" s="5">
         <v>46162.68239902778</v>
@@ -11737,16 +11745,16 @@
         <v>46162.76535802083</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I178" s="5">
         <v>46227</v>
@@ -11764,13 +11772,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11780,7 +11788,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B179" s="9">
         <v>46162.682403321756</v>
@@ -11790,16 +11798,16 @@
         <v>46162.76535458333</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I179" s="9">
         <v>46227</v>
@@ -11817,13 +11825,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11833,7 +11841,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B180" s="5">
         <v>46162.68240755787</v>
@@ -11843,16 +11851,16 @@
         <v>46162.76535162037</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I180" s="5">
         <v>46227</v>
@@ -11870,13 +11878,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11886,7 +11894,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B181" s="9">
         <v>46162.68241208333</v>
@@ -11896,16 +11904,16 @@
         <v>46162.765348796296</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I181" s="9">
         <v>46227</v>
@@ -11923,13 +11931,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11939,7 +11947,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B182" s="5">
         <v>46162.682416400465</v>
@@ -11949,16 +11957,16 @@
         <v>46162.765344976855</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I182" s="5">
         <v>46227</v>
@@ -11976,13 +11984,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O182" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="P182" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="P182" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11992,7 +12000,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B183" s="9">
         <v>46162.68241952546</v>
@@ -12002,16 +12010,16 @@
         <v>46162.765340763886</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I183" s="9">
         <v>46227</v>
@@ -12029,10 +12037,10 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P183" s="10" t="s">
         <v>26</v>
@@ -12045,7 +12053,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B184" s="5">
         <v>46162.6824222338</v>
@@ -12055,16 +12063,16 @@
         <v>46162.765337488425</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I184" s="5">
         <v>46227</v>
@@ -12082,13 +12090,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12098,7 +12106,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B185" s="9">
         <v>46162.68242513889</v>
@@ -12108,16 +12116,16 @@
         <v>46162.76533056713</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I185" s="9">
         <v>46227</v>
@@ -12135,13 +12143,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12151,7 +12159,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B186" s="5">
         <v>46162.682428125</v>
@@ -12161,16 +12169,16 @@
         <v>46162.76532990741</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I186" s="5">
         <v>46227</v>
@@ -12188,13 +12196,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12204,7 +12212,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B187" s="9">
         <v>46162.68243688658</v>
@@ -12214,7 +12222,7 @@
         <v>46162.76634032407</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12241,13 +12249,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q187" s="9">
         <v>46230</v>
@@ -12267,7 +12275,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B188" s="5">
         <v>46162.68244069444</v>
@@ -12277,7 +12285,7 @@
         <v>46162.766318043985</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12304,13 +12312,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12320,7 +12328,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B189" s="9">
         <v>46162.68244457176</v>
@@ -12330,7 +12338,7 @@
         <v>46162.76631474537</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12357,13 +12365,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12373,7 +12381,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B190" s="5">
         <v>46162.68244844908</v>
@@ -12383,7 +12391,7 @@
         <v>46162.76631193287</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12410,13 +12418,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12426,7 +12434,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B191" s="9">
         <v>46162.68245221065</v>
@@ -12436,7 +12444,7 @@
         <v>46162.76630898148</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12463,13 +12471,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12479,7 +12487,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B192" s="5">
         <v>46162.68245652778</v>
@@ -12489,7 +12497,7 @@
         <v>46162.76630527778</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12516,13 +12524,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12532,7 +12540,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B193" s="9">
         <v>46162.68246049769</v>
@@ -12542,7 +12550,7 @@
         <v>46162.76630212963</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12569,10 +12577,10 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P193" s="10" t="s">
         <v>26</v>
@@ -12585,7 +12593,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B194" s="5">
         <v>46162.68246318287</v>
@@ -12595,7 +12603,7 @@
         <v>46162.76629917824</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12622,13 +12630,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12638,7 +12646,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B195" s="9">
         <v>46162.68246601852</v>
@@ -12648,7 +12656,7 @@
         <v>46162.76629561343</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12675,13 +12683,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12691,7 +12699,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B196" s="5">
         <v>46162.68246881945</v>
@@ -12701,7 +12709,7 @@
         <v>46162.766289004634</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12728,13 +12736,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12744,7 +12752,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B197" s="9">
         <v>46162.68247158565</v>
@@ -12754,7 +12762,7 @@
         <v>46162.76628835648</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12781,13 +12789,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12797,7 +12805,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B198" s="5">
         <v>46162.68248012732</v>
@@ -12807,16 +12815,16 @@
         <v>46162.76653042824</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I198" s="5">
         <v>46231</v>
@@ -12834,13 +12842,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q198" s="5">
         <v>46231</v>
@@ -12860,7 +12868,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B199" s="9">
         <v>46162.682524502314</v>
@@ -12870,16 +12878,16 @@
         <v>46162.766515462965</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I199" s="9">
         <v>46231</v>
@@ -12897,13 +12905,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -12913,7 +12921,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B200" s="5">
         <v>46162.682533032406</v>
@@ -12923,16 +12931,16 @@
         <v>46162.76651282408</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I200" s="5">
         <v>46231</v>
@@ -12950,13 +12958,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12966,7 +12974,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B201" s="9">
         <v>46162.68253883102</v>
@@ -12976,16 +12984,16 @@
         <v>46162.76651023148</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I201" s="9">
         <v>46231</v>
@@ -13003,13 +13011,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q201" s="10"/>
       <c r="R201" s="10"/>
@@ -13019,7 +13027,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B202" s="5">
         <v>46162.68254368055</v>
@@ -13029,16 +13037,16 @@
         <v>46162.76650773148</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I202" s="5">
         <v>46231</v>
@@ -13056,13 +13064,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13072,7 +13080,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B203" s="9">
         <v>46162.68255409722</v>
@@ -13082,16 +13090,16 @@
         <v>46162.76650408565</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I203" s="9">
         <v>46231</v>
@@ -13109,13 +13117,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13125,7 +13133,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B204" s="5">
         <v>46162.6825590625</v>
@@ -13135,16 +13143,16 @@
         <v>46162.76650106482</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I204" s="5">
         <v>46231</v>
@@ -13162,13 +13170,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13178,7 +13186,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B205" s="9">
         <v>46162.68256261574</v>
@@ -13188,16 +13196,16 @@
         <v>46162.76649841435</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I205" s="9">
         <v>46231</v>
@@ -13215,13 +13223,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13231,7 +13239,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B206" s="5">
         <v>46162.682566006944</v>
@@ -13241,16 +13249,16 @@
         <v>46162.76649456019</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I206" s="5">
         <v>46231</v>
@@ -13268,13 +13276,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13284,7 +13292,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B207" s="9">
         <v>46162.682569386576</v>
@@ -13294,16 +13302,16 @@
         <v>46162.766489050926</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I207" s="9">
         <v>46231</v>
@@ -13321,13 +13329,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13337,7 +13345,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B208" s="5">
         <v>46162.68257278935</v>
@@ -13347,16 +13355,16 @@
         <v>46162.76648839121</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I208" s="5">
         <v>46231</v>
@@ -13374,13 +13382,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13390,7 +13398,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B209" s="9">
         <v>46162.68258331019</v>
@@ -13400,16 +13408,16 @@
         <v>46162.76671087963</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I209" s="9">
         <v>46232</v>
@@ -13427,13 +13435,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Q209" s="9">
         <v>46232</v>
@@ -13453,7 +13461,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B210" s="5">
         <v>46162.6825891551</v>
@@ -13463,16 +13471,16 @@
         <v>46162.76670017361</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I210" s="5">
         <v>46232</v>
@@ -13490,13 +13498,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13506,7 +13514,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B211" s="9">
         <v>46162.68259327546</v>
@@ -13516,16 +13524,16 @@
         <v>46162.76669680556</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I211" s="9">
         <v>46232</v>
@@ -13543,13 +13551,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13559,7 +13567,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B212" s="5">
         <v>46162.682597499996</v>
@@ -13569,16 +13577,16 @@
         <v>46162.76669409723</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I212" s="5">
         <v>46232</v>
@@ -13596,13 +13604,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13612,7 +13620,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B213" s="9">
         <v>46162.68260168981</v>
@@ -13622,16 +13630,16 @@
         <v>46162.766691377314</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I213" s="9">
         <v>46232</v>
@@ -13649,13 +13657,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13665,7 +13673,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B214" s="5">
         <v>46162.68260615741</v>
@@ -13675,16 +13683,16 @@
         <v>46162.766687662035</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I214" s="5">
         <v>46232</v>
@@ -13702,13 +13710,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13718,7 +13726,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B215" s="9">
         <v>46162.68261056713</v>
@@ -13728,16 +13736,16 @@
         <v>46162.76668472222</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I215" s="9">
         <v>46232</v>
@@ -13755,10 +13763,10 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13771,7 +13779,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B216" s="5">
         <v>46162.682613564815</v>
@@ -13781,16 +13789,16 @@
         <v>46162.76668173611</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I216" s="5">
         <v>46232</v>
@@ -13808,10 +13816,10 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13824,7 +13832,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B217" s="9">
         <v>46162.682616666665</v>
@@ -13834,16 +13842,16 @@
         <v>46162.76667282407</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I217" s="9">
         <v>46232</v>
@@ -13861,10 +13869,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13877,7 +13885,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B218" s="5">
         <v>46162.682619583335</v>
@@ -13887,16 +13895,16 @@
         <v>46162.76667212963</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I218" s="5">
         <v>46232</v>
@@ -13914,10 +13922,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>
@@ -13930,7 +13938,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B219" s="9">
         <v>46162.68262266203</v>
@@ -13940,16 +13948,16 @@
         <v>46162.76667141204</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I219" s="9">
         <v>46232</v>
@@ -13967,10 +13975,10 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>26</v>
@@ -13983,7 +13991,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B220" s="5">
         <v>46162.682665625005</v>
@@ -13993,7 +14001,7 @@
         <v>46162.76005167824</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>25</v>
@@ -14017,7 +14025,7 @@
         <v>26</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>26</v>
@@ -14030,7 +14038,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B221" s="9">
         <v>46162.68266950232</v>
@@ -14040,16 +14048,16 @@
         <v>46162.76676789352</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I221" s="9">
         <v>46233</v>
@@ -14067,13 +14075,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q221" s="9">
         <v>46233</v>
@@ -14093,7 +14101,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B222" s="5">
         <v>46162.68267490741</v>
@@ -14103,7 +14111,7 @@
         <v>46162.76682827546</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14130,13 +14138,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q222" s="5">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.87718591435</v>
+        <v>46198.16913447916</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>91</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -167,9 +167,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214977075698269</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete OT4327</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214977075717388</t>
@@ -2454,9 +2454,11 @@
       <c r="B10" s="5">
         <v>46162.68116798611</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46198.68205895834</v>
+      </c>
       <c r="D10" s="5">
-        <v>46197.777048703705</v>
+        <v>46198.68207692129</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2491,14 +2493,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="12" t="s">
-        <v>47</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="9">
         <v>46162.68129303241</v>
@@ -2510,16 +2514,16 @@
         <v>46197.77703842593</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I11" s="9">
         <v>46149</v>
@@ -2531,7 +2535,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2543,7 +2547,7 @@
         <v>39</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="9">
         <v>46149</v>
@@ -2552,7 +2556,7 @@
         <v>46150</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T11" s="10">
         <v>1</v>
@@ -2563,7 +2567,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46162.68129826389</v>
@@ -2575,16 +2579,16 @@
         <v>46197.77703841435</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2596,7 +2600,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2608,7 +2612,7 @@
         <v>39</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2617,7 +2621,7 @@
         <v>46150</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2628,7 +2632,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="9">
         <v>46162.68130347222</v>
@@ -2640,16 +2644,16 @@
         <v>46197.777039189816</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I13" s="9">
         <v>46149</v>
@@ -2661,7 +2665,7 @@
         <v>26</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>26</v>
@@ -2673,7 +2677,7 @@
         <v>39</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9">
         <v>46149</v>
@@ -2682,7 +2686,7 @@
         <v>46157</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T13" s="10">
         <v>1</v>
@@ -2693,17 +2697,17 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46162.68117188658</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.587885057874</v>
+        <v>46198.68510511574</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2727,7 +2731,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2740,26 +2744,28 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="9">
         <v>46162.681316030095</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46198.68228026621</v>
+      </c>
       <c r="D15" s="9">
-        <v>46197.66702332176</v>
+        <v>46198.6822819213</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I15" s="9">
         <v>46153</v>
@@ -2777,13 +2783,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="9">
         <v>46153</v>
@@ -2792,37 +2798,39 @@
         <v>46154</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46162.68132108796</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46198.68509829861</v>
+      </c>
       <c r="D16" s="5">
-        <v>46197.66978644676</v>
+        <v>46198.685114224536</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I16" s="5">
         <v>46153</v>
@@ -2840,13 +2848,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46153</v>
@@ -2855,18 +2863,18 @@
         <v>46154</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9">
         <v>46162.68132700231</v>
@@ -2878,16 +2886,16 @@
         <v>46197.66978645833</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46153</v>
@@ -2905,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46153</v>
@@ -2920,13 +2928,13 @@
         <v>46154</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2968,7 +2976,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>80</v>
@@ -3031,7 +3039,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>80</v>
@@ -3094,7 +3102,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>80</v>
@@ -3157,7 +3165,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>80</v>
@@ -3190,7 +3198,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46162.701055185185</v>
+        <v>46198.685312800924</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -3235,9 +3243,11 @@
       <c r="B23" s="9">
         <v>46162.681348645834</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46198.68530165509</v>
+      </c>
       <c r="D23" s="9">
-        <v>46169.87666193287</v>
+        <v>46198.68532041667</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -3282,13 +3292,13 @@
         <v>46160</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3298,9 +3308,11 @@
       <c r="B24" s="5">
         <v>46162.68135300926</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46198.68525414352</v>
+      </c>
       <c r="D24" s="5">
-        <v>46169.87692592593</v>
+        <v>46198.68525572917</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3333,7 +3345,7 @@
         <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>102</v>
@@ -3341,7 +3353,7 @@
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -3357,9 +3369,11 @@
       <c r="B25" s="9">
         <v>46162.68135747685</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46198.68528871528</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.876936932866</v>
+        <v>46198.68529017361</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3400,7 +3414,7 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
@@ -3463,7 +3477,7 @@
         <v>46160</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3514,7 +3528,7 @@
         <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>111</v>
@@ -3522,7 +3536,7 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3581,7 +3595,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3599,7 +3613,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46196.1721819213</v>
+        <v>46198.68314474537</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3660,9 +3674,11 @@
       <c r="B30" s="5">
         <v>46162.681382083334</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46198.68232337963</v>
+      </c>
       <c r="D30" s="5">
-        <v>46169.877024456015</v>
+        <v>46198.682324814814</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3695,7 +3711,7 @@
         <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>120</v>
@@ -3703,7 +3719,7 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3721,7 +3737,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46195.16987640046</v>
+        <v>46198.68233005787</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3762,7 +3778,7 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3778,9 +3794,11 @@
       <c r="B32" s="5">
         <v>46162.68139224537</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46198.683139166664</v>
+      </c>
       <c r="D32" s="5">
-        <v>46197.70342619213</v>
+        <v>46198.683140567126</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3821,7 +3839,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3943,7 +3961,7 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3998,7 +4016,7 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
@@ -4230,7 +4248,7 @@
         <v>46231</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -4658,7 +4676,7 @@
         <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>176</v>
@@ -4688,7 +4706,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.703094780096</v>
+        <v>46198.68315570602</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4738,8 +4756,8 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="11" t="s">
-        <v>82</v>
+      <c r="U48" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4857,7 +4875,7 @@
         <v>46225</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -5890,7 +5908,7 @@
         <v>46209</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -6483,7 +6501,7 @@
         <v>46216</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -7076,7 +7094,7 @@
         <v>46217</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -7714,7 +7732,7 @@
         <v>46161</v>
       </c>
       <c r="S103" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T103" s="10">
         <v>0</v>
@@ -7732,7 +7750,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46162.763977916664</v>
+        <v>46198.685305949075</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>284</v>
@@ -7775,13 +7793,13 @@
         <v>46161</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="11" t="s">
-        <v>82</v>
+      <c r="U104" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7897,7 +7915,7 @@
         <v>46232</v>
       </c>
       <c r="S106" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -7971,10 +7989,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I108" s="5">
         <v>46218</v>
@@ -8007,7 +8025,7 @@
         <v>46224</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
@@ -8034,10 +8052,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I109" s="9">
         <v>46218</v>
@@ -8087,10 +8105,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I110" s="5">
         <v>46218</v>
@@ -8140,10 +8158,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I111" s="9">
         <v>46218</v>
@@ -8193,10 +8211,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I112" s="5">
         <v>46218</v>
@@ -8246,10 +8264,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I113" s="9">
         <v>46218</v>
@@ -8299,10 +8317,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I114" s="5">
         <v>46218</v>
@@ -8352,10 +8370,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I115" s="9">
         <v>46218</v>
@@ -8405,10 +8423,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I116" s="5">
         <v>46218</v>
@@ -8458,10 +8476,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I117" s="9">
         <v>46218</v>
@@ -8511,10 +8529,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I118" s="5">
         <v>46218</v>
@@ -8564,10 +8582,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I119" s="9">
         <v>46219</v>
@@ -8600,7 +8618,7 @@
         <v>46219</v>
       </c>
       <c r="S119" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T119" s="10">
         <v>0</v>
@@ -8627,10 +8645,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I120" s="5">
         <v>46219</v>
@@ -8680,10 +8698,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I121" s="9">
         <v>46219</v>
@@ -8733,10 +8751,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I122" s="5">
         <v>46219</v>
@@ -8786,10 +8804,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I123" s="9">
         <v>46219</v>
@@ -8839,10 +8857,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I124" s="5">
         <v>46219</v>
@@ -8892,10 +8910,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I125" s="9">
         <v>46219</v>
@@ -8945,10 +8963,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I126" s="5">
         <v>46219</v>
@@ -8998,10 +9016,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I127" s="9">
         <v>46219</v>
@@ -9051,10 +9069,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I128" s="5">
         <v>46219</v>
@@ -9104,10 +9122,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I129" s="9">
         <v>46219</v>
@@ -9157,10 +9175,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I130" s="5">
         <v>46220</v>
@@ -9193,7 +9211,7 @@
         <v>46220</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -9220,10 +9238,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I131" s="9">
         <v>46220</v>
@@ -9273,10 +9291,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I132" s="5">
         <v>46220</v>
@@ -9326,10 +9344,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I133" s="9">
         <v>46220</v>
@@ -9379,10 +9397,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I134" s="5">
         <v>46220</v>
@@ -9432,10 +9450,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I135" s="9">
         <v>46220</v>
@@ -9485,10 +9503,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I136" s="5">
         <v>46220</v>
@@ -9538,10 +9556,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I137" s="9">
         <v>46220</v>
@@ -9591,10 +9609,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I138" s="5">
         <v>46220</v>
@@ -9644,10 +9662,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I139" s="9">
         <v>46220</v>
@@ -9697,10 +9715,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I140" s="5">
         <v>46220</v>
@@ -9750,10 +9768,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I141" s="9">
         <v>46223</v>
@@ -9786,7 +9804,7 @@
         <v>46223</v>
       </c>
       <c r="S141" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T141" s="10">
         <v>0</v>
@@ -9813,10 +9831,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I142" s="5">
         <v>46223</v>
@@ -9866,10 +9884,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I143" s="9">
         <v>46223</v>
@@ -9919,10 +9937,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I144" s="5">
         <v>46223</v>
@@ -9972,10 +9990,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I145" s="9">
         <v>46223</v>
@@ -10025,10 +10043,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I146" s="5">
         <v>46223</v>
@@ -10078,10 +10096,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I147" s="9">
         <v>46223</v>
@@ -10131,10 +10149,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I148" s="5">
         <v>46223</v>
@@ -10184,10 +10202,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I149" s="9">
         <v>46223</v>
@@ -10237,10 +10255,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I150" s="5">
         <v>46223</v>
@@ -10290,10 +10308,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I151" s="9">
         <v>46223</v>
@@ -10343,10 +10361,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I152" s="5">
         <v>46224</v>
@@ -10379,7 +10397,7 @@
         <v>46224</v>
       </c>
       <c r="S152" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T152" s="6">
         <v>0</v>
@@ -10406,10 +10424,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I153" s="9">
         <v>46224</v>
@@ -10459,10 +10477,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I154" s="5">
         <v>46224</v>
@@ -10512,10 +10530,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I155" s="9">
         <v>46224</v>
@@ -10565,10 +10583,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I156" s="5">
         <v>46224</v>
@@ -10618,10 +10636,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I157" s="9">
         <v>46224</v>
@@ -10671,10 +10689,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I158" s="5">
         <v>46224</v>
@@ -10724,10 +10742,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I159" s="9">
         <v>46224</v>
@@ -10777,10 +10795,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I160" s="5">
         <v>46224</v>
@@ -10830,10 +10848,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I161" s="9">
         <v>46224</v>
@@ -10883,10 +10901,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I162" s="5">
         <v>46224</v>
@@ -10936,10 +10954,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I163" s="9">
         <v>46226</v>
@@ -10972,7 +10990,7 @@
         <v>46226</v>
       </c>
       <c r="S163" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T163" s="10">
         <v>0</v>
@@ -10999,10 +11017,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I164" s="6"/>
       <c r="J164" s="5">
@@ -11050,10 +11068,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I165" s="10"/>
       <c r="J165" s="9">
@@ -11101,10 +11119,10 @@
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11152,10 +11170,10 @@
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I167" s="10"/>
       <c r="J167" s="9">
@@ -11203,10 +11221,10 @@
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11254,10 +11272,10 @@
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I169" s="10"/>
       <c r="J169" s="9">
@@ -11305,10 +11323,10 @@
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11356,10 +11374,10 @@
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I171" s="10"/>
       <c r="J171" s="9">
@@ -11407,10 +11425,10 @@
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11458,10 +11476,10 @@
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I173" s="10"/>
       <c r="J173" s="9">
@@ -11592,7 +11610,7 @@
         <v>46227</v>
       </c>
       <c r="S175" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T175" s="10">
         <v>0</v>
@@ -12149,10 +12167,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I186" s="5">
         <v>46230</v>
@@ -12185,7 +12203,7 @@
         <v>46230</v>
       </c>
       <c r="S186" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T186" s="6">
         <v>0</v>
@@ -12212,10 +12230,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I187" s="9">
         <v>46230</v>
@@ -12265,10 +12283,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I188" s="5">
         <v>46230</v>
@@ -12318,10 +12336,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I189" s="9">
         <v>46230</v>
@@ -12371,10 +12389,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I190" s="5">
         <v>46230</v>
@@ -12424,10 +12442,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I191" s="9">
         <v>46230</v>
@@ -12477,10 +12495,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I192" s="5">
         <v>46230</v>
@@ -12530,10 +12548,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I193" s="9">
         <v>46230</v>
@@ -12583,10 +12601,10 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I194" s="5">
         <v>46230</v>
@@ -12636,10 +12654,10 @@
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I195" s="9">
         <v>46230</v>
@@ -12689,10 +12707,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I196" s="5">
         <v>46230</v>
@@ -12778,7 +12796,7 @@
         <v>46231</v>
       </c>
       <c r="S197" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T197" s="10">
         <v>0</v>
@@ -13371,7 +13389,7 @@
         <v>46232</v>
       </c>
       <c r="S208" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T208" s="6">
         <v>0</v>
@@ -14011,7 +14029,7 @@
         <v>46241</v>
       </c>
       <c r="S220" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T220" s="6">
         <v>0</v>
@@ -14038,10 +14056,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I221" s="9">
         <v>46233</v>
@@ -14074,7 +14092,7 @@
         <v>46241</v>
       </c>
       <c r="S221" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T221" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="469">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -289,67 +289,67 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT4327</t>
   </si>
   <si>
+    <t>1214977075717403</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT4327</t>
+  </si>
+  <si>
+    <t>1214977075717413</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732911</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT4327</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT4327</t>
+  </si>
+  <si>
+    <t>1214969047720958</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe OT4327,Motor OT4327,rodete OT4327,Materiales corte Laser OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732921</t>
+  </si>
+  <si>
+    <t>Alabe OT4327</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT4327,Fabricación Alabe OT4327</t>
+  </si>
+  <si>
+    <t>1214977075732936</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT4327</t>
+  </si>
+  <si>
+    <t>Alabe OT4327,Fabricación Alabe OT4327</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214977075717403</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT4327</t>
-  </si>
-  <si>
-    <t>1214977075717413</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732911</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT4327</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT4327</t>
-  </si>
-  <si>
-    <t>1214969047720958</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe OT4327,Motor OT4327,rodete OT4327,Materiales corte Laser OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732921</t>
-  </si>
-  <si>
-    <t>Alabe OT4327</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT4327,Fabricación Alabe OT4327</t>
-  </si>
-  <si>
-    <t>1214977075732936</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT4327</t>
-  </si>
-  <si>
-    <t>Alabe OT4327,Fabricación Alabe OT4327</t>
   </si>
   <si>
     <t>1214977316760264</t>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46190.17346704861</v>
+        <v>46198.7965890162</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2996,23 +2996,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>82</v>
+      <c r="U18" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46162.68133762731</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46190.17346712963</v>
+        <v>46198.79658804398</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3045,7 +3045,7 @@
         <v>80</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46188</v>
@@ -3059,23 +3059,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>82</v>
+      <c r="U19" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46162.68134119213</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46190.17346684028</v>
+        <v>46198.79658851852</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3108,7 +3108,7 @@
         <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46188</v>
@@ -3122,23 +3122,23 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>82</v>
+      <c r="U20" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46162.6813446875</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46190.1734668287</v>
+        <v>46198.79658900463</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -3171,7 +3171,7 @@
         <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46188</v>
@@ -3185,13 +3185,13 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
-        <v>82</v>
+      <c r="U21" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46162.68117578704</v>
@@ -3201,7 +3201,7 @@
         <v>46198.685312800924</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3225,7 +3225,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46162.681348645834</v>
@@ -3250,16 +3250,16 @@
         <v>46198.68532041667</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I23" s="9">
         <v>46155</v>
@@ -3277,13 +3277,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46155</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46162.68135300926</v>
@@ -3315,16 +3315,16 @@
         <v>46198.68525572917</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46155</v>
@@ -3342,13 +3342,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3382,10 +3382,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I25" s="9">
         <v>46157</v>
@@ -3403,10 +3403,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>105</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3441,10 +3441,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46155</v>
@@ -3462,13 +3462,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46155</v>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46155</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3563,10 +3563,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46157</v>
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3622,10 +3622,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3643,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46155</v>
@@ -3664,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3687,10 +3687,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46167</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3807,10 +3807,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46167</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3887,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46190</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4064,7 +4064,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>141</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4100,7 +4100,7 @@
         <v>46189.16936783565</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -4130,7 +4130,7 @@
         <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>143</v>
@@ -4183,7 +4183,7 @@
         <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>146</v>
@@ -4233,7 +4233,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>151</v>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4269,7 +4269,7 @@
         <v>46198.16913447916</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4299,7 +4299,7 @@
         <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -4352,7 +4352,7 @@
         <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>156</v>
@@ -4455,7 +4455,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>163</v>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4491,7 +4491,7 @@
         <v>46191.1693375926</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4521,7 +4521,7 @@
         <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>165</v>
@@ -4574,7 +4574,7 @@
         <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>168</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46197.70289550926</v>
+        <v>46198.796516539354</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4630,7 +4630,9 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -4704,9 +4706,11 @@
       <c r="B48" s="5">
         <v>46162.68151027778</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46198.796495462964</v>
+      </c>
       <c r="D48" s="5">
-        <v>46198.68315570602</v>
+        <v>46198.796512534725</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4754,10 +4758,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4767,9 +4771,11 @@
       <c r="B49" s="9">
         <v>46162.6815165625</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46198.79653876157</v>
+      </c>
       <c r="D49" s="9">
-        <v>46186.16887460648</v>
+        <v>46198.796557442125</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4817,10 +4823,10 @@
         <v>33</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4881,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5499,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5560,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5621,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5682,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5743,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5804,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5914,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -6507,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6519,7 +6525,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46162.763601388884</v>
+        <v>46198.79655543981</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>191</v>
@@ -6572,7 +6578,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46162.76359828704</v>
+        <v>46198.79656188657</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>191</v>
@@ -6625,7 +6631,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46162.763595428245</v>
+        <v>46198.79655649306</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>191</v>
@@ -6678,7 +6684,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46162.76359266204</v>
+        <v>46198.796557222224</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>191</v>
@@ -7100,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7112,7 +7118,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.76379824074</v>
+        <v>46198.79656256945</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -7165,7 +7171,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46162.76379479167</v>
+        <v>46198.79657365741</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7218,7 +7224,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46162.763791562495</v>
+        <v>46198.79657413195</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>191</v>
@@ -7271,7 +7277,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46162.76378862269</v>
+        <v>46198.79657465278</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>191</v>
@@ -7738,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7860,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7921,7 +7927,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8031,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8624,7 +8630,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8636,7 +8642,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.764425138885</v>
+        <v>46198.79655782407</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>191</v>
@@ -8689,7 +8695,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.7644221875</v>
+        <v>46198.79657496528</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>191</v>
@@ -8742,7 +8748,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.76441872685</v>
+        <v>46198.79657011574</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>191</v>
@@ -8795,7 +8801,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46162.76441527778</v>
+        <v>46198.79655399306</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>191</v>
@@ -8901,7 +8907,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46162.76440929398</v>
+        <v>46198.7965582176</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>191</v>
@@ -8954,7 +8960,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46162.76440640046</v>
+        <v>46198.796559062495</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>191</v>
@@ -9007,7 +9013,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46162.764403761576</v>
+        <v>46198.796559594906</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>191</v>
@@ -9060,7 +9066,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46162.764396388884</v>
+        <v>46198.79656293981</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>191</v>
@@ -9113,7 +9119,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46162.76439568287</v>
+        <v>46198.79657047454</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>191</v>
@@ -9217,7 +9223,7 @@
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9229,7 +9235,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46162.76461333333</v>
+        <v>46198.79656021991</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>191</v>
@@ -9282,7 +9288,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46162.764610439815</v>
+        <v>46198.79656121528</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>191</v>
@@ -9335,7 +9341,7 @@
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46162.76460753472</v>
+        <v>46198.7965709375</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>191</v>
@@ -9388,7 +9394,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46162.76460444444</v>
+        <v>46198.79655481481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>191</v>
@@ -9810,7 +9816,7 @@
         <v>0</v>
       </c>
       <c r="U141" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -9822,7 +9828,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46162.76477363426</v>
+        <v>46198.79657170139</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>191</v>
@@ -9875,7 +9881,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46162.76477071759</v>
+        <v>46198.796572175925</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>191</v>
@@ -9928,7 +9934,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46162.764767141205</v>
+        <v>46198.796563564814</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>191</v>
@@ -9981,7 +9987,7 @@
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46162.764764039355</v>
+        <v>46198.79657305556</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>191</v>
@@ -10403,7 +10409,7 @@
         <v>0</v>
       </c>
       <c r="U152" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
@@ -10996,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="U163" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
@@ -11616,7 +11622,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -12209,7 +12215,7 @@
         <v>0</v>
       </c>
       <c r="U186" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
@@ -12802,7 +12808,7 @@
         <v>0</v>
       </c>
       <c r="U197" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
@@ -13395,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="U208" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
@@ -14035,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="U220" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
@@ -14098,7 +14104,7 @@
         <v>0</v>
       </c>
       <c r="U221" s="11" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46195.19788605324</v>
+        <v>46202.169330289355</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.19788600694</v>
+        <v>46202.16932775463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.87714701389</v>
+        <v>46202.16933497685</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46195.197886145834</v>
+        <v>46202.16933210648</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87727920139</v>
+        <v>46202.169333576385</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46162.763335578704</v>
+        <v>46202.17884375</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>228</v>
@@ -5913,8 +5913,8 @@
       <c r="R69" s="9">
         <v>46209</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>53</v>
+      <c r="S69" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -439,238 +439,238 @@
     <t xml:space="preserve">Generación OC materiales corte Laser OT4327,Fabricacion Corte Lase OT4327 </t>
   </si>
   <si>
+    <t>1214977533942291</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT4327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT4327,Fabricacion Corte Lase OT4327 </t>
+  </si>
+  <si>
+    <t>1214977533942309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Lase OT4327 </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT4327</t>
+  </si>
+  <si>
+    <t>1214977075712010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma OT4327 </t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT4327,Fabricación Corte Plasma  OT4327</t>
+  </si>
+  <si>
+    <t>1214977316848064</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma OT4327 ,Fabricación Corte Plasma  OT4327</t>
+  </si>
+  <si>
+    <t>1214977316848079</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  OT4327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Materiales corte plasma,Materiales Corte Plasma OT4327 </t>
+  </si>
+  <si>
+    <t>1214977316851341</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT4327</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT4327,Generacion OC Fabricación Externa OT4327</t>
+  </si>
+  <si>
+    <t>1214977316851351</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT4327,Fabricación estructura proveedor externo OT4327</t>
+  </si>
+  <si>
+    <t>1214977316851366</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT4327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT4327,Control de calidad fabricación externa  OT4327,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214977075855431</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT4327</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214977075855441</t>
+  </si>
+  <si>
+    <t>Mecanizado OT4327</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT4327,Fabricación  OT4327</t>
+  </si>
+  <si>
+    <t>1214977075855451</t>
+  </si>
+  <si>
+    <t>Mecanizado OT4327,Fabricación  OT4327</t>
+  </si>
+  <si>
+    <t>1214977075856727</t>
+  </si>
+  <si>
+    <t>Fabricación  OT4327</t>
+  </si>
+  <si>
+    <t>Mecanizado OT4327,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214969047720960</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977075856742</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977521258828</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT4327</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214977521270201</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Propuesta Mecanizado OT4327,Propuesta Fabricación externa  OT4327,propuesta Corte Laser OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405347</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405357</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405367</t>
+  </si>
+  <si>
+    <t>1214977316866399</t>
+  </si>
+  <si>
+    <t>1214977316866404</t>
+  </si>
+  <si>
+    <t>1214977316866409</t>
+  </si>
+  <si>
+    <t>1214977316866414</t>
+  </si>
+  <si>
+    <t>1214977316866419</t>
+  </si>
+  <si>
+    <t>1214977316884296</t>
+  </si>
+  <si>
+    <t>1214977316884301</t>
+  </si>
+  <si>
+    <t>1214977316884306</t>
+  </si>
+  <si>
+    <t>1214977316832250</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214977316832260</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977533942291</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT4327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT4327,Fabricacion Corte Lase OT4327 </t>
-  </si>
-  <si>
-    <t>1214977533942309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Lase OT4327 </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT4327</t>
-  </si>
-  <si>
-    <t>1214977075712010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma OT4327 </t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT4327,Fabricación Corte Plasma  OT4327</t>
-  </si>
-  <si>
-    <t>1214977316848064</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma OT4327 ,Fabricación Corte Plasma  OT4327</t>
-  </si>
-  <si>
-    <t>1214977316848079</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  OT4327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Materiales corte plasma,Materiales Corte Plasma OT4327 </t>
-  </si>
-  <si>
-    <t>1214977316851341</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT4327</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT4327,Generacion OC Fabricación Externa OT4327</t>
-  </si>
-  <si>
-    <t>1214977316851351</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT4327,Fabricación estructura proveedor externo OT4327</t>
-  </si>
-  <si>
-    <t>1214977316851366</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT4327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT4327,Control de calidad fabricación externa  OT4327,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214977075855431</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT4327</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214977075855441</t>
-  </si>
-  <si>
-    <t>Mecanizado OT4327</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT4327,Fabricación  OT4327</t>
-  </si>
-  <si>
-    <t>1214977075855451</t>
-  </si>
-  <si>
-    <t>Mecanizado OT4327,Fabricación  OT4327</t>
-  </si>
-  <si>
-    <t>1214977075856727</t>
-  </si>
-  <si>
-    <t>Fabricación  OT4327</t>
-  </si>
-  <si>
-    <t>Mecanizado OT4327,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214969047720960</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977075856742</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977521258828</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT4327</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214977521270201</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Propuesta Mecanizado OT4327,Propuesta Fabricación externa  OT4327,propuesta Corte Laser OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405347</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405357</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405367</t>
-  </si>
-  <si>
-    <t>1214977316866399</t>
-  </si>
-  <si>
-    <t>1214977316866404</t>
-  </si>
-  <si>
-    <t>1214977316866409</t>
-  </si>
-  <si>
-    <t>1214977316866414</t>
-  </si>
-  <si>
-    <t>1214977316866419</t>
-  </si>
-  <si>
-    <t>1214977316884296</t>
-  </si>
-  <si>
-    <t>1214977316884301</t>
-  </si>
-  <si>
-    <t>1214977316884306</t>
-  </si>
-  <si>
-    <t>1214977316832250</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214977316832260</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214977075952529</t>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46202.169330289355</v>
+        <v>46203.20693458333</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3901,8 +3901,8 @@
       <c r="R33" s="9">
         <v>46202</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>132</v>
+      <c r="S33" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46162.68140180556</v>
@@ -3923,7 +3923,7 @@
         <v>46191.169341932866</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3956,7 +3956,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46162.681406793985</v>
@@ -3982,7 +3982,7 @@
         <v>46169.87710333333</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -4008,10 +4008,10 @@
         <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -4027,17 +4027,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46162.68146234954</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46202.16932775463</v>
+        <v>46203.20693486111</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4067,7 +4067,7 @@
         <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -4078,8 +4078,8 @@
       <c r="R36" s="5">
         <v>46202</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>132</v>
+      <c r="S36" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46162.68146784722</v>
@@ -4127,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46162.68147298611</v>
@@ -4153,7 +4153,7 @@
         <v>46202.16933497685</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4180,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46162.681477175924</v>
@@ -4206,16 +4206,16 @@
         <v>46169.876735</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I39" s="9">
         <v>46190</v>
@@ -4236,7 +4236,7 @@
         <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.68148049769</v>
@@ -4275,10 +4275,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46190</v>
@@ -4296,13 +4296,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46162.681484872686</v>
@@ -4322,16 +4322,16 @@
         <v>46169.87719863426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46199</v>
@@ -4349,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46162.68148924768</v>
@@ -4375,16 +4375,16 @@
         <v>46169.877211388884</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46230</v>
@@ -4402,10 +4402,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4418,17 +4418,17 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46162.68149232639</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46202.16933210648</v>
+        <v>46203.20693501158</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4458,7 +4458,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4469,8 +4469,8 @@
       <c r="R43" s="9">
         <v>46202</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>132</v>
+      <c r="S43" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.68149587963</v>
@@ -4518,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46162.6815003125</v>
@@ -4544,7 +4544,7 @@
         <v>46202.169333576385</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4571,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46162.68117938658</v>
@@ -4597,7 +4597,7 @@
         <v>46198.796516539354</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4621,7 +4621,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46162.68150506944</v>
@@ -4648,16 +4648,16 @@
         <v>46197.703074074074</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4675,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.68151027778</v>
@@ -4713,16 +4713,16 @@
         <v>46198.796512534725</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46176</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46162.6815165625</v>
@@ -4784,10 +4784,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="9">
         <v>46185</v>
@@ -4805,13 +4805,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46185</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46162.68153015046</v>
@@ -4841,16 +4841,16 @@
         <v>46162.76230295139</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4866,10 +4866,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46162.68153354166</v>
@@ -4902,16 +4902,16 @@
         <v>46162.76229798611</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4927,13 +4927,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.68153736111</v>
@@ -4953,16 +4953,16 @@
         <v>46162.76229449074</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4978,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.68154143519</v>
@@ -5004,16 +5004,16 @@
         <v>46162.76229145833</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -5029,13 +5029,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -5045,7 +5045,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.68154440972</v>
@@ -5055,16 +5055,16 @@
         <v>46162.76228877315</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -5080,13 +5080,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5096,7 +5096,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46162.68154740741</v>
@@ -5106,16 +5106,16 @@
         <v>46162.76228596065</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="9">
@@ -5131,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46162.68155047453</v>
@@ -5157,16 +5157,16 @@
         <v>46162.762282870375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5182,10 +5182,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5198,7 +5198,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="9">
         <v>46162.681552766204</v>
@@ -5208,16 +5208,16 @@
         <v>46162.76227917824</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="9">
@@ -5233,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46162.68155516204</v>
@@ -5259,16 +5259,16 @@
         <v>46162.76227634259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5284,13 +5284,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5300,7 +5300,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46162.6815574537</v>
@@ -5310,16 +5310,16 @@
         <v>46162.7622690162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="9">
@@ -5335,10 +5335,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B60" s="5">
         <v>46162.68155952546</v>
@@ -5361,16 +5361,16 @@
         <v>46162.762268391205</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5386,10 +5386,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B61" s="9">
         <v>46162.681598807874</v>
@@ -5412,7 +5412,7 @@
         <v>46162.707360960645</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5436,7 +5436,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5449,26 +5449,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46162.681602743054</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46196.168763634254</v>
+        <v>46203.17051119213</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5484,13 +5484,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="5">
         <v>46203</v>
@@ -5499,7 +5499,7 @@
         <v>46203</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5526,10 +5526,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5545,7 +5545,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>212</v>
@@ -5560,7 +5560,7 @@
         <v>46204</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.16876357639</v>
+        <v>46203.170507187504</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5587,10 +5587,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5606,10 +5606,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>216</v>
@@ -5621,7 +5621,7 @@
         <v>46203</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5648,10 +5648,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I65" s="10"/>
       <c r="J65" s="9">
@@ -5667,7 +5667,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>215</v>
@@ -5682,7 +5682,7 @@
         <v>46204</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46196.16876371528</v>
+        <v>46203.17051256944</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5709,10 +5709,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5728,10 +5728,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>222</v>
@@ -5743,7 +5743,7 @@
         <v>46203</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5770,10 +5770,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I67" s="10"/>
       <c r="J67" s="9">
@@ -5789,7 +5789,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>221</v>
@@ -5804,7 +5804,7 @@
         <v>46204</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5914,7 +5914,7 @@
         <v>46209</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>46162.763318530095</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5988,7 +5988,7 @@
         <v>46162.76331560186</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -6041,7 +6041,7 @@
         <v>46162.76331271991</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6094,7 +6094,7 @@
         <v>46162.763309710645</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6147,7 +6147,7 @@
         <v>46162.763306759254</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6200,7 +6200,7 @@
         <v>46162.76330359954</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6233,7 +6233,7 @@
         <v>243</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6253,7 +6253,7 @@
         <v>46162.7633006713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6286,7 +6286,7 @@
         <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6306,7 +6306,7 @@
         <v>46162.763297384256</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6339,7 +6339,7 @@
         <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6359,7 +6359,7 @@
         <v>46162.763290891206</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6392,7 +6392,7 @@
         <v>236</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6412,7 +6412,7 @@
         <v>46162.763290243056</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6445,7 +6445,7 @@
         <v>236</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6528,7 +6528,7 @@
         <v>46198.79655543981</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6581,7 +6581,7 @@
         <v>46198.79656188657</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6634,7 +6634,7 @@
         <v>46198.79655649306</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6687,7 +6687,7 @@
         <v>46198.796557222224</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6740,7 +6740,7 @@
         <v>46162.763589780094</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6770,7 +6770,7 @@
         <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>252</v>
@@ -6793,7 +6793,7 @@
         <v>46162.763586388886</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6823,10 +6823,10 @@
         <v>249</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6846,7 +6846,7 @@
         <v>46162.763583657405</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6876,7 +6876,7 @@
         <v>249</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>26</v>
@@ -6899,7 +6899,7 @@
         <v>46162.763580983796</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6929,10 +6929,10 @@
         <v>249</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6952,7 +6952,7 @@
         <v>46162.76357417824</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6982,10 +6982,10 @@
         <v>249</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7005,7 +7005,7 @@
         <v>46162.763573530094</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7035,10 +7035,10 @@
         <v>249</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7064,10 +7064,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I91" s="9">
         <v>46217</v>
@@ -7121,16 +7121,16 @@
         <v>46198.79656256945</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I92" s="5">
         <v>46217</v>
@@ -7174,16 +7174,16 @@
         <v>46198.79657365741</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I93" s="9">
         <v>46217</v>
@@ -7227,16 +7227,16 @@
         <v>46198.79657413195</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I94" s="5">
         <v>46217</v>
@@ -7280,16 +7280,16 @@
         <v>46198.79657465278</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I95" s="9">
         <v>46217</v>
@@ -7333,16 +7333,16 @@
         <v>46162.763785347226</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I96" s="5">
         <v>46217</v>
@@ -7363,7 +7363,7 @@
         <v>263</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>271</v>
@@ -7386,16 +7386,16 @@
         <v>46162.763782152775</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I97" s="9">
         <v>46217</v>
@@ -7416,10 +7416,10 @@
         <v>263</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7439,16 +7439,16 @@
         <v>46162.76377949074</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I98" s="5">
         <v>46217</v>
@@ -7472,7 +7472,7 @@
         <v>274</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7492,16 +7492,16 @@
         <v>46162.76377262731</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I99" s="9">
         <v>46217</v>
@@ -7522,10 +7522,10 @@
         <v>263</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7545,16 +7545,16 @@
         <v>46162.76377197917</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I100" s="5">
         <v>46217</v>
@@ -7575,10 +7575,10 @@
         <v>263</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7598,16 +7598,16 @@
         <v>46162.7637712963</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I101" s="9">
         <v>46217</v>
@@ -7628,10 +7628,10 @@
         <v>263</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7651,7 +7651,7 @@
         <v>46162.708598171295</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7704,10 +7704,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7723,7 +7723,7 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>113</v>
@@ -7765,10 +7765,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I104" s="6"/>
       <c r="J104" s="5">
@@ -7784,7 +7784,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>104</v>
@@ -7826,10 +7826,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I105" s="10"/>
       <c r="J105" s="9">
@@ -7845,7 +7845,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>122</v>
@@ -7887,10 +7887,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7906,10 +7906,10 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>291</v>
@@ -8052,7 +8052,7 @@
         <v>46162.764253263886</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8105,7 +8105,7 @@
         <v>46162.76425003472</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8158,7 +8158,7 @@
         <v>46162.764246273146</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8188,7 +8188,7 @@
         <v>296</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>302</v>
@@ -8211,7 +8211,7 @@
         <v>46162.76424304398</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8241,7 +8241,7 @@
         <v>296</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>304</v>
@@ -8264,7 +8264,7 @@
         <v>46162.764240081015</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8294,10 +8294,10 @@
         <v>296</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8317,7 +8317,7 @@
         <v>46162.76423697917</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8347,10 +8347,10 @@
         <v>296</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8370,7 +8370,7 @@
         <v>46162.76423423611</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8400,10 +8400,10 @@
         <v>296</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8423,7 +8423,7 @@
         <v>46162.76423152778</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8453,10 +8453,10 @@
         <v>296</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8476,7 +8476,7 @@
         <v>46162.764224479164</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8506,10 +8506,10 @@
         <v>296</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8529,7 +8529,7 @@
         <v>46162.76422390046</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8559,10 +8559,10 @@
         <v>296</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8645,7 +8645,7 @@
         <v>46198.79655782407</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8698,7 +8698,7 @@
         <v>46198.79657496528</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8751,7 +8751,7 @@
         <v>46198.79657011574</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8804,7 +8804,7 @@
         <v>46198.79655399306</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8857,7 +8857,7 @@
         <v>46162.76441243055</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8887,7 +8887,7 @@
         <v>312</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>320</v>
@@ -8910,7 +8910,7 @@
         <v>46198.7965582176</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8943,7 +8943,7 @@
         <v>324</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8963,7 +8963,7 @@
         <v>46198.796559062495</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8996,7 +8996,7 @@
         <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9016,7 +9016,7 @@
         <v>46198.796559594906</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9049,7 +9049,7 @@
         <v>324</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9069,7 +9069,7 @@
         <v>46198.79656293981</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9102,7 +9102,7 @@
         <v>326</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9122,7 +9122,7 @@
         <v>46198.79657047454</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9155,7 +9155,7 @@
         <v>324</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9238,7 +9238,7 @@
         <v>46198.79656021991</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9291,7 +9291,7 @@
         <v>46198.79656121528</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9344,7 +9344,7 @@
         <v>46198.7965709375</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9397,7 +9397,7 @@
         <v>46198.79655481481</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9450,7 +9450,7 @@
         <v>46162.764601250004</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9480,7 +9480,7 @@
         <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>342</v>
@@ -9503,7 +9503,7 @@
         <v>46162.76459766204</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9536,7 +9536,7 @@
         <v>344</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9556,7 +9556,7 @@
         <v>46162.76459489584</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9586,10 +9586,10 @@
         <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9609,7 +9609,7 @@
         <v>46162.76458689815</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9642,7 +9642,7 @@
         <v>344</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9662,7 +9662,7 @@
         <v>46162.76458621528</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9695,7 +9695,7 @@
         <v>344</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9715,7 +9715,7 @@
         <v>46162.76458552083</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9748,7 +9748,7 @@
         <v>344</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9831,7 +9831,7 @@
         <v>46198.79657170139</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9884,7 +9884,7 @@
         <v>46198.796572175925</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9937,7 +9937,7 @@
         <v>46198.796563564814</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9990,7 +9990,7 @@
         <v>46198.79657305556</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10043,7 +10043,7 @@
         <v>46162.76476091435</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10073,7 +10073,7 @@
         <v>350</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>360</v>
@@ -10096,7 +10096,7 @@
         <v>46162.76475773148</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10149,7 +10149,7 @@
         <v>46162.76475452546</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10182,7 +10182,7 @@
         <v>362</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10202,7 +10202,7 @@
         <v>46162.764749594906</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10235,7 +10235,7 @@
         <v>362</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10255,7 +10255,7 @@
         <v>46162.76474296296</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10308,7 +10308,7 @@
         <v>46162.764742141204</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10424,7 +10424,7 @@
         <v>46162.764935011575</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10454,7 +10454,7 @@
         <v>370</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P153" s="10" t="s">
         <v>372</v>
@@ -10477,7 +10477,7 @@
         <v>46162.76493179398</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10507,7 +10507,7 @@
         <v>370</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>372</v>
@@ -10530,7 +10530,7 @@
         <v>46162.76492869213</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10560,7 +10560,7 @@
         <v>370</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>372</v>
@@ -10583,7 +10583,7 @@
         <v>46162.764925613425</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10613,7 +10613,7 @@
         <v>370</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>376</v>
@@ -10636,7 +10636,7 @@
         <v>46162.76492271991</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10666,7 +10666,7 @@
         <v>370</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>372</v>
@@ -10689,7 +10689,7 @@
         <v>46162.764919444446</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10719,7 +10719,7 @@
         <v>370</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>26</v>
@@ -10742,7 +10742,7 @@
         <v>46162.76491637732</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10772,10 +10772,10 @@
         <v>370</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10795,7 +10795,7 @@
         <v>46162.76491366898</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10825,7 +10825,7 @@
         <v>370</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>26</v>
@@ -10848,7 +10848,7 @@
         <v>46162.764907199075</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10878,7 +10878,7 @@
         <v>370</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P161" s="10" t="s">
         <v>26</v>
@@ -10901,7 +10901,7 @@
         <v>46162.76490642361</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10931,7 +10931,7 @@
         <v>370</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>26</v>
@@ -11017,7 +11017,7 @@
         <v>46162.76513244213</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11045,7 +11045,7 @@
         <v>384</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>387</v>
@@ -11068,7 +11068,7 @@
         <v>46162.765129583335</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11096,7 +11096,7 @@
         <v>384</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P165" s="10" t="s">
         <v>387</v>
@@ -11119,7 +11119,7 @@
         <v>46162.76512658565</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11147,7 +11147,7 @@
         <v>384</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>387</v>
@@ -11170,7 +11170,7 @@
         <v>46162.76512369213</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11198,7 +11198,7 @@
         <v>384</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P167" s="10" t="s">
         <v>387</v>
@@ -11221,7 +11221,7 @@
         <v>46162.765120752316</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11249,7 +11249,7 @@
         <v>384</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>392</v>
@@ -11272,7 +11272,7 @@
         <v>46162.76511746528</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11300,7 +11300,7 @@
         <v>384</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11323,7 +11323,7 @@
         <v>46162.765109942135</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11351,10 +11351,10 @@
         <v>384</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11374,7 +11374,7 @@
         <v>46162.76510700231</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11402,10 +11402,10 @@
         <v>384</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11425,7 +11425,7 @@
         <v>46162.76510052083</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11453,10 +11453,10 @@
         <v>384</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11476,7 +11476,7 @@
         <v>46162.76510002315</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11504,10 +11504,10 @@
         <v>384</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11637,7 +11637,7 @@
         <v>46162.76536123843</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11667,7 +11667,7 @@
         <v>402</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>407</v>
@@ -11690,7 +11690,7 @@
         <v>46162.76535802083</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11720,7 +11720,7 @@
         <v>402</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>407</v>
@@ -11743,7 +11743,7 @@
         <v>46162.76535458333</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11773,7 +11773,7 @@
         <v>402</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>407</v>
@@ -11796,7 +11796,7 @@
         <v>46162.76535162037</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11826,7 +11826,7 @@
         <v>402</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>411</v>
@@ -11849,7 +11849,7 @@
         <v>46162.765348796296</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11879,7 +11879,7 @@
         <v>402</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>411</v>
@@ -11902,7 +11902,7 @@
         <v>46162.765344976855</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -11932,10 +11932,10 @@
         <v>402</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11955,7 +11955,7 @@
         <v>46162.765340763886</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -11985,7 +11985,7 @@
         <v>402</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>26</v>
@@ -12008,7 +12008,7 @@
         <v>46162.765337488425</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12038,10 +12038,10 @@
         <v>402</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12061,7 +12061,7 @@
         <v>46162.76533056713</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12091,10 +12091,10 @@
         <v>402</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12114,7 +12114,7 @@
         <v>46162.76532990741</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12144,10 +12144,10 @@
         <v>402</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12230,7 +12230,7 @@
         <v>46162.766318043985</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12260,7 +12260,7 @@
         <v>419</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>421</v>
@@ -12283,7 +12283,7 @@
         <v>46162.76631474537</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12313,7 +12313,7 @@
         <v>419</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>421</v>
@@ -12336,7 +12336,7 @@
         <v>46162.76631193287</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12366,7 +12366,7 @@
         <v>419</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P189" s="10" t="s">
         <v>424</v>
@@ -12389,7 +12389,7 @@
         <v>46162.76630898148</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12419,7 +12419,7 @@
         <v>419</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P190" s="6" t="s">
         <v>424</v>
@@ -12442,7 +12442,7 @@
         <v>46162.76630527778</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12472,7 +12472,7 @@
         <v>419</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P191" s="10" t="s">
         <v>424</v>
@@ -12495,7 +12495,7 @@
         <v>46162.76630212963</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12525,7 +12525,7 @@
         <v>419</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>26</v>
@@ -12548,7 +12548,7 @@
         <v>46162.76629917824</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12578,10 +12578,10 @@
         <v>419</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12601,7 +12601,7 @@
         <v>46162.76629561343</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12631,10 +12631,10 @@
         <v>419</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12654,7 +12654,7 @@
         <v>46162.766289004634</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12684,10 +12684,10 @@
         <v>419</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12707,7 +12707,7 @@
         <v>46162.76628835648</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12737,10 +12737,10 @@
         <v>419</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12823,7 +12823,7 @@
         <v>46162.766515462965</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12853,7 +12853,7 @@
         <v>433</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>435</v>
@@ -12876,7 +12876,7 @@
         <v>46162.76651282408</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -12906,7 +12906,7 @@
         <v>433</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P199" s="10" t="s">
         <v>435</v>
@@ -12929,7 +12929,7 @@
         <v>46162.76651023148</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -12959,7 +12959,7 @@
         <v>433</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>438</v>
@@ -12982,7 +12982,7 @@
         <v>46162.76650773148</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
@@ -13012,7 +13012,7 @@
         <v>433</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>438</v>
@@ -13035,7 +13035,7 @@
         <v>46162.76650408565</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13065,7 +13065,7 @@
         <v>433</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>441</v>
@@ -13088,7 +13088,7 @@
         <v>46162.76650106482</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13118,10 +13118,10 @@
         <v>433</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13141,7 +13141,7 @@
         <v>46162.76649841435</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13171,10 +13171,10 @@
         <v>433</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13194,7 +13194,7 @@
         <v>46162.76649456019</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13224,10 +13224,10 @@
         <v>433</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13247,7 +13247,7 @@
         <v>46162.766489050926</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13277,10 +13277,10 @@
         <v>433</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13300,7 +13300,7 @@
         <v>46162.76648839121</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13330,10 +13330,10 @@
         <v>433</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13416,7 +13416,7 @@
         <v>46162.76670017361</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13446,7 +13446,7 @@
         <v>448</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>448</v>
@@ -13469,7 +13469,7 @@
         <v>46162.76669680556</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13499,7 +13499,7 @@
         <v>448</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>448</v>
@@ -13522,7 +13522,7 @@
         <v>46162.76669409723</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13552,7 +13552,7 @@
         <v>448</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>448</v>
@@ -13575,7 +13575,7 @@
         <v>46162.766691377314</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13605,7 +13605,7 @@
         <v>448</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>448</v>
@@ -13628,7 +13628,7 @@
         <v>46162.766687662035</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13658,7 +13658,7 @@
         <v>448</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P213" s="10" t="s">
         <v>448</v>
@@ -13681,7 +13681,7 @@
         <v>46162.76668472222</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13711,7 +13711,7 @@
         <v>448</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>26</v>
@@ -13734,7 +13734,7 @@
         <v>46162.76668173611</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13764,7 +13764,7 @@
         <v>448</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P215" s="10" t="s">
         <v>26</v>
@@ -13787,7 +13787,7 @@
         <v>46162.76667282407</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13817,7 +13817,7 @@
         <v>448</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>26</v>
@@ -13840,7 +13840,7 @@
         <v>46162.76667212963</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13870,7 +13870,7 @@
         <v>448</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>26</v>
@@ -13893,7 +13893,7 @@
         <v>46162.76667141204</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
@@ -13923,7 +13923,7 @@
         <v>448</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>26</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -670,19 +670,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1214977075952529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977075952529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
     <t>1214977177463236</t>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46203.17051119213</v>
+        <v>46204.18876318287</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5498,8 +5498,8 @@
       <c r="R62" s="5">
         <v>46203</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>209</v>
+      <c r="S62" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5510,17 +5510,17 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B63" s="9">
         <v>46162.68160836806</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46197.17514756945</v>
+        <v>46204.169723969906</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5548,10 +5548,10 @@
         <v>202</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>213</v>
       </c>
       <c r="Q63" s="9">
         <v>46204</v>
@@ -5560,7 +5560,7 @@
         <v>46204</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46203.170507187504</v>
+        <v>46204.188763275466</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5620,8 +5620,8 @@
       <c r="R64" s="5">
         <v>46203</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>209</v>
+      <c r="S64" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.175148090275</v>
+        <v>46204.1697262963</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>218</v>
@@ -5682,7 +5682,7 @@
         <v>46204</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.17051256944</v>
+        <v>46204.18876412037</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5742,8 +5742,8 @@
       <c r="R66" s="5">
         <v>46203</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>209</v>
+      <c r="S66" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46197.17514795139</v>
+        <v>46204.16973459491</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>222</v>
@@ -5804,7 +5804,7 @@
         <v>46204</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5914,7 +5914,7 @@
         <v>46209</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -682,61 +682,61 @@
     <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
+    <t>1214977177463236</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214977177463256</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977534119621</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214977534119636</t>
+  </si>
+  <si>
+    <t>1214977521366438</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1214977521366448</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977177463236</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214977177463256</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977534119621</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214977534119636</t>
-  </si>
-  <si>
-    <t>1214977521366438</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1214977521366448</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
     <t>1214977534136624</t>
@@ -2074,13 +2074,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.68116403936</v>
+        <v>46162.514497372686</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87789798611</v>
+        <v>46175.711231319445</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.877909409726</v>
+        <v>46175.711242743055</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2127,13 +2127,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.68127501158</v>
+        <v>46162.51460834491</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87787195602</v>
+        <v>46175.71120528935</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.877898136576</v>
+        <v>46175.711231469904</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2192,13 +2192,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.681278564814</v>
+        <v>46162.51461189815</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87787261574</v>
+        <v>46175.711205949076</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87789836805</v>
+        <v>46175.71123170139</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2257,13 +2257,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.6812825</v>
+        <v>46162.51461583334</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.87787303241</v>
+        <v>46175.71120636574</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87789847222</v>
+        <v>46175.71123180556</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2322,13 +2322,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.68128590278</v>
+        <v>46162.51461923611</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87787347222</v>
+        <v>46175.71120680556</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87789923611</v>
+        <v>46175.71123256945</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2387,13 +2387,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.68128952546</v>
+        <v>46162.5146228588</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.877874224534</v>
+        <v>46175.71120755787</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.877899837964</v>
+        <v>46175.7112331713</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2452,13 +2452,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.68116798611</v>
+        <v>46162.51450131944</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.68205895834</v>
+        <v>46198.515392291665</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.68207692129</v>
+        <v>46198.51541025463</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2505,13 +2505,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.68129303241</v>
+        <v>46162.51462636574</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.66700505787</v>
+        <v>46197.500338391204</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.77703842593</v>
+        <v>46197.61037175926</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>48</v>
@@ -2570,13 +2570,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.68129826389</v>
+        <v>46162.51463159722</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.66976853009</v>
+        <v>46197.503101863425</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.77703841435</v>
+        <v>46197.61037174768</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2635,13 +2635,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.68130347222</v>
+        <v>46162.51463680556</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.671156689816</v>
+        <v>46197.504490023144</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.777039189816</v>
+        <v>46197.61037252315</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2700,11 +2700,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.68117188658</v>
+        <v>46162.51450521991</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.68510511574</v>
+        <v>46198.51843844907</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2747,13 +2747,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.681316030095</v>
+        <v>46162.514649363424</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.68228026621</v>
+        <v>46198.515613599535</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.6822819213</v>
+        <v>46198.515615254626</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2812,13 +2812,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.68132108796</v>
+        <v>46162.51465442129</v>
       </c>
       <c r="C16" s="5">
-        <v>46198.68509829861</v>
+        <v>46198.51843163194</v>
       </c>
       <c r="D16" s="5">
-        <v>46198.685114224536</v>
+        <v>46198.51844755787</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2877,13 +2877,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.68132700231</v>
+        <v>46162.51466033565</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.587876516205</v>
+        <v>46197.42120984953</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.66978645833</v>
+        <v>46197.50311979167</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2942,11 +2942,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.68133263889</v>
+        <v>46162.51466597222</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.7965890162</v>
+        <v>46198.62992234954</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3005,11 +3005,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.68133762731</v>
+        <v>46162.51467096065</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.79658804398</v>
+        <v>46198.629921377316</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3068,11 +3068,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.68134119213</v>
+        <v>46162.51467452546</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.79658851852</v>
+        <v>46198.629921851854</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3131,11 +3131,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.6813446875</v>
+        <v>46162.51467802083</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.79658900463</v>
+        <v>46198.62992233796</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3194,11 +3194,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.68117578704</v>
+        <v>46162.514509120374</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.685312800924</v>
+        <v>46198.51864613426</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3241,13 +3241,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.681348645834</v>
+        <v>46162.51468197917</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.68530165509</v>
+        <v>46198.518634988424</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.68532041667</v>
+        <v>46198.51865375</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3306,13 +3306,13 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.68135300926</v>
+        <v>46162.51468634259</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.68525414352</v>
+        <v>46198.51858747685</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.68525572917</v>
+        <v>46198.5185890625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3367,13 +3367,13 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.68135747685</v>
+        <v>46162.51469081019</v>
       </c>
       <c r="C25" s="9">
-        <v>46198.68528871528</v>
+        <v>46198.51862204861</v>
       </c>
       <c r="D25" s="9">
-        <v>46198.68529017361</v>
+        <v>46198.51862350694</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3428,11 +3428,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.68136241898</v>
+        <v>46162.51469575231</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46192.853174930555</v>
+        <v>46192.68650826389</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3491,11 +3491,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.6813671412</v>
+        <v>46162.51470047454</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.58788623843</v>
+        <v>46197.421219571756</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3550,11 +3550,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.6813721875</v>
+        <v>46162.514705520836</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.87699585648</v>
+        <v>46169.71032918982</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3609,11 +3609,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.68137706019</v>
+        <v>46162.514710393516</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46198.68314474537</v>
+        <v>46198.5164780787</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3672,13 +3672,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.681382083334</v>
+        <v>46162.51471541666</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.68232337963</v>
+        <v>46198.51565671296</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.682324814814</v>
+        <v>46198.51565814815</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3733,11 +3733,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.681387523146</v>
+        <v>46162.51472085648</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46198.68233005787</v>
+        <v>46198.515663391205</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3792,13 +3792,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.68139224537</v>
+        <v>46162.5147255787</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.683139166664</v>
+        <v>46198.5164725</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.683140567126</v>
+        <v>46198.51647390046</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3853,11 +3853,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.68139699074</v>
+        <v>46162.514730324074</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46203.20693458333</v>
+        <v>46203.040267916665</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3916,11 +3916,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.68140180556</v>
+        <v>46162.51473513889</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.169341932866</v>
+        <v>46191.00267526621</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3975,11 +3975,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.681406793985</v>
+        <v>46162.51474012731</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.87710333333</v>
+        <v>46169.71043666667</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -4030,11 +4030,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.68146234954</v>
+        <v>46162.51479568287</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46203.20693486111</v>
+        <v>46203.04026819444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -4093,11 +4093,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.68146784722</v>
+        <v>46162.51480118056</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46189.16936783565</v>
+        <v>46189.00270116898</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4146,11 +4146,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.68147298611</v>
+        <v>46162.51480631944</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46202.16933497685</v>
+        <v>46202.00266831019</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4199,11 +4199,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.681477175924</v>
+        <v>46162.51481050926</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.876735</v>
+        <v>46169.710068333334</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4262,11 +4262,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.68148049769</v>
+        <v>46162.51481383102</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.16913447916</v>
+        <v>46198.002467812505</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4315,11 +4315,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.681484872686</v>
+        <v>46162.51481820602</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87719863426</v>
+        <v>46169.71053196759</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4368,11 +4368,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.68148924768</v>
+        <v>46162.51482258102</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.877211388884</v>
+        <v>46169.71054472223</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4421,11 +4421,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.68149232639</v>
+        <v>46162.514825659724</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46203.20693501158</v>
+        <v>46203.04026834491</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4484,11 +4484,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.68149587963</v>
+        <v>46162.51482921296</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.1693375926</v>
+        <v>46191.002670925925</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4537,11 +4537,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.6815003125</v>
+        <v>46162.51483364584</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46202.169333576385</v>
+        <v>46202.00266690972</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4590,11 +4590,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.68117938658</v>
+        <v>46162.51451271991</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.796516539354</v>
+        <v>46198.62984987268</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4639,13 +4639,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.68150506944</v>
+        <v>46162.51483840278</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.70288993056</v>
+        <v>46197.53622326389</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.703074074074</v>
+        <v>46197.5364074074</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4704,13 +4704,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.68151027778</v>
+        <v>46162.51484361111</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.796495462964</v>
+        <v>46198.6298287963</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.796512534725</v>
+        <v>46198.629845868054</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4769,13 +4769,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.6815165625</v>
+        <v>46162.51484989583</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.79653876157</v>
+        <v>46198.62987209491</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.796557442125</v>
+        <v>46198.62989077547</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4834,11 +4834,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.68153015046</v>
+        <v>46162.5148634838</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46162.76230295139</v>
+        <v>46162.59563628472</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4895,11 +4895,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.68153354166</v>
+        <v>46162.514866875004</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46162.76229798611</v>
+        <v>46162.59563131945</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4946,11 +4946,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.68153736111</v>
+        <v>46162.514870694446</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46162.76229449074</v>
+        <v>46162.59562782408</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4997,11 +4997,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.68154143519</v>
+        <v>46162.514874768516</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46162.76229145833</v>
+        <v>46162.59562479166</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5048,11 +5048,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.68154440972</v>
+        <v>46162.51487774306</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.76228877315</v>
+        <v>46162.595622106484</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5099,11 +5099,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.68154740741</v>
+        <v>46162.51488074074</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46162.76228596065</v>
+        <v>46162.59561929398</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -5150,11 +5150,11 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.68155047453</v>
+        <v>46162.514883807875</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.762282870375</v>
+        <v>46162.595616203704</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>190</v>
@@ -5201,11 +5201,11 @@
         <v>197</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.681552766204</v>
+        <v>46162.51488609954</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46162.76227917824</v>
+        <v>46162.59561251158</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>190</v>
@@ -5252,11 +5252,11 @@
         <v>198</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.68155516204</v>
+        <v>46162.51488849537</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.76227634259</v>
+        <v>46162.595609675926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>190</v>
@@ -5303,11 +5303,11 @@
         <v>199</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.6815574537</v>
+        <v>46162.51489078703</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46162.7622690162</v>
+        <v>46162.59560234954</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>190</v>
@@ -5354,11 +5354,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.68155952546</v>
+        <v>46162.514892858795</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46162.762268391205</v>
+        <v>46162.59560172453</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>190</v>
@@ -5405,11 +5405,11 @@
         <v>201</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.681598807874</v>
+        <v>46162.5149321412</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46162.707360960645</v>
+        <v>46162.54069429398</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>202</v>
@@ -5452,11 +5452,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.681602743054</v>
+        <v>46162.51493607639</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46204.18876318287</v>
+        <v>46204.0220965162</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5513,11 +5513,11 @@
         <v>209</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.68160836806</v>
+        <v>46162.51494170139</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46204.169723969906</v>
+        <v>46205.0072115625</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>210</v>
@@ -5559,8 +5559,8 @@
       <c r="R63" s="9">
         <v>46204</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>213</v>
+      <c r="S63" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5571,17 +5571,17 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.681615208334</v>
+        <v>46162.51494854166</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46204.188763275466</v>
+        <v>46204.022096608795</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5612,7 +5612,7 @@
         <v>144</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46203</v>
@@ -5632,17 +5632,17 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.68162069445</v>
+        <v>46162.51495402778</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46204.1697262963</v>
+        <v>46205.007211805554</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5670,10 +5670,10 @@
         <v>202</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q65" s="9">
         <v>46204</v>
@@ -5681,8 +5681,8 @@
       <c r="R65" s="9">
         <v>46204</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>213</v>
+      <c r="S65" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5693,17 +5693,17 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.681625983794</v>
+        <v>46162.51495931713</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46204.18876412037</v>
+        <v>46204.02209745371</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5734,7 +5734,7 @@
         <v>166</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q66" s="5">
         <v>46203</v>
@@ -5754,17 +5754,17 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.68163075231</v>
+        <v>46162.51496408565</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46204.16973459491</v>
+        <v>46205.007211759264</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5792,10 +5792,10 @@
         <v>202</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="9">
         <v>46204</v>
@@ -5803,8 +5803,8 @@
       <c r="R67" s="9">
         <v>46204</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>213</v>
+      <c r="S67" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5815,17 +5815,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.68163611111</v>
+        <v>46162.51496944444</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.763323391206</v>
+        <v>46162.596656724534</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5849,7 +5849,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5862,26 +5862,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.6816390162</v>
+        <v>46162.51497234954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46202.17884375</v>
+        <v>46202.012177083336</v>
       </c>
       <c r="E69" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="10" t="s">
+      <c r="H69" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I69" s="9">
         <v>46205</v>
@@ -5899,13 +5899,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q69" s="9">
         <v>46205</v>
@@ -5914,7 +5914,7 @@
         <v>46209</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -5928,11 +5928,11 @@
         <v>232</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.68164390046</v>
+        <v>46162.5149772338</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.763318530095</v>
+        <v>46162.59665186342</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5941,10 +5941,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I70" s="5">
         <v>46205</v>
@@ -5962,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>233</v>
@@ -5981,11 +5981,11 @@
         <v>235</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.681651203704</v>
+        <v>46162.51498453703</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.76331560186</v>
+        <v>46162.596648935185</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -5994,10 +5994,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6015,7 +6015,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>236</v>
@@ -6034,11 +6034,11 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.68165733796</v>
+        <v>46162.5149906713</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.76331271991</v>
+        <v>46162.596646053236</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6047,10 +6047,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I72" s="5">
         <v>46205</v>
@@ -6068,7 +6068,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>238</v>
@@ -6087,11 +6087,11 @@
         <v>240</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.68166336806</v>
+        <v>46162.514996701386</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.763309710645</v>
+        <v>46162.59664304398</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6100,10 +6100,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6121,7 +6121,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>236</v>
@@ -6140,11 +6140,11 @@
         <v>241</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.68166935185</v>
+        <v>46162.515002685184</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.763306759254</v>
+        <v>46162.5966400926</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6153,10 +6153,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I74" s="5">
         <v>46205</v>
@@ -6174,7 +6174,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>236</v>
@@ -6193,11 +6193,11 @@
         <v>242</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.68167571759</v>
+        <v>46162.51500905093</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.76330359954</v>
+        <v>46162.59663693287</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6206,10 +6206,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6227,7 +6227,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>243</v>
@@ -6246,11 +6246,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.68168109954</v>
+        <v>46162.515014432865</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.7633006713</v>
+        <v>46162.59663400463</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6259,10 +6259,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I76" s="5">
         <v>46205</v>
@@ -6280,7 +6280,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>233</v>
@@ -6299,11 +6299,11 @@
         <v>245</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.68168630787</v>
+        <v>46162.5150196412</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.763297384256</v>
+        <v>46162.59663071759</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6312,10 +6312,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I77" s="9">
         <v>46205</v>
@@ -6333,7 +6333,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>236</v>
@@ -6352,11 +6352,11 @@
         <v>246</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.68169194444</v>
+        <v>46162.51502527778</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.763290891206</v>
+        <v>46162.596624224534</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>190</v>
@@ -6365,10 +6365,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I78" s="5">
         <v>46205</v>
@@ -6386,7 +6386,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>236</v>
@@ -6405,11 +6405,11 @@
         <v>247</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.681698229164</v>
+        <v>46162.5150315625</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.763290243056</v>
+        <v>46162.59662357639</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>190</v>
@@ -6418,10 +6418,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I79" s="9">
         <v>46205</v>
@@ -6439,7 +6439,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>236</v>
@@ -6458,11 +6458,11 @@
         <v>248</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.68171431713</v>
+        <v>46162.515047650464</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.76361657407</v>
+        <v>46162.59694990741</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>249</v>
@@ -6471,10 +6471,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I80" s="5">
         <v>46210</v>
@@ -6492,13 +6492,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q80" s="5">
         <v>46210</v>
@@ -6521,11 +6521,11 @@
         <v>250</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.681718935186</v>
+        <v>46162.515052268514</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.79655543981</v>
+        <v>46198.62988877315</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>190</v>
@@ -6534,10 +6534,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I81" s="9">
         <v>46210</v>
@@ -6574,11 +6574,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.68172515046</v>
+        <v>46162.5150584838</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.79656188657</v>
+        <v>46198.62989521991</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>190</v>
@@ -6587,10 +6587,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I82" s="5">
         <v>46210</v>
@@ -6627,11 +6627,11 @@
         <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.68173074074</v>
+        <v>46162.515064074076</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.79655649306</v>
+        <v>46198.62988982639</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>190</v>
@@ -6640,10 +6640,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I83" s="9">
         <v>46210</v>
@@ -6680,11 +6680,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.68173619213</v>
+        <v>46162.51506952546</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.796557222224</v>
+        <v>46198.62989055556</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>190</v>
@@ -6693,10 +6693,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I84" s="5">
         <v>46210</v>
@@ -6733,11 +6733,11 @@
         <v>256</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.681741747685</v>
+        <v>46162.51507508101</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46162.763589780094</v>
+        <v>46162.59692311342</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6746,10 +6746,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I85" s="9">
         <v>46210</v>
@@ -6786,11 +6786,11 @@
         <v>257</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.68178277778</v>
+        <v>46162.51511611111</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46162.763586388886</v>
+        <v>46162.59691972222</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6799,10 +6799,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I86" s="5">
         <v>46210</v>
@@ -6839,11 +6839,11 @@
         <v>258</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.68178671296</v>
+        <v>46162.5151200463</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46162.763583657405</v>
+        <v>46162.59691699074</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6852,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I87" s="9">
         <v>46210</v>
@@ -6892,11 +6892,11 @@
         <v>259</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.68178976852</v>
+        <v>46162.51512310185</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46162.763580983796</v>
+        <v>46162.596914317124</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6905,10 +6905,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I88" s="5">
         <v>46210</v>
@@ -6945,11 +6945,11 @@
         <v>260</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.68179300926</v>
+        <v>46162.515126342594</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.76357417824</v>
+        <v>46162.59690751157</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>190</v>
@@ -6958,10 +6958,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I89" s="9">
         <v>46210</v>
@@ -6998,11 +6998,11 @@
         <v>261</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.68179625</v>
+        <v>46162.515129583335</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.763573530094</v>
+        <v>46162.59690686343</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -7011,10 +7011,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I90" s="5">
         <v>46210</v>
@@ -7051,11 +7051,11 @@
         <v>262</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.681806875</v>
+        <v>46162.51514020833</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.763839050924</v>
+        <v>46162.59717238426</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>263</v>
@@ -7085,13 +7085,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q91" s="9">
         <v>46217</v>
@@ -7114,11 +7114,11 @@
         <v>264</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.68181175926</v>
+        <v>46162.51514509259</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.79656256945</v>
+        <v>46198.62989590278</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -7167,11 +7167,11 @@
         <v>266</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.68181751158</v>
+        <v>46162.515150844905</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46198.79657365741</v>
+        <v>46198.62990699074</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -7220,11 +7220,11 @@
         <v>267</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.681823032406</v>
+        <v>46162.51515636574</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.79657413195</v>
+        <v>46198.62990746528</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>190</v>
@@ -7273,11 +7273,11 @@
         <v>269</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.681828368055</v>
+        <v>46162.51516170139</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.79657465278</v>
+        <v>46198.62990798611</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7326,11 +7326,11 @@
         <v>270</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.68183400463</v>
+        <v>46162.51516733796</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.763785347226</v>
+        <v>46162.597118680555</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7379,11 +7379,11 @@
         <v>272</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.6818390625</v>
+        <v>46162.51517239583</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.763782152775</v>
+        <v>46162.59711548611</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7432,11 +7432,11 @@
         <v>273</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.68184208333</v>
+        <v>46162.515175416665</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46162.76377949074</v>
+        <v>46162.59711282408</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7485,11 +7485,11 @@
         <v>275</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.6818458912</v>
+        <v>46162.51517922454</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.76377262731</v>
+        <v>46162.59710596065</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7538,11 +7538,11 @@
         <v>276</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.681849375</v>
+        <v>46162.51518270833</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46162.76377197917</v>
+        <v>46162.597105312496</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7591,11 +7591,11 @@
         <v>277</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.68185259259</v>
+        <v>46162.51518592593</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46162.7637712963</v>
+        <v>46162.59710462963</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7644,11 +7644,11 @@
         <v>278</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.681862557874</v>
+        <v>46162.5151958912</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.708598171295</v>
+        <v>46162.54193150463</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>202</v>
@@ -7691,11 +7691,11 @@
         <v>280</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.68186600694</v>
+        <v>46162.515199340276</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.76398071759</v>
+        <v>46162.59731405093</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>281</v>
@@ -7752,11 +7752,11 @@
         <v>283</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.681872870366</v>
+        <v>46162.51520620371</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46198.685305949075</v>
+        <v>46198.51863928241</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>284</v>
@@ -7813,11 +7813,11 @@
         <v>286</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.681879930555</v>
+        <v>46162.51521326389</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46197.17676240741</v>
+        <v>46197.01009574074</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>287</v>
@@ -7874,11 +7874,11 @@
         <v>289</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.681886412036</v>
+        <v>46162.51521974537</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.763970266205</v>
+        <v>46162.59730359954</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>290</v>
@@ -7935,11 +7935,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.68189086806</v>
+        <v>46162.51522420139</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.710864479166</v>
+        <v>46162.5441978125</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>293</v>
@@ -7982,11 +7982,11 @@
         <v>295</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.681893761575</v>
+        <v>46162.515227094904</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.76425648148</v>
+        <v>46162.59758981482</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>296</v>
@@ -8045,11 +8045,11 @@
         <v>298</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.68190694445</v>
+        <v>46162.515240277775</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.764253263886</v>
+        <v>46162.59758659722</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>190</v>
@@ -8098,11 +8098,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.68191104167</v>
+        <v>46162.515244375</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.76425003472</v>
+        <v>46162.59758336806</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8151,11 +8151,11 @@
         <v>301</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.68191516204</v>
+        <v>46162.51524849537</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46162.764246273146</v>
+        <v>46162.59757960648</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8204,11 +8204,11 @@
         <v>303</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.68191947917</v>
+        <v>46162.5152528125</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.76424304398</v>
+        <v>46162.59757637732</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8257,11 +8257,11 @@
         <v>305</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.68192371528</v>
+        <v>46162.51525704861</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46162.764240081015</v>
+        <v>46162.59757341435</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8310,11 +8310,11 @@
         <v>306</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.68192716435</v>
+        <v>46162.51526049769</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.76423697917</v>
+        <v>46162.5975703125</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8363,11 +8363,11 @@
         <v>307</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.6819303588</v>
+        <v>46162.51526369213</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.76423423611</v>
+        <v>46162.59756756945</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>190</v>
@@ -8416,11 +8416,11 @@
         <v>308</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.6819334375</v>
+        <v>46162.51526677083</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.76423152778</v>
+        <v>46162.59756486111</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8469,11 +8469,11 @@
         <v>309</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.68193662037</v>
+        <v>46162.5152699537</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.764224479164</v>
+        <v>46162.5975578125</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8522,11 +8522,11 @@
         <v>310</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.68193976852</v>
+        <v>46162.51527310185</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.76422390046</v>
+        <v>46162.59755723379</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8575,11 +8575,11 @@
         <v>311</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.68199361111</v>
+        <v>46162.51532694444</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.76445266204</v>
+        <v>46162.59778599537</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>312</v>
@@ -8612,7 +8612,7 @@
         <v>293</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>293</v>
@@ -8638,11 +8638,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.68199872685</v>
+        <v>46162.51533206018</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46198.79655782407</v>
+        <v>46198.62989115741</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8691,11 +8691,11 @@
         <v>316</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.6820043287</v>
+        <v>46162.51533766204</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46198.79657496528</v>
+        <v>46198.62990829861</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8744,11 +8744,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.68200945602</v>
+        <v>46162.51534278935</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46198.79657011574</v>
+        <v>46198.62990344907</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8797,11 +8797,11 @@
         <v>321</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.68201590278</v>
+        <v>46162.51534923611</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46198.79655399306</v>
+        <v>46198.62988732639</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8850,11 +8850,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.682022175926</v>
+        <v>46162.515355509255</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.76441243055</v>
+        <v>46162.59774576389</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8903,11 +8903,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.68202664352</v>
+        <v>46162.51535997685</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46198.7965582176</v>
+        <v>46198.629891550925</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>190</v>
@@ -8956,11 +8956,11 @@
         <v>325</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.682031874996</v>
+        <v>46162.51536520833</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46198.796559062495</v>
+        <v>46198.62989239584</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -9009,11 +9009,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.682037129634</v>
+        <v>46162.51537046296</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46198.796559594906</v>
+        <v>46198.62989292824</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -9062,11 +9062,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.68204233796</v>
+        <v>46162.5153756713</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46198.79656293981</v>
+        <v>46198.62989627315</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -9115,11 +9115,11 @@
         <v>329</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.68204753472</v>
+        <v>46162.515380868055</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46198.79657047454</v>
+        <v>46198.62990380787</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -9168,11 +9168,11 @@
         <v>330</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.68206118056</v>
+        <v>46162.51539451389</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46162.76461746528</v>
+        <v>46162.59795079861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>331</v>
@@ -9205,7 +9205,7 @@
         <v>293</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>293</v>
@@ -9231,11 +9231,11 @@
         <v>332</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.68206542824</v>
+        <v>46162.51539876158</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.79656021991</v>
+        <v>46198.62989355324</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9284,11 +9284,11 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.68207142361</v>
+        <v>46162.515404756945</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.79656121528</v>
+        <v>46198.62989454861</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9337,11 +9337,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.682082997686</v>
+        <v>46162.51541633102</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.7965709375</v>
+        <v>46198.629904270834</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9390,11 +9390,11 @@
         <v>338</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.682089317124</v>
+        <v>46162.51542265047</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.79655481481</v>
+        <v>46198.62988814815</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9443,11 +9443,11 @@
         <v>341</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.68209565972</v>
+        <v>46162.51542899305</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46162.764601250004</v>
+        <v>46162.59793458333</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>190</v>
@@ -9496,11 +9496,11 @@
         <v>343</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.68209994213</v>
+        <v>46162.51543327546</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46162.76459766204</v>
+        <v>46162.59793099537</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9549,11 +9549,11 @@
         <v>345</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.682104189815</v>
+        <v>46162.51543752315</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46162.76459489584</v>
+        <v>46162.59792822917</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>190</v>
@@ -9602,11 +9602,11 @@
         <v>346</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.68210733796</v>
+        <v>46162.5154406713</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46162.76458689815</v>
+        <v>46162.59792023148</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9655,11 +9655,11 @@
         <v>347</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.68211155092</v>
+        <v>46162.51544488426</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46162.76458621528</v>
+        <v>46162.597919548614</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>190</v>
@@ -9708,11 +9708,11 @@
         <v>348</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.68211587963</v>
+        <v>46162.515449212966</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.76458552083</v>
+        <v>46162.59791885417</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9761,11 +9761,11 @@
         <v>349</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.68212817129</v>
+        <v>46162.515461504634</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.76477166667</v>
+        <v>46162.598105</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>350</v>
@@ -9798,7 +9798,7 @@
         <v>293</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>293</v>
@@ -9824,11 +9824,11 @@
         <v>351</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.68213233796</v>
+        <v>46162.5154656713</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.79657170139</v>
+        <v>46198.62990503472</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9877,11 +9877,11 @@
         <v>354</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.682137881944</v>
+        <v>46162.51547121527</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.796572175925</v>
+        <v>46198.62990550926</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -9930,11 +9930,11 @@
         <v>355</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.682143275466</v>
+        <v>46162.515476608794</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.796563564814</v>
+        <v>46198.62989689814</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9983,11 +9983,11 @@
         <v>357</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.68214959491</v>
+        <v>46162.51548292824</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46198.79657305556</v>
+        <v>46198.62990638889</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10036,11 +10036,11 @@
         <v>359</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.6821980324</v>
+        <v>46162.515531365745</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46162.76476091435</v>
+        <v>46162.59809424769</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10089,11 +10089,11 @@
         <v>361</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.68220454861</v>
+        <v>46162.51553788195</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.76475773148</v>
+        <v>46162.598091064814</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>190</v>
@@ -10142,11 +10142,11 @@
         <v>364</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.6822112963</v>
+        <v>46162.51554462963</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.76475452546</v>
+        <v>46162.5980878588</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -10195,11 +10195,11 @@
         <v>365</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.68221605324</v>
+        <v>46162.515549386575</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.764749594906</v>
+        <v>46162.59808292824</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>190</v>
@@ -10248,11 +10248,11 @@
         <v>366</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.68222200232</v>
+        <v>46162.515555335645</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.76474296296</v>
+        <v>46162.5980762963</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>190</v>
@@ -10301,11 +10301,11 @@
         <v>368</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.68222814814</v>
+        <v>46162.51556148149</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.764742141204</v>
+        <v>46162.59807547454</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>190</v>
@@ -10354,11 +10354,11 @@
         <v>369</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.68224497685</v>
+        <v>46162.51557831018</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.76494858797</v>
+        <v>46162.598281921295</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>370</v>
@@ -10391,7 +10391,7 @@
         <v>293</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>293</v>
@@ -10417,11 +10417,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.68224997685</v>
+        <v>46162.51558331019</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.764935011575</v>
+        <v>46162.59826834491</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>190</v>
@@ -10470,11 +10470,11 @@
         <v>373</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.682255844906</v>
+        <v>46162.51558917824</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.76493179398</v>
+        <v>46162.598265127315</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>190</v>
@@ -10523,11 +10523,11 @@
         <v>374</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.682261354166</v>
+        <v>46162.5155946875</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.76492869213</v>
+        <v>46162.598262025465</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>190</v>
@@ -10576,11 +10576,11 @@
         <v>375</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.68226693287</v>
+        <v>46162.515600266204</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46162.764925613425</v>
+        <v>46162.59825894676</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10629,11 +10629,11 @@
         <v>377</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.68227229167</v>
+        <v>46162.515605625</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46162.76492271991</v>
+        <v>46162.59825605324</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10682,11 +10682,11 @@
         <v>378</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.68227762732</v>
+        <v>46162.51561096065</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46162.764919444446</v>
+        <v>46162.59825277778</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10735,11 +10735,11 @@
         <v>379</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.68228032408</v>
+        <v>46162.51561365741</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46162.76491637732</v>
+        <v>46162.598249710645</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10788,11 +10788,11 @@
         <v>380</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.68228446759</v>
+        <v>46162.51561780093</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.76491366898</v>
+        <v>46162.598247002315</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>190</v>
@@ -10841,11 +10841,11 @@
         <v>381</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.68228719907</v>
+        <v>46162.5156205324</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.764907199075</v>
+        <v>46162.5982405324</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>190</v>
@@ -10894,11 +10894,11 @@
         <v>382</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.68229016203</v>
+        <v>46162.515623495376</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.76490642361</v>
+        <v>46162.598239756946</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>190</v>
@@ -10947,11 +10947,11 @@
         <v>383</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.68230002315</v>
+        <v>46162.51563335648</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.7651559838</v>
+        <v>46162.598489317126</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>384</v>
@@ -10984,7 +10984,7 @@
         <v>293</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P163" s="10" t="s">
         <v>385</v>
@@ -11010,11 +11010,11 @@
         <v>386</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.682309502314</v>
+        <v>46162.51564283565</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.76513244213</v>
+        <v>46162.59846577546</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>190</v>
@@ -11061,11 +11061,11 @@
         <v>388</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.68231375</v>
+        <v>46162.51564708333</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.765129583335</v>
+        <v>46162.59846291666</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>190</v>
@@ -11112,11 +11112,11 @@
         <v>389</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.682318101855</v>
+        <v>46162.515651435184</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.76512658565</v>
+        <v>46162.59845991898</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>190</v>
@@ -11163,11 +11163,11 @@
         <v>390</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.682322430555</v>
+        <v>46162.515655763884</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.76512369213</v>
+        <v>46162.598457025466</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>190</v>
@@ -11214,11 +11214,11 @@
         <v>391</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.682326759255</v>
+        <v>46162.51566009259</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.765120752316</v>
+        <v>46162.598454085644</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>190</v>
@@ -11265,11 +11265,11 @@
         <v>393</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.68236239583</v>
+        <v>46162.51569572916</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.76511746528</v>
+        <v>46162.598450798614</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11316,11 +11316,11 @@
         <v>394</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.682365960645</v>
+        <v>46162.51569929398</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.765109942135</v>
+        <v>46162.59844327546</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11367,11 +11367,11 @@
         <v>395</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.68236944445</v>
+        <v>46162.515702777775</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.76510700231</v>
+        <v>46162.59844033565</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11418,11 +11418,11 @@
         <v>396</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.68237259259</v>
+        <v>46162.51570592592</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.76510052083</v>
+        <v>46162.59843385417</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11469,11 +11469,11 @@
         <v>397</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.682375902776</v>
+        <v>46162.51570923611</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.76510002315</v>
+        <v>46162.598433356485</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>190</v>
@@ -11520,11 +11520,11 @@
         <v>398</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.682386099536</v>
+        <v>46162.51571943287</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.711784837964</v>
+        <v>46162.5451181713</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>399</v>
@@ -11567,11 +11567,11 @@
         <v>401</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.68238924768</v>
+        <v>46162.51572258102</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.76537538195</v>
+        <v>46162.598708715275</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>402</v>
@@ -11630,11 +11630,11 @@
         <v>406</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.682394664356</v>
+        <v>46162.515727997685</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.76536123843</v>
+        <v>46162.59869457176</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>190</v>
@@ -11683,11 +11683,11 @@
         <v>408</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.68239902778</v>
+        <v>46162.51573236111</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.76535802083</v>
+        <v>46162.59869135417</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>190</v>
@@ -11736,11 +11736,11 @@
         <v>409</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.682403321756</v>
+        <v>46162.51573665509</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.76535458333</v>
+        <v>46162.59868791667</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>190</v>
@@ -11789,11 +11789,11 @@
         <v>410</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.68240755787</v>
+        <v>46162.515740891205</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.76535162037</v>
+        <v>46162.5986849537</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>190</v>
@@ -11842,11 +11842,11 @@
         <v>412</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.68241208333</v>
+        <v>46162.51574541666</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.765348796296</v>
+        <v>46162.598682129625</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>190</v>
@@ -11895,11 +11895,11 @@
         <v>413</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.682416400465</v>
+        <v>46162.51574973379</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.765344976855</v>
+        <v>46162.59867831018</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>190</v>
@@ -11948,11 +11948,11 @@
         <v>414</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.68241952546</v>
+        <v>46162.515752858795</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.765340763886</v>
+        <v>46162.59867409722</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12001,11 +12001,11 @@
         <v>415</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.6824222338</v>
+        <v>46162.51575556713</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.765337488425</v>
+        <v>46162.59867082176</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12054,11 +12054,11 @@
         <v>416</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.68242513889</v>
+        <v>46162.51575847222</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.76533056713</v>
+        <v>46162.59866390046</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12107,11 +12107,11 @@
         <v>417</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.682428125</v>
+        <v>46162.51576145833</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.76532990741</v>
+        <v>46162.598663240744</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12160,11 +12160,11 @@
         <v>418</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.68243688658</v>
+        <v>46162.51577021991</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.76634032407</v>
+        <v>46162.59967365741</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>419</v>
@@ -12197,7 +12197,7 @@
         <v>399</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>399</v>
@@ -12223,11 +12223,11 @@
         <v>420</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.68244069444</v>
+        <v>46162.51577402778</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.766318043985</v>
+        <v>46162.59965137731</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>190</v>
@@ -12276,11 +12276,11 @@
         <v>422</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.68244457176</v>
+        <v>46162.51577790509</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.76631474537</v>
+        <v>46162.5996480787</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>190</v>
@@ -12329,11 +12329,11 @@
         <v>423</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.68244844908</v>
+        <v>46162.51578178241</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.76631193287</v>
+        <v>46162.59964526621</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>190</v>
@@ -12382,11 +12382,11 @@
         <v>425</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.68245221065</v>
+        <v>46162.51578554398</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.76630898148</v>
+        <v>46162.59964231482</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>190</v>
@@ -12435,11 +12435,11 @@
         <v>426</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.68245652778</v>
+        <v>46162.51578986111</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.76630527778</v>
+        <v>46162.59963861111</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>190</v>
@@ -12488,11 +12488,11 @@
         <v>427</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.68246049769</v>
+        <v>46162.515793831015</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.76630212963</v>
+        <v>46162.59963546296</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>190</v>
@@ -12541,11 +12541,11 @@
         <v>428</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.68246318287</v>
+        <v>46162.51579651621</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.76629917824</v>
+        <v>46162.59963251157</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>190</v>
@@ -12594,11 +12594,11 @@
         <v>429</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.68246601852</v>
+        <v>46162.51579935185</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.76629561343</v>
+        <v>46162.59962894676</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>190</v>
@@ -12647,11 +12647,11 @@
         <v>430</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.68246881945</v>
+        <v>46162.515802152775</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.766289004634</v>
+        <v>46162.59962233796</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>190</v>
@@ -12700,11 +12700,11 @@
         <v>431</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.68247158565</v>
+        <v>46162.51580491898</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.76628835648</v>
+        <v>46162.59962168982</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12753,11 +12753,11 @@
         <v>432</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.68248012732</v>
+        <v>46162.515813460646</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.76653042824</v>
+        <v>46162.59986376157</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>433</v>
@@ -12766,10 +12766,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I197" s="9">
         <v>46231</v>
@@ -12790,7 +12790,7 @@
         <v>399</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P197" s="10" t="s">
         <v>399</v>
@@ -12816,11 +12816,11 @@
         <v>434</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.682524502314</v>
+        <v>46162.51585783565</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.766515462965</v>
+        <v>46162.59984879629</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12829,10 +12829,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I198" s="5">
         <v>46231</v>
@@ -12869,11 +12869,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.682533032406</v>
+        <v>46162.51586636574</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.76651282408</v>
+        <v>46162.599846157405</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12882,10 +12882,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I199" s="9">
         <v>46231</v>
@@ -12922,11 +12922,11 @@
         <v>437</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.68253883102</v>
+        <v>46162.51587216435</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.76651023148</v>
+        <v>46162.599843564814</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>190</v>
@@ -12935,10 +12935,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I200" s="5">
         <v>46231</v>
@@ -12975,11 +12975,11 @@
         <v>439</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.68254368055</v>
+        <v>46162.51587701389</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.76650773148</v>
+        <v>46162.59984106482</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>190</v>
@@ -12988,10 +12988,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I201" s="9">
         <v>46231</v>
@@ -13028,11 +13028,11 @@
         <v>440</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.68255409722</v>
+        <v>46162.515887430556</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.76650408565</v>
+        <v>46162.59983741898</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>190</v>
@@ -13041,10 +13041,10 @@
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I202" s="5">
         <v>46231</v>
@@ -13081,11 +13081,11 @@
         <v>442</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.6825590625</v>
+        <v>46162.51589239584</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.76650106482</v>
+        <v>46162.59983439815</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>190</v>
@@ -13094,10 +13094,10 @@
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I203" s="9">
         <v>46231</v>
@@ -13134,11 +13134,11 @@
         <v>443</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.68256261574</v>
+        <v>46162.51589594907</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.76649841435</v>
+        <v>46162.599831747684</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>190</v>
@@ -13147,10 +13147,10 @@
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I204" s="5">
         <v>46231</v>
@@ -13187,11 +13187,11 @@
         <v>444</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.682566006944</v>
+        <v>46162.51589934027</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.76649456019</v>
+        <v>46162.599827893515</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>190</v>
@@ -13200,10 +13200,10 @@
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I205" s="9">
         <v>46231</v>
@@ -13240,11 +13240,11 @@
         <v>445</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.682569386576</v>
+        <v>46162.51590271991</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.766489050926</v>
+        <v>46162.59982238426</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>190</v>
@@ -13253,10 +13253,10 @@
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I206" s="5">
         <v>46231</v>
@@ -13293,11 +13293,11 @@
         <v>446</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.68257278935</v>
+        <v>46162.51590612269</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.76648839121</v>
+        <v>46162.599821724536</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>190</v>
@@ -13306,10 +13306,10 @@
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I207" s="9">
         <v>46231</v>
@@ -13346,11 +13346,11 @@
         <v>447</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.68258331019</v>
+        <v>46162.51591664352</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.76671087963</v>
+        <v>46162.60004421296</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>448</v>
@@ -13359,10 +13359,10 @@
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I208" s="5">
         <v>46232</v>
@@ -13383,7 +13383,7 @@
         <v>399</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>449</v>
@@ -13409,11 +13409,11 @@
         <v>450</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.6825891551</v>
+        <v>46162.51592248843</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.76670017361</v>
+        <v>46162.60003350694</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13422,10 +13422,10 @@
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I209" s="9">
         <v>46232</v>
@@ -13462,11 +13462,11 @@
         <v>451</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.68259327546</v>
+        <v>46162.5159266088</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.76669680556</v>
+        <v>46162.600030138885</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13475,10 +13475,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I210" s="5">
         <v>46232</v>
@@ -13515,11 +13515,11 @@
         <v>452</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.682597499996</v>
+        <v>46162.51593083334</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.76669409723</v>
+        <v>46162.600027430555</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13528,10 +13528,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I211" s="9">
         <v>46232</v>
@@ -13568,11 +13568,11 @@
         <v>453</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.68260168981</v>
+        <v>46162.51593502315</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.766691377314</v>
+        <v>46162.60002471065</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13581,10 +13581,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I212" s="5">
         <v>46232</v>
@@ -13621,11 +13621,11 @@
         <v>454</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.68260615741</v>
+        <v>46162.51593949074</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.766687662035</v>
+        <v>46162.60002099537</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>190</v>
@@ -13634,10 +13634,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I213" s="9">
         <v>46232</v>
@@ -13674,11 +13674,11 @@
         <v>455</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.68261056713</v>
+        <v>46162.515943900464</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.76668472222</v>
+        <v>46162.60001805556</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>190</v>
@@ -13687,10 +13687,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I214" s="5">
         <v>46232</v>
@@ -13727,11 +13727,11 @@
         <v>456</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.682613564815</v>
+        <v>46162.515946898144</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.76668173611</v>
+        <v>46162.600015069445</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>190</v>
@@ -13740,10 +13740,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I215" s="9">
         <v>46232</v>
@@ -13780,11 +13780,11 @@
         <v>457</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.682616666665</v>
+        <v>46162.51595</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.76667282407</v>
+        <v>46162.60000615741</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>190</v>
@@ -13793,10 +13793,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I216" s="5">
         <v>46232</v>
@@ -13833,11 +13833,11 @@
         <v>458</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.682619583335</v>
+        <v>46162.51595291667</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.76667212963</v>
+        <v>46162.60000546296</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>190</v>
@@ -13846,10 +13846,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I217" s="9">
         <v>46232</v>
@@ -13886,11 +13886,11 @@
         <v>459</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.68262266203</v>
+        <v>46162.515955995375</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.76667141204</v>
+        <v>46162.60000474537</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>190</v>
@@ -13899,10 +13899,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I218" s="5">
         <v>46232</v>
@@ -13939,11 +13939,11 @@
         <v>460</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.682665625005</v>
+        <v>46162.51599895833</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.76005167824</v>
+        <v>46162.59338501157</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>461</v>
@@ -13986,11 +13986,11 @@
         <v>463</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.68266950232</v>
+        <v>46162.51600283565</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.76676789352</v>
+        <v>46162.60010122685</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>464</v>
@@ -14049,11 +14049,11 @@
         <v>467</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.68267490741</v>
+        <v>46162.51600824074</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46197.777038217595</v>
+        <v>46197.61037155092</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>468</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2074,13 +2074,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.514497372686</v>
+        <v>46162.68116403936</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.711231319445</v>
+        <v>46175.87789798611</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.711242743055</v>
+        <v>46175.877909409726</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2127,13 +2127,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.51460834491</v>
+        <v>46162.68127501158</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.71120528935</v>
+        <v>46175.87787195602</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.711231469904</v>
+        <v>46175.877898136576</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2192,13 +2192,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.51461189815</v>
+        <v>46162.681278564814</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.711205949076</v>
+        <v>46175.87787261574</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71123170139</v>
+        <v>46175.87789836805</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2257,13 +2257,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.51461583334</v>
+        <v>46162.6812825</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71120636574</v>
+        <v>46175.87787303241</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71123180556</v>
+        <v>46175.87789847222</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2322,13 +2322,13 @@
         <v>38</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.51461923611</v>
+        <v>46162.68128590278</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71120680556</v>
+        <v>46175.87787347222</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71123256945</v>
+        <v>46175.87789923611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>39</v>
@@ -2387,13 +2387,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.5146228588</v>
+        <v>46162.68128952546</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.71120755787</v>
+        <v>46175.877874224534</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.7112331713</v>
+        <v>46175.877899837964</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2452,13 +2452,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.51450131944</v>
+        <v>46162.68116798611</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.515392291665</v>
+        <v>46198.68205895834</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.51541025463</v>
+        <v>46198.68207692129</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2505,13 +2505,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.51462636574</v>
+        <v>46162.68129303241</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.500338391204</v>
+        <v>46197.66700505787</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.61037175926</v>
+        <v>46197.77703842593</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>48</v>
@@ -2570,13 +2570,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.51463159722</v>
+        <v>46162.68129826389</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.503101863425</v>
+        <v>46197.66976853009</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.61037174768</v>
+        <v>46197.77703841435</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2635,13 +2635,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.51463680556</v>
+        <v>46162.68130347222</v>
       </c>
       <c r="C13" s="9">
-        <v>46197.504490023144</v>
+        <v>46197.671156689816</v>
       </c>
       <c r="D13" s="9">
-        <v>46197.61037252315</v>
+        <v>46197.777039189816</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>59</v>
@@ -2700,11 +2700,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.51450521991</v>
+        <v>46162.68117188658</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.51843844907</v>
+        <v>46198.68510511574</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2747,13 +2747,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.514649363424</v>
+        <v>46162.681316030095</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.515613599535</v>
+        <v>46198.68228026621</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.515615254626</v>
+        <v>46198.6822819213</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2812,13 +2812,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.51465442129</v>
+        <v>46162.68132108796</v>
       </c>
       <c r="C16" s="5">
-        <v>46198.51843163194</v>
+        <v>46198.68509829861</v>
       </c>
       <c r="D16" s="5">
-        <v>46198.51844755787</v>
+        <v>46198.685114224536</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2877,13 +2877,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.51466033565</v>
+        <v>46162.68132700231</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.42120984953</v>
+        <v>46197.587876516205</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.50311979167</v>
+        <v>46197.66978645833</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2942,11 +2942,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.51466597222</v>
+        <v>46162.68133263889</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.62992234954</v>
+        <v>46198.7965890162</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3005,11 +3005,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.51467096065</v>
+        <v>46162.68133762731</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.629921377316</v>
+        <v>46198.79658804398</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3068,11 +3068,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.51467452546</v>
+        <v>46162.68134119213</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.629921851854</v>
+        <v>46198.79658851852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3131,11 +3131,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.51467802083</v>
+        <v>46162.6813446875</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.62992233796</v>
+        <v>46198.79658900463</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3194,11 +3194,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.514509120374</v>
+        <v>46162.68117578704</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.51864613426</v>
+        <v>46198.685312800924</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3241,13 +3241,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.51468197917</v>
+        <v>46162.681348645834</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.518634988424</v>
+        <v>46198.68530165509</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.51865375</v>
+        <v>46198.68532041667</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3306,13 +3306,13 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.51468634259</v>
+        <v>46162.68135300926</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.51858747685</v>
+        <v>46198.68525414352</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.5185890625</v>
+        <v>46198.68525572917</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3367,13 +3367,13 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.51469081019</v>
+        <v>46162.68135747685</v>
       </c>
       <c r="C25" s="9">
-        <v>46198.51862204861</v>
+        <v>46198.68528871528</v>
       </c>
       <c r="D25" s="9">
-        <v>46198.51862350694</v>
+        <v>46198.68529017361</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3428,11 +3428,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.51469575231</v>
+        <v>46162.68136241898</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46192.68650826389</v>
+        <v>46192.853174930555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3491,11 +3491,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.51470047454</v>
+        <v>46162.6813671412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.421219571756</v>
+        <v>46197.58788623843</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3550,11 +3550,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.514705520836</v>
+        <v>46162.6813721875</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.71032918982</v>
+        <v>46169.87699585648</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3609,11 +3609,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.514710393516</v>
+        <v>46162.68137706019</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46198.5164780787</v>
+        <v>46198.68314474537</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3672,13 +3672,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.51471541666</v>
+        <v>46162.681382083334</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.51565671296</v>
+        <v>46198.68232337963</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.51565814815</v>
+        <v>46198.682324814814</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3733,11 +3733,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.51472085648</v>
+        <v>46162.681387523146</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46198.515663391205</v>
+        <v>46198.68233005787</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3792,13 +3792,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.5147255787</v>
+        <v>46162.68139224537</v>
       </c>
       <c r="C32" s="5">
-        <v>46198.5164725</v>
+        <v>46198.683139166664</v>
       </c>
       <c r="D32" s="5">
-        <v>46198.51647390046</v>
+        <v>46198.683140567126</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3853,11 +3853,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.514730324074</v>
+        <v>46162.68139699074</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46203.040267916665</v>
+        <v>46203.20693458333</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3916,11 +3916,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.51473513889</v>
+        <v>46162.68140180556</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.00267526621</v>
+        <v>46191.169341932866</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3975,11 +3975,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.51474012731</v>
+        <v>46162.681406793985</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.71043666667</v>
+        <v>46169.87710333333</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -4030,11 +4030,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.51479568287</v>
+        <v>46162.68146234954</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46203.04026819444</v>
+        <v>46203.20693486111</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -4093,11 +4093,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.51480118056</v>
+        <v>46162.68146784722</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46189.00270116898</v>
+        <v>46189.16936783565</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4146,11 +4146,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.51480631944</v>
+        <v>46162.68147298611</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46202.00266831019</v>
+        <v>46202.16933497685</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4199,11 +4199,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.51481050926</v>
+        <v>46162.681477175924</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.710068333334</v>
+        <v>46169.876735</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4262,11 +4262,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.51481383102</v>
+        <v>46162.68148049769</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.002467812505</v>
+        <v>46198.16913447916</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4315,11 +4315,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.51481820602</v>
+        <v>46162.681484872686</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.71053196759</v>
+        <v>46169.87719863426</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4368,11 +4368,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.51482258102</v>
+        <v>46162.68148924768</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.71054472223</v>
+        <v>46169.877211388884</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4421,11 +4421,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.514825659724</v>
+        <v>46162.68149232639</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46203.04026834491</v>
+        <v>46203.20693501158</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4484,11 +4484,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.51482921296</v>
+        <v>46162.68149587963</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.002670925925</v>
+        <v>46191.1693375926</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4537,11 +4537,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.51483364584</v>
+        <v>46162.6815003125</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46202.00266690972</v>
+        <v>46202.169333576385</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4590,11 +4590,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.51451271991</v>
+        <v>46162.68117938658</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46198.62984987268</v>
+        <v>46198.796516539354</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4639,13 +4639,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.51483840278</v>
+        <v>46162.68150506944</v>
       </c>
       <c r="C47" s="9">
-        <v>46197.53622326389</v>
+        <v>46197.70288993056</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.5364074074</v>
+        <v>46197.703074074074</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4704,13 +4704,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.51484361111</v>
+        <v>46162.68151027778</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.6298287963</v>
+        <v>46198.796495462964</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.629845868054</v>
+        <v>46198.796512534725</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4769,13 +4769,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.51484989583</v>
+        <v>46162.6815165625</v>
       </c>
       <c r="C49" s="9">
-        <v>46198.62987209491</v>
+        <v>46198.79653876157</v>
       </c>
       <c r="D49" s="9">
-        <v>46198.62989077547</v>
+        <v>46198.796557442125</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>80</v>
@@ -4834,11 +4834,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.5148634838</v>
+        <v>46162.68153015046</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46162.59563628472</v>
+        <v>46162.76230295139</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4895,11 +4895,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.514866875004</v>
+        <v>46162.68153354166</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46162.59563131945</v>
+        <v>46162.76229798611</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4946,11 +4946,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.514870694446</v>
+        <v>46162.68153736111</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46162.59562782408</v>
+        <v>46162.76229449074</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4997,11 +4997,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.514874768516</v>
+        <v>46162.68154143519</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46162.59562479166</v>
+        <v>46162.76229145833</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -5048,11 +5048,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.51487774306</v>
+        <v>46162.68154440972</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46162.595622106484</v>
+        <v>46162.76228877315</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5099,11 +5099,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.51488074074</v>
+        <v>46162.68154740741</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46162.59561929398</v>
+        <v>46162.76228596065</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -5150,11 +5150,11 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.514883807875</v>
+        <v>46162.68155047453</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46162.595616203704</v>
+        <v>46162.762282870375</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>190</v>
@@ -5201,11 +5201,11 @@
         <v>197</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.51488609954</v>
+        <v>46162.681552766204</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46162.59561251158</v>
+        <v>46162.76227917824</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>190</v>
@@ -5252,11 +5252,11 @@
         <v>198</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.51488849537</v>
+        <v>46162.68155516204</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.595609675926</v>
+        <v>46162.76227634259</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>190</v>
@@ -5303,11 +5303,11 @@
         <v>199</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.51489078703</v>
+        <v>46162.6815574537</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46162.59560234954</v>
+        <v>46162.7622690162</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>190</v>
@@ -5354,11 +5354,11 @@
         <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.514892858795</v>
+        <v>46162.68155952546</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46162.59560172453</v>
+        <v>46162.762268391205</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>190</v>
@@ -5405,11 +5405,11 @@
         <v>201</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.5149321412</v>
+        <v>46162.681598807874</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46162.54069429398</v>
+        <v>46162.707360960645</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>202</v>
@@ -5452,11 +5452,11 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.51493607639</v>
+        <v>46162.681602743054</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46204.0220965162</v>
+        <v>46204.18876318287</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>205</v>
@@ -5513,11 +5513,11 @@
         <v>209</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.51494170139</v>
+        <v>46162.68160836806</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46205.0072115625</v>
+        <v>46205.173878229165</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>210</v>
@@ -5574,11 +5574,11 @@
         <v>213</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.51494854166</v>
+        <v>46162.681615208334</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46204.022096608795</v>
+        <v>46204.188763275466</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>214</v>
@@ -5635,11 +5635,11 @@
         <v>216</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.51495402778</v>
+        <v>46162.68162069445</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46205.007211805554</v>
+        <v>46205.173878472226</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>217</v>
@@ -5696,11 +5696,11 @@
         <v>219</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.51495931713</v>
+        <v>46162.681625983794</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46204.02209745371</v>
+        <v>46204.18876412037</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>220</v>
@@ -5757,11 +5757,11 @@
         <v>222</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.51496408565</v>
+        <v>46162.68163075231</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46205.007211759264</v>
+        <v>46205.17387842592</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>221</v>
@@ -5818,11 +5818,11 @@
         <v>223</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.51496944444</v>
+        <v>46162.68163611111</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46162.596656724534</v>
+        <v>46162.763323391206</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>224</v>
@@ -5865,11 +5865,11 @@
         <v>226</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.51497234954</v>
+        <v>46162.6816390162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46202.012177083336</v>
+        <v>46202.17884375</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5928,11 +5928,11 @@
         <v>232</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.5149772338</v>
+        <v>46162.68164390046</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.59665186342</v>
+        <v>46162.763318530095</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5981,11 +5981,11 @@
         <v>235</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.51498453703</v>
+        <v>46162.681651203704</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.596648935185</v>
+        <v>46162.76331560186</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -6034,11 +6034,11 @@
         <v>237</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.5149906713</v>
+        <v>46162.68165733796</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.596646053236</v>
+        <v>46162.76331271991</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6087,11 +6087,11 @@
         <v>240</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.514996701386</v>
+        <v>46162.68166336806</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.59664304398</v>
+        <v>46162.763309710645</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6140,11 +6140,11 @@
         <v>241</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.515002685184</v>
+        <v>46162.68166935185</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.5966400926</v>
+        <v>46162.763306759254</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6193,11 +6193,11 @@
         <v>242</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.51500905093</v>
+        <v>46162.68167571759</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.59663693287</v>
+        <v>46162.76330359954</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6246,11 +6246,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.515014432865</v>
+        <v>46162.68168109954</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.59663400463</v>
+        <v>46162.7633006713</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6299,11 +6299,11 @@
         <v>245</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.5150196412</v>
+        <v>46162.68168630787</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.59663071759</v>
+        <v>46162.763297384256</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6352,11 +6352,11 @@
         <v>246</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.51502527778</v>
+        <v>46162.68169194444</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.596624224534</v>
+        <v>46162.763290891206</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>190</v>
@@ -6405,11 +6405,11 @@
         <v>247</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.5150315625</v>
+        <v>46162.681698229164</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.59662357639</v>
+        <v>46162.763290243056</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>190</v>
@@ -6458,11 +6458,11 @@
         <v>248</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.515047650464</v>
+        <v>46162.68171431713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.59694990741</v>
+        <v>46162.76361657407</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>249</v>
@@ -6521,11 +6521,11 @@
         <v>250</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.515052268514</v>
+        <v>46162.681718935186</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.62988877315</v>
+        <v>46198.79655543981</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>190</v>
@@ -6574,11 +6574,11 @@
         <v>253</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.5150584838</v>
+        <v>46162.68172515046</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.62989521991</v>
+        <v>46198.79656188657</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>190</v>
@@ -6627,11 +6627,11 @@
         <v>254</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.515064074076</v>
+        <v>46162.68173074074</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.62988982639</v>
+        <v>46198.79655649306</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>190</v>
@@ -6680,11 +6680,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.51506952546</v>
+        <v>46162.68173619213</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.62989055556</v>
+        <v>46198.796557222224</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>190</v>
@@ -6733,11 +6733,11 @@
         <v>256</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.51507508101</v>
+        <v>46162.681741747685</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46162.59692311342</v>
+        <v>46162.763589780094</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6786,11 +6786,11 @@
         <v>257</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.51511611111</v>
+        <v>46162.68178277778</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46162.59691972222</v>
+        <v>46162.763586388886</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6839,11 +6839,11 @@
         <v>258</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.5151200463</v>
+        <v>46162.68178671296</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46162.59691699074</v>
+        <v>46162.763583657405</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6892,11 +6892,11 @@
         <v>259</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.51512310185</v>
+        <v>46162.68178976852</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46162.596914317124</v>
+        <v>46162.763580983796</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6945,11 +6945,11 @@
         <v>260</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.515126342594</v>
+        <v>46162.68179300926</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46162.59690751157</v>
+        <v>46162.76357417824</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>190</v>
@@ -6998,11 +6998,11 @@
         <v>261</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.515129583335</v>
+        <v>46162.68179625</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46162.59690686343</v>
+        <v>46162.763573530094</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -7051,11 +7051,11 @@
         <v>262</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.51514020833</v>
+        <v>46162.681806875</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46162.59717238426</v>
+        <v>46162.763839050924</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>263</v>
@@ -7114,11 +7114,11 @@
         <v>264</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.51514509259</v>
+        <v>46162.68181175926</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.62989590278</v>
+        <v>46198.79656256945</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -7167,11 +7167,11 @@
         <v>266</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.515150844905</v>
+        <v>46162.68181751158</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46198.62990699074</v>
+        <v>46198.79657365741</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -7220,11 +7220,11 @@
         <v>267</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.51515636574</v>
+        <v>46162.681823032406</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.62990746528</v>
+        <v>46198.79657413195</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>190</v>
@@ -7273,11 +7273,11 @@
         <v>269</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.51516170139</v>
+        <v>46162.681828368055</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.62990798611</v>
+        <v>46198.79657465278</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7326,11 +7326,11 @@
         <v>270</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.51516733796</v>
+        <v>46162.68183400463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46162.597118680555</v>
+        <v>46162.763785347226</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7379,11 +7379,11 @@
         <v>272</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.51517239583</v>
+        <v>46162.6818390625</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46162.59711548611</v>
+        <v>46162.763782152775</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7432,11 +7432,11 @@
         <v>273</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.515175416665</v>
+        <v>46162.68184208333</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46162.59711282408</v>
+        <v>46162.76377949074</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7485,11 +7485,11 @@
         <v>275</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.51517922454</v>
+        <v>46162.6818458912</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.59710596065</v>
+        <v>46162.76377262731</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>190</v>
@@ -7538,11 +7538,11 @@
         <v>276</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.51518270833</v>
+        <v>46162.681849375</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46162.597105312496</v>
+        <v>46162.76377197917</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7591,11 +7591,11 @@
         <v>277</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.51518592593</v>
+        <v>46162.68185259259</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46162.59710462963</v>
+        <v>46162.7637712963</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7644,11 +7644,11 @@
         <v>278</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.5151958912</v>
+        <v>46162.681862557874</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46162.54193150463</v>
+        <v>46162.708598171295</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>202</v>
@@ -7691,11 +7691,11 @@
         <v>280</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.515199340276</v>
+        <v>46162.68186600694</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46162.59731405093</v>
+        <v>46162.76398071759</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>281</v>
@@ -7752,11 +7752,11 @@
         <v>283</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.51520620371</v>
+        <v>46162.681872870366</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46198.51863928241</v>
+        <v>46198.685305949075</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>284</v>
@@ -7813,11 +7813,11 @@
         <v>286</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.51521326389</v>
+        <v>46162.681879930555</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46197.01009574074</v>
+        <v>46197.17676240741</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>287</v>
@@ -7874,11 +7874,11 @@
         <v>289</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.51521974537</v>
+        <v>46162.681886412036</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46162.59730359954</v>
+        <v>46162.763970266205</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>290</v>
@@ -7935,11 +7935,11 @@
         <v>292</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.51522420139</v>
+        <v>46162.68189086806</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46162.5441978125</v>
+        <v>46162.710864479166</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>293</v>
@@ -7982,11 +7982,11 @@
         <v>295</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.515227094904</v>
+        <v>46162.681893761575</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46162.59758981482</v>
+        <v>46162.76425648148</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>296</v>
@@ -8045,11 +8045,11 @@
         <v>298</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.515240277775</v>
+        <v>46162.68190694445</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46162.59758659722</v>
+        <v>46162.764253263886</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>190</v>
@@ -8098,11 +8098,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.515244375</v>
+        <v>46162.68191104167</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46162.59758336806</v>
+        <v>46162.76425003472</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8151,11 +8151,11 @@
         <v>301</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.51524849537</v>
+        <v>46162.68191516204</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46162.59757960648</v>
+        <v>46162.764246273146</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8204,11 +8204,11 @@
         <v>303</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.5152528125</v>
+        <v>46162.68191947917</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46162.59757637732</v>
+        <v>46162.76424304398</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8257,11 +8257,11 @@
         <v>305</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.51525704861</v>
+        <v>46162.68192371528</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46162.59757341435</v>
+        <v>46162.764240081015</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8310,11 +8310,11 @@
         <v>306</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.51526049769</v>
+        <v>46162.68192716435</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.5975703125</v>
+        <v>46162.76423697917</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>190</v>
@@ -8363,11 +8363,11 @@
         <v>307</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.51526369213</v>
+        <v>46162.6819303588</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46162.59756756945</v>
+        <v>46162.76423423611</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>190</v>
@@ -8416,11 +8416,11 @@
         <v>308</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.51526677083</v>
+        <v>46162.6819334375</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.59756486111</v>
+        <v>46162.76423152778</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8469,11 +8469,11 @@
         <v>309</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.5152699537</v>
+        <v>46162.68193662037</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.5975578125</v>
+        <v>46162.764224479164</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8522,11 +8522,11 @@
         <v>310</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.51527310185</v>
+        <v>46162.68193976852</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.59755723379</v>
+        <v>46162.76422390046</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8575,11 +8575,11 @@
         <v>311</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.51532694444</v>
+        <v>46162.68199361111</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.59778599537</v>
+        <v>46162.76445266204</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>312</v>
@@ -8638,11 +8638,11 @@
         <v>313</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.51533206018</v>
+        <v>46162.68199872685</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46198.62989115741</v>
+        <v>46198.79655782407</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>190</v>
@@ -8691,11 +8691,11 @@
         <v>316</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.51533766204</v>
+        <v>46162.6820043287</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46198.62990829861</v>
+        <v>46198.79657496528</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8744,11 +8744,11 @@
         <v>318</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.51534278935</v>
+        <v>46162.68200945602</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46198.62990344907</v>
+        <v>46198.79657011574</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8797,11 +8797,11 @@
         <v>321</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.51534923611</v>
+        <v>46162.68201590278</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46198.62988732639</v>
+        <v>46198.79655399306</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8850,11 +8850,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.515355509255</v>
+        <v>46162.682022175926</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46162.59774576389</v>
+        <v>46162.76441243055</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8903,11 +8903,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.51535997685</v>
+        <v>46162.68202664352</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46198.629891550925</v>
+        <v>46198.7965582176</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>190</v>
@@ -8956,11 +8956,11 @@
         <v>325</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.51536520833</v>
+        <v>46162.682031874996</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46198.62989239584</v>
+        <v>46198.796559062495</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -9009,11 +9009,11 @@
         <v>327</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.51537046296</v>
+        <v>46162.682037129634</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46198.62989292824</v>
+        <v>46198.796559594906</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -9062,11 +9062,11 @@
         <v>328</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.5153756713</v>
+        <v>46162.68204233796</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46198.62989627315</v>
+        <v>46198.79656293981</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -9115,11 +9115,11 @@
         <v>329</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.515380868055</v>
+        <v>46162.68204753472</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46198.62990380787</v>
+        <v>46198.79657047454</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -9168,11 +9168,11 @@
         <v>330</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.51539451389</v>
+        <v>46162.68206118056</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46162.59795079861</v>
+        <v>46162.76461746528</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>331</v>
@@ -9231,11 +9231,11 @@
         <v>332</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.51539876158</v>
+        <v>46162.68206542824</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46198.62989355324</v>
+        <v>46198.79656021991</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9284,11 +9284,11 @@
         <v>334</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.515404756945</v>
+        <v>46162.68207142361</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46198.62989454861</v>
+        <v>46198.79656121528</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9337,11 +9337,11 @@
         <v>336</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.51541633102</v>
+        <v>46162.682082997686</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46198.629904270834</v>
+        <v>46198.7965709375</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9390,11 +9390,11 @@
         <v>338</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.51542265047</v>
+        <v>46162.682089317124</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46198.62988814815</v>
+        <v>46198.79655481481</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9443,11 +9443,11 @@
         <v>341</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.51542899305</v>
+        <v>46162.68209565972</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46162.59793458333</v>
+        <v>46162.764601250004</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>190</v>
@@ -9496,11 +9496,11 @@
         <v>343</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.51543327546</v>
+        <v>46162.68209994213</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46162.59793099537</v>
+        <v>46162.76459766204</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>190</v>
@@ -9549,11 +9549,11 @@
         <v>345</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.51543752315</v>
+        <v>46162.682104189815</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46162.59792822917</v>
+        <v>46162.76459489584</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>190</v>
@@ -9602,11 +9602,11 @@
         <v>346</v>
       </c>
       <c r="B138" s="5">
-        <v>46162.5154406713</v>
+        <v>46162.68210733796</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46162.59792023148</v>
+        <v>46162.76458689815</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>190</v>
@@ -9655,11 +9655,11 @@
         <v>347</v>
       </c>
       <c r="B139" s="9">
-        <v>46162.51544488426</v>
+        <v>46162.68211155092</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46162.597919548614</v>
+        <v>46162.76458621528</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>190</v>
@@ -9708,11 +9708,11 @@
         <v>348</v>
       </c>
       <c r="B140" s="5">
-        <v>46162.515449212966</v>
+        <v>46162.68211587963</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46162.59791885417</v>
+        <v>46162.76458552083</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>190</v>
@@ -9761,11 +9761,11 @@
         <v>349</v>
       </c>
       <c r="B141" s="9">
-        <v>46162.515461504634</v>
+        <v>46162.68212817129</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46162.598105</v>
+        <v>46162.76477166667</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>350</v>
@@ -9824,11 +9824,11 @@
         <v>351</v>
       </c>
       <c r="B142" s="5">
-        <v>46162.5154656713</v>
+        <v>46162.68213233796</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46198.62990503472</v>
+        <v>46198.79657170139</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>190</v>
@@ -9877,11 +9877,11 @@
         <v>354</v>
       </c>
       <c r="B143" s="9">
-        <v>46162.51547121527</v>
+        <v>46162.682137881944</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46198.62990550926</v>
+        <v>46198.796572175925</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>190</v>
@@ -9930,11 +9930,11 @@
         <v>355</v>
       </c>
       <c r="B144" s="5">
-        <v>46162.515476608794</v>
+        <v>46162.682143275466</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46198.62989689814</v>
+        <v>46198.796563564814</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>190</v>
@@ -9983,11 +9983,11 @@
         <v>357</v>
       </c>
       <c r="B145" s="9">
-        <v>46162.51548292824</v>
+        <v>46162.68214959491</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46198.62990638889</v>
+        <v>46198.79657305556</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>190</v>
@@ -10036,11 +10036,11 @@
         <v>359</v>
       </c>
       <c r="B146" s="5">
-        <v>46162.515531365745</v>
+        <v>46162.6821980324</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46162.59809424769</v>
+        <v>46162.76476091435</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>190</v>
@@ -10089,11 +10089,11 @@
         <v>361</v>
       </c>
       <c r="B147" s="9">
-        <v>46162.51553788195</v>
+        <v>46162.68220454861</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46162.598091064814</v>
+        <v>46162.76475773148</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>190</v>
@@ -10142,11 +10142,11 @@
         <v>364</v>
       </c>
       <c r="B148" s="5">
-        <v>46162.51554462963</v>
+        <v>46162.6822112963</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46162.5980878588</v>
+        <v>46162.76475452546</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>190</v>
@@ -10195,11 +10195,11 @@
         <v>365</v>
       </c>
       <c r="B149" s="9">
-        <v>46162.515549386575</v>
+        <v>46162.68221605324</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46162.59808292824</v>
+        <v>46162.764749594906</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>190</v>
@@ -10248,11 +10248,11 @@
         <v>366</v>
       </c>
       <c r="B150" s="5">
-        <v>46162.515555335645</v>
+        <v>46162.68222200232</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46162.5980762963</v>
+        <v>46162.76474296296</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>190</v>
@@ -10301,11 +10301,11 @@
         <v>368</v>
       </c>
       <c r="B151" s="9">
-        <v>46162.51556148149</v>
+        <v>46162.68222814814</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46162.59807547454</v>
+        <v>46162.764742141204</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>190</v>
@@ -10354,11 +10354,11 @@
         <v>369</v>
       </c>
       <c r="B152" s="5">
-        <v>46162.51557831018</v>
+        <v>46162.68224497685</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46162.598281921295</v>
+        <v>46162.76494858797</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>370</v>
@@ -10417,11 +10417,11 @@
         <v>371</v>
       </c>
       <c r="B153" s="9">
-        <v>46162.51558331019</v>
+        <v>46162.68224997685</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46162.59826834491</v>
+        <v>46162.764935011575</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>190</v>
@@ -10470,11 +10470,11 @@
         <v>373</v>
       </c>
       <c r="B154" s="5">
-        <v>46162.51558917824</v>
+        <v>46162.682255844906</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46162.598265127315</v>
+        <v>46162.76493179398</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>190</v>
@@ -10523,11 +10523,11 @@
         <v>374</v>
       </c>
       <c r="B155" s="9">
-        <v>46162.5155946875</v>
+        <v>46162.682261354166</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46162.598262025465</v>
+        <v>46162.76492869213</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>190</v>
@@ -10576,11 +10576,11 @@
         <v>375</v>
       </c>
       <c r="B156" s="5">
-        <v>46162.515600266204</v>
+        <v>46162.68226693287</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46162.59825894676</v>
+        <v>46162.764925613425</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>190</v>
@@ -10629,11 +10629,11 @@
         <v>377</v>
       </c>
       <c r="B157" s="9">
-        <v>46162.515605625</v>
+        <v>46162.68227229167</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46162.59825605324</v>
+        <v>46162.76492271991</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>190</v>
@@ -10682,11 +10682,11 @@
         <v>378</v>
       </c>
       <c r="B158" s="5">
-        <v>46162.51561096065</v>
+        <v>46162.68227762732</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46162.59825277778</v>
+        <v>46162.764919444446</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>190</v>
@@ -10735,11 +10735,11 @@
         <v>379</v>
       </c>
       <c r="B159" s="9">
-        <v>46162.51561365741</v>
+        <v>46162.68228032408</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46162.598249710645</v>
+        <v>46162.76491637732</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>190</v>
@@ -10788,11 +10788,11 @@
         <v>380</v>
       </c>
       <c r="B160" s="5">
-        <v>46162.51561780093</v>
+        <v>46162.68228446759</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.598247002315</v>
+        <v>46162.76491366898</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>190</v>
@@ -10841,11 +10841,11 @@
         <v>381</v>
       </c>
       <c r="B161" s="9">
-        <v>46162.5156205324</v>
+        <v>46162.68228719907</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46162.5982405324</v>
+        <v>46162.764907199075</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>190</v>
@@ -10894,11 +10894,11 @@
         <v>382</v>
       </c>
       <c r="B162" s="5">
-        <v>46162.515623495376</v>
+        <v>46162.68229016203</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46162.598239756946</v>
+        <v>46162.76490642361</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>190</v>
@@ -10947,11 +10947,11 @@
         <v>383</v>
       </c>
       <c r="B163" s="9">
-        <v>46162.51563335648</v>
+        <v>46162.68230002315</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46162.598489317126</v>
+        <v>46162.7651559838</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>384</v>
@@ -11010,11 +11010,11 @@
         <v>386</v>
       </c>
       <c r="B164" s="5">
-        <v>46162.51564283565</v>
+        <v>46162.682309502314</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46162.59846577546</v>
+        <v>46162.76513244213</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>190</v>
@@ -11061,11 +11061,11 @@
         <v>388</v>
       </c>
       <c r="B165" s="9">
-        <v>46162.51564708333</v>
+        <v>46162.68231375</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46162.59846291666</v>
+        <v>46162.765129583335</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>190</v>
@@ -11112,11 +11112,11 @@
         <v>389</v>
       </c>
       <c r="B166" s="5">
-        <v>46162.515651435184</v>
+        <v>46162.682318101855</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46162.59845991898</v>
+        <v>46162.76512658565</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>190</v>
@@ -11163,11 +11163,11 @@
         <v>390</v>
       </c>
       <c r="B167" s="9">
-        <v>46162.515655763884</v>
+        <v>46162.682322430555</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46162.598457025466</v>
+        <v>46162.76512369213</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>190</v>
@@ -11214,11 +11214,11 @@
         <v>391</v>
       </c>
       <c r="B168" s="5">
-        <v>46162.51566009259</v>
+        <v>46162.682326759255</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46162.598454085644</v>
+        <v>46162.765120752316</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>190</v>
@@ -11265,11 +11265,11 @@
         <v>393</v>
       </c>
       <c r="B169" s="9">
-        <v>46162.51569572916</v>
+        <v>46162.68236239583</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46162.598450798614</v>
+        <v>46162.76511746528</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>190</v>
@@ -11316,11 +11316,11 @@
         <v>394</v>
       </c>
       <c r="B170" s="5">
-        <v>46162.51569929398</v>
+        <v>46162.682365960645</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46162.59844327546</v>
+        <v>46162.765109942135</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>190</v>
@@ -11367,11 +11367,11 @@
         <v>395</v>
       </c>
       <c r="B171" s="9">
-        <v>46162.515702777775</v>
+        <v>46162.68236944445</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.59844033565</v>
+        <v>46162.76510700231</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>190</v>
@@ -11418,11 +11418,11 @@
         <v>396</v>
       </c>
       <c r="B172" s="5">
-        <v>46162.51570592592</v>
+        <v>46162.68237259259</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46162.59843385417</v>
+        <v>46162.76510052083</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>190</v>
@@ -11469,11 +11469,11 @@
         <v>397</v>
       </c>
       <c r="B173" s="9">
-        <v>46162.51570923611</v>
+        <v>46162.682375902776</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46162.598433356485</v>
+        <v>46162.76510002315</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>190</v>
@@ -11520,11 +11520,11 @@
         <v>398</v>
       </c>
       <c r="B174" s="5">
-        <v>46162.51571943287</v>
+        <v>46162.682386099536</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46162.5451181713</v>
+        <v>46162.711784837964</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>399</v>
@@ -11567,11 +11567,11 @@
         <v>401</v>
       </c>
       <c r="B175" s="9">
-        <v>46162.51572258102</v>
+        <v>46162.68238924768</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46162.598708715275</v>
+        <v>46162.76537538195</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>402</v>
@@ -11630,11 +11630,11 @@
         <v>406</v>
       </c>
       <c r="B176" s="5">
-        <v>46162.515727997685</v>
+        <v>46162.682394664356</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46162.59869457176</v>
+        <v>46162.76536123843</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>190</v>
@@ -11683,11 +11683,11 @@
         <v>408</v>
       </c>
       <c r="B177" s="9">
-        <v>46162.51573236111</v>
+        <v>46162.68239902778</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46162.59869135417</v>
+        <v>46162.76535802083</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>190</v>
@@ -11736,11 +11736,11 @@
         <v>409</v>
       </c>
       <c r="B178" s="5">
-        <v>46162.51573665509</v>
+        <v>46162.682403321756</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46162.59868791667</v>
+        <v>46162.76535458333</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>190</v>
@@ -11789,11 +11789,11 @@
         <v>410</v>
       </c>
       <c r="B179" s="9">
-        <v>46162.515740891205</v>
+        <v>46162.68240755787</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46162.5986849537</v>
+        <v>46162.76535162037</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>190</v>
@@ -11842,11 +11842,11 @@
         <v>412</v>
       </c>
       <c r="B180" s="5">
-        <v>46162.51574541666</v>
+        <v>46162.68241208333</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46162.598682129625</v>
+        <v>46162.765348796296</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>190</v>
@@ -11895,11 +11895,11 @@
         <v>413</v>
       </c>
       <c r="B181" s="9">
-        <v>46162.51574973379</v>
+        <v>46162.682416400465</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46162.59867831018</v>
+        <v>46162.765344976855</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>190</v>
@@ -11948,11 +11948,11 @@
         <v>414</v>
       </c>
       <c r="B182" s="5">
-        <v>46162.515752858795</v>
+        <v>46162.68241952546</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.59867409722</v>
+        <v>46162.765340763886</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>190</v>
@@ -12001,11 +12001,11 @@
         <v>415</v>
       </c>
       <c r="B183" s="9">
-        <v>46162.51575556713</v>
+        <v>46162.6824222338</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46162.59867082176</v>
+        <v>46162.765337488425</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>190</v>
@@ -12054,11 +12054,11 @@
         <v>416</v>
       </c>
       <c r="B184" s="5">
-        <v>46162.51575847222</v>
+        <v>46162.68242513889</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46162.59866390046</v>
+        <v>46162.76533056713</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>190</v>
@@ -12107,11 +12107,11 @@
         <v>417</v>
       </c>
       <c r="B185" s="9">
-        <v>46162.51576145833</v>
+        <v>46162.682428125</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46162.598663240744</v>
+        <v>46162.76532990741</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>190</v>
@@ -12160,11 +12160,11 @@
         <v>418</v>
       </c>
       <c r="B186" s="5">
-        <v>46162.51577021991</v>
+        <v>46162.68243688658</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46162.59967365741</v>
+        <v>46162.76634032407</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>419</v>
@@ -12223,11 +12223,11 @@
         <v>420</v>
       </c>
       <c r="B187" s="9">
-        <v>46162.51577402778</v>
+        <v>46162.68244069444</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46162.59965137731</v>
+        <v>46162.766318043985</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>190</v>
@@ -12276,11 +12276,11 @@
         <v>422</v>
       </c>
       <c r="B188" s="5">
-        <v>46162.51577790509</v>
+        <v>46162.68244457176</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46162.5996480787</v>
+        <v>46162.76631474537</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>190</v>
@@ -12329,11 +12329,11 @@
         <v>423</v>
       </c>
       <c r="B189" s="9">
-        <v>46162.51578178241</v>
+        <v>46162.68244844908</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46162.59964526621</v>
+        <v>46162.76631193287</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>190</v>
@@ -12382,11 +12382,11 @@
         <v>425</v>
       </c>
       <c r="B190" s="5">
-        <v>46162.51578554398</v>
+        <v>46162.68245221065</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46162.59964231482</v>
+        <v>46162.76630898148</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>190</v>
@@ -12435,11 +12435,11 @@
         <v>426</v>
       </c>
       <c r="B191" s="9">
-        <v>46162.51578986111</v>
+        <v>46162.68245652778</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46162.59963861111</v>
+        <v>46162.76630527778</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>190</v>
@@ -12488,11 +12488,11 @@
         <v>427</v>
       </c>
       <c r="B192" s="5">
-        <v>46162.515793831015</v>
+        <v>46162.68246049769</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46162.59963546296</v>
+        <v>46162.76630212963</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>190</v>
@@ -12541,11 +12541,11 @@
         <v>428</v>
       </c>
       <c r="B193" s="9">
-        <v>46162.51579651621</v>
+        <v>46162.68246318287</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46162.59963251157</v>
+        <v>46162.76629917824</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>190</v>
@@ -12594,11 +12594,11 @@
         <v>429</v>
       </c>
       <c r="B194" s="5">
-        <v>46162.51579935185</v>
+        <v>46162.68246601852</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.59962894676</v>
+        <v>46162.76629561343</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>190</v>
@@ -12647,11 +12647,11 @@
         <v>430</v>
       </c>
       <c r="B195" s="9">
-        <v>46162.515802152775</v>
+        <v>46162.68246881945</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.59962233796</v>
+        <v>46162.766289004634</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>190</v>
@@ -12700,11 +12700,11 @@
         <v>431</v>
       </c>
       <c r="B196" s="5">
-        <v>46162.51580491898</v>
+        <v>46162.68247158565</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.59962168982</v>
+        <v>46162.76628835648</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>190</v>
@@ -12753,11 +12753,11 @@
         <v>432</v>
       </c>
       <c r="B197" s="9">
-        <v>46162.515813460646</v>
+        <v>46162.68248012732</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.59986376157</v>
+        <v>46162.76653042824</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>433</v>
@@ -12816,11 +12816,11 @@
         <v>434</v>
       </c>
       <c r="B198" s="5">
-        <v>46162.51585783565</v>
+        <v>46162.682524502314</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.59984879629</v>
+        <v>46162.766515462965</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>190</v>
@@ -12869,11 +12869,11 @@
         <v>436</v>
       </c>
       <c r="B199" s="9">
-        <v>46162.51586636574</v>
+        <v>46162.682533032406</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.599846157405</v>
+        <v>46162.76651282408</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>190</v>
@@ -12922,11 +12922,11 @@
         <v>437</v>
       </c>
       <c r="B200" s="5">
-        <v>46162.51587216435</v>
+        <v>46162.68253883102</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.599843564814</v>
+        <v>46162.76651023148</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>190</v>
@@ -12975,11 +12975,11 @@
         <v>439</v>
       </c>
       <c r="B201" s="9">
-        <v>46162.51587701389</v>
+        <v>46162.68254368055</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.59984106482</v>
+        <v>46162.76650773148</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>190</v>
@@ -13028,11 +13028,11 @@
         <v>440</v>
       </c>
       <c r="B202" s="5">
-        <v>46162.515887430556</v>
+        <v>46162.68255409722</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.59983741898</v>
+        <v>46162.76650408565</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>190</v>
@@ -13081,11 +13081,11 @@
         <v>442</v>
       </c>
       <c r="B203" s="9">
-        <v>46162.51589239584</v>
+        <v>46162.6825590625</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.59983439815</v>
+        <v>46162.76650106482</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>190</v>
@@ -13134,11 +13134,11 @@
         <v>443</v>
       </c>
       <c r="B204" s="5">
-        <v>46162.51589594907</v>
+        <v>46162.68256261574</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.599831747684</v>
+        <v>46162.76649841435</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>190</v>
@@ -13187,11 +13187,11 @@
         <v>444</v>
       </c>
       <c r="B205" s="9">
-        <v>46162.51589934027</v>
+        <v>46162.682566006944</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46162.599827893515</v>
+        <v>46162.76649456019</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>190</v>
@@ -13240,11 +13240,11 @@
         <v>445</v>
       </c>
       <c r="B206" s="5">
-        <v>46162.51590271991</v>
+        <v>46162.682569386576</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46162.59982238426</v>
+        <v>46162.766489050926</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>190</v>
@@ -13293,11 +13293,11 @@
         <v>446</v>
       </c>
       <c r="B207" s="9">
-        <v>46162.51590612269</v>
+        <v>46162.68257278935</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46162.599821724536</v>
+        <v>46162.76648839121</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>190</v>
@@ -13346,11 +13346,11 @@
         <v>447</v>
       </c>
       <c r="B208" s="5">
-        <v>46162.51591664352</v>
+        <v>46162.68258331019</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46162.60004421296</v>
+        <v>46162.76671087963</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>448</v>
@@ -13409,11 +13409,11 @@
         <v>450</v>
       </c>
       <c r="B209" s="9">
-        <v>46162.51592248843</v>
+        <v>46162.6825891551</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46162.60003350694</v>
+        <v>46162.76670017361</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>190</v>
@@ -13462,11 +13462,11 @@
         <v>451</v>
       </c>
       <c r="B210" s="5">
-        <v>46162.5159266088</v>
+        <v>46162.68259327546</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46162.600030138885</v>
+        <v>46162.76669680556</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>190</v>
@@ -13515,11 +13515,11 @@
         <v>452</v>
       </c>
       <c r="B211" s="9">
-        <v>46162.51593083334</v>
+        <v>46162.682597499996</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46162.600027430555</v>
+        <v>46162.76669409723</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>190</v>
@@ -13568,11 +13568,11 @@
         <v>453</v>
       </c>
       <c r="B212" s="5">
-        <v>46162.51593502315</v>
+        <v>46162.68260168981</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46162.60002471065</v>
+        <v>46162.766691377314</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>190</v>
@@ -13621,11 +13621,11 @@
         <v>454</v>
       </c>
       <c r="B213" s="9">
-        <v>46162.51593949074</v>
+        <v>46162.68260615741</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46162.60002099537</v>
+        <v>46162.766687662035</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>190</v>
@@ -13674,11 +13674,11 @@
         <v>455</v>
       </c>
       <c r="B214" s="5">
-        <v>46162.515943900464</v>
+        <v>46162.68261056713</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46162.60001805556</v>
+        <v>46162.76668472222</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>190</v>
@@ -13727,11 +13727,11 @@
         <v>456</v>
       </c>
       <c r="B215" s="9">
-        <v>46162.515946898144</v>
+        <v>46162.682613564815</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46162.600015069445</v>
+        <v>46162.76668173611</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>190</v>
@@ -13780,11 +13780,11 @@
         <v>457</v>
       </c>
       <c r="B216" s="5">
-        <v>46162.51595</v>
+        <v>46162.682616666665</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.60000615741</v>
+        <v>46162.76667282407</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>190</v>
@@ -13833,11 +13833,11 @@
         <v>458</v>
       </c>
       <c r="B217" s="9">
-        <v>46162.51595291667</v>
+        <v>46162.682619583335</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.60000546296</v>
+        <v>46162.76667212963</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>190</v>
@@ -13886,11 +13886,11 @@
         <v>459</v>
       </c>
       <c r="B218" s="5">
-        <v>46162.515955995375</v>
+        <v>46162.68262266203</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.60000474537</v>
+        <v>46162.76667141204</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>190</v>
@@ -13939,11 +13939,11 @@
         <v>460</v>
       </c>
       <c r="B219" s="9">
-        <v>46162.51599895833</v>
+        <v>46162.682665625005</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.59338501157</v>
+        <v>46162.76005167824</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>461</v>
@@ -13986,11 +13986,11 @@
         <v>463</v>
       </c>
       <c r="B220" s="5">
-        <v>46162.51600283565</v>
+        <v>46162.68266950232</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.60010122685</v>
+        <v>46162.76676789352</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>464</v>
@@ -14049,11 +14049,11 @@
         <v>467</v>
       </c>
       <c r="B221" s="9">
-        <v>46162.51600824074</v>
+        <v>46162.68267490741</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46197.61037155092</v>
+        <v>46197.777038217595</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>468</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="469">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -2702,9 +2702,11 @@
       <c r="B14" s="5">
         <v>46162.68117188658</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46206.557440902776</v>
+      </c>
       <c r="D14" s="5">
-        <v>46198.68510511574</v>
+        <v>46206.557457048606</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2739,8 +2741,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2944,9 +2950,11 @@
       <c r="B18" s="5">
         <v>46162.68133263889</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46206.556716527775</v>
+      </c>
       <c r="D18" s="5">
-        <v>46198.7965890162</v>
+        <v>46206.55673405093</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2994,10 +3002,10 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -3007,9 +3015,11 @@
       <c r="B19" s="9">
         <v>46162.68133762731</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46206.55692722222</v>
+      </c>
       <c r="D19" s="9">
-        <v>46198.79658804398</v>
+        <v>46206.556944236116</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -3057,10 +3067,10 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3070,9 +3080,11 @@
       <c r="B20" s="5">
         <v>46162.68134119213</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46206.5574193287</v>
+      </c>
       <c r="D20" s="5">
-        <v>46198.79658851852</v>
+        <v>46206.557437372685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -3120,10 +3132,10 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3133,9 +3145,11 @@
       <c r="B21" s="9">
         <v>46162.6813446875</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46206.55726760416</v>
+      </c>
       <c r="D21" s="9">
-        <v>46198.79658900463</v>
+        <v>46206.55728555555</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -3183,10 +3197,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3920,7 +3934,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46191.169341932866</v>
+        <v>46206.556728298616</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -4097,7 +4111,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46189.16936783565</v>
+        <v>46206.55693574074</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4266,7 +4280,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46198.16913447916</v>
+        <v>46206.557276481486</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4488,7 +4502,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.1693375926</v>
+        <v>46206.55742607639</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46202.17884375</v>
+        <v>46209.16941291667</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>227</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.763318530095</v>
+        <v>46209.16941966435</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.76331560186</v>
+        <v>46209.169420833336</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.76331271991</v>
+        <v>46209.169414675926</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.763309710645</v>
+        <v>46209.1694077662</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>190</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.763306759254</v>
+        <v>46209.16940909722</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.76330359954</v>
+        <v>46209.16941032407</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.7633006713</v>
+        <v>46209.16941153935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.763297384256</v>
+        <v>46209.169415868055</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.763290891206</v>
+        <v>46209.169417094905</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>190</v>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.763290243056</v>
+        <v>46209.16941840277</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>190</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.76361657407</v>
+        <v>46209.17731128472</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>249</v>
@@ -6520,8 +6520,8 @@
       <c r="R80" s="5">
         <v>46216</v>
       </c>
-      <c r="S80" s="7" t="s">
-        <v>53</v>
+      <c r="S80" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46198.685312800924</v>
+        <v>46209.81560255787</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3821,9 +3821,11 @@
       <c r="B33" s="9">
         <v>46162.68139699074</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46209.81558148148</v>
+      </c>
       <c r="D33" s="9">
-        <v>46203.20693458333</v>
+        <v>46209.81560570602</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>127</v>
@@ -3871,10 +3873,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3884,9 +3886,11 @@
       <c r="B34" s="5">
         <v>46162.68140180556</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46209.81493861111</v>
+      </c>
       <c r="D34" s="5">
-        <v>46206.556728298616</v>
+        <v>46209.81552725694</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3943,9 +3947,11 @@
       <c r="B35" s="9">
         <v>46162.681406793985</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46209.815563553246</v>
+      </c>
       <c r="D35" s="9">
-        <v>46169.87710333333</v>
+        <v>46209.81556505787</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3998,9 +4004,11 @@
       <c r="B36" s="5">
         <v>46162.68146234954</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46209.81632271991</v>
+      </c>
       <c r="D36" s="5">
-        <v>46203.20693486111</v>
+        <v>46209.81633390047</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -4048,10 +4056,10 @@
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4061,9 +4069,11 @@
       <c r="B37" s="9">
         <v>46162.68146784722</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46209.81626413194</v>
+      </c>
       <c r="D37" s="9">
-        <v>46206.55693574074</v>
+        <v>46209.816265671296</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -4114,9 +4124,11 @@
       <c r="B38" s="5">
         <v>46162.68147298611</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46209.81630756945</v>
+      </c>
       <c r="D38" s="5">
-        <v>46202.16933497685</v>
+        <v>46209.816309050926</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -4167,9 +4179,11 @@
       <c r="B39" s="9">
         <v>46162.68149232639</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46209.81704866898</v>
+      </c>
       <c r="D39" s="9">
-        <v>46203.20693501158</v>
+        <v>46209.81705996528</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>146</v>
@@ -4217,10 +4231,10 @@
         <v>33</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4230,9 +4244,11 @@
       <c r="B40" s="5">
         <v>46162.68149587963</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46209.81661462963</v>
+      </c>
       <c r="D40" s="5">
-        <v>46206.55742607639</v>
+        <v>46209.81661650463</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>87</v>
@@ -4283,9 +4299,11 @@
       <c r="B41" s="9">
         <v>46162.6815003125</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46209.81703546296</v>
+      </c>
       <c r="D41" s="9">
-        <v>46202.169333576385</v>
+        <v>46209.81703686343</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>151</v>
@@ -5200,7 +5218,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46204.18876318287</v>
+        <v>46209.81557859953</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>190</v>
@@ -5248,8 +5266,8 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>101</v>
+      <c r="U58" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5322,7 +5340,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46204.188763275466</v>
+        <v>46209.81632625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>201</v>
@@ -5370,8 +5388,8 @@
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="11" t="s">
-        <v>101</v>
+      <c r="U60" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5444,7 +5462,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46204.18876412037</v>
+        <v>46209.81705302083</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>207</v>
@@ -5492,8 +5510,8 @@
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="11" t="s">
-        <v>101</v>
+      <c r="U62" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -697,61 +697,61 @@
     <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
+    <t>1214977534136624</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4327- ZVN 2-9-103/2,Generación OC </t>
+  </si>
+  <si>
+    <t>1214977534136649</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214977521376017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Generación OC ,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177507310</t>
+  </si>
+  <si>
+    <t>1214977177507495</t>
+  </si>
+  <si>
+    <t>1214977177507520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214977316993231</t>
+  </si>
+  <si>
+    <t>1214977521406360</t>
+  </si>
+  <si>
+    <t>1214977521406380</t>
+  </si>
+  <si>
+    <t>1214977521432284</t>
+  </si>
+  <si>
+    <t>1214977317011416</t>
+  </si>
+  <si>
+    <t>fABRICACIÓN</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977534136624</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4327- ZVN 2-9-103/2,Generación OC </t>
-  </si>
-  <si>
-    <t>1214977534136649</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214977521376017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Generación OC ,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177507310</t>
-  </si>
-  <si>
-    <t>1214977177507495</t>
-  </si>
-  <si>
-    <t>1214977177507520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214977316993231</t>
-  </si>
-  <si>
-    <t>1214977521406360</t>
-  </si>
-  <si>
-    <t>1214977521406380</t>
-  </si>
-  <si>
-    <t>1214977521432284</t>
-  </si>
-  <si>
-    <t>1214977317011416</t>
-  </si>
-  <si>
-    <t>fABRICACIÓN</t>
   </si>
   <si>
     <t>1214977317011431</t>
@@ -4354,9 +4354,11 @@
       <c r="B42" s="5">
         <v>46162.68117938658</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46210.52926681713</v>
+      </c>
       <c r="D42" s="5">
-        <v>46198.796516539354</v>
+        <v>46210.52928206019</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4391,9 +4393,11 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="12" t="s">
-        <v>75</v>
+      <c r="T42" s="6">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46209.723954456014</v>
+        <v>46210.18510166666</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>214</v>
@@ -5675,8 +5679,8 @@
       <c r="R65" s="9">
         <v>46209</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>218</v>
+      <c r="S65" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5687,7 +5691,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46162.68164390046</v>
@@ -5727,10 +5731,10 @@
         <v>214</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5740,7 +5744,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B67" s="9">
         <v>46162.681651203704</v>
@@ -5780,10 +5784,10 @@
         <v>214</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5793,7 +5797,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B68" s="5">
         <v>46162.68165733796</v>
@@ -5833,10 +5837,10 @@
         <v>214</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5846,7 +5850,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B69" s="9">
         <v>46162.68166336806</v>
@@ -5886,10 +5890,10 @@
         <v>214</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5899,7 +5903,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46162.68166935185</v>
@@ -5939,10 +5943,10 @@
         <v>214</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5952,7 +5956,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
         <v>46162.68167571759</v>
@@ -5992,7 +5996,7 @@
         <v>214</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>175</v>
@@ -6005,7 +6009,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46162.68168109954</v>
@@ -6045,7 +6049,7 @@
         <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>175</v>
@@ -6058,7 +6062,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B73" s="9">
         <v>46162.68168630787</v>
@@ -6098,7 +6102,7 @@
         <v>214</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>175</v>
@@ -6111,7 +6115,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B74" s="5">
         <v>46162.68169194444</v>
@@ -6151,7 +6155,7 @@
         <v>214</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>175</v>
@@ -6164,7 +6168,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B75" s="9">
         <v>46162.681698229164</v>
@@ -6204,7 +6208,7 @@
         <v>214</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>175</v>
@@ -6217,7 +6221,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B76" s="5">
         <v>46162.68171431713</v>
@@ -6227,7 +6231,7 @@
         <v>46209.724007199075</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6269,7 +6273,7 @@
         <v>46216</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -6317,7 +6321,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>238</v>
@@ -6370,7 +6374,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>238</v>
@@ -6423,7 +6427,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>238</v>
@@ -6476,7 +6480,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>238</v>
@@ -6529,7 +6533,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>175</v>
@@ -6582,7 +6586,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>175</v>
@@ -6635,7 +6639,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>175</v>
@@ -6688,7 +6692,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>175</v>
@@ -6741,7 +6745,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>175</v>
@@ -6794,7 +6798,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>175</v>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46209.72363071759</v>
+        <v>46210.17838744213</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>250</v>
@@ -6861,8 +6865,8 @@
       <c r="R87" s="9">
         <v>46217</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>53</v>
+      <c r="S87" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46162.76445266204</v>
+        <v>46212.189656875</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>294</v>
@@ -8328,8 +8328,8 @@
       <c r="R114" s="5">
         <v>46219</v>
       </c>
-      <c r="S114" s="7" t="s">
-        <v>53</v>
+      <c r="S114" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46209.81560255787</v>
+        <v>46212.656587488425</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3396,9 +3396,11 @@
       <c r="B26" s="5">
         <v>46162.68136241898</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46212.656571493055</v>
+      </c>
       <c r="D26" s="5">
-        <v>46192.853174930555</v>
+        <v>46212.65659090278</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>106</v>
@@ -3446,10 +3448,10 @@
         <v>53</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3459,9 +3461,11 @@
       <c r="B27" s="9">
         <v>46162.6813671412</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46212.656519537035</v>
+      </c>
       <c r="D27" s="9">
-        <v>46197.58788623843</v>
+        <v>46212.65652209491</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>109</v>
@@ -3518,9 +3522,11 @@
       <c r="B28" s="5">
         <v>46162.6813721875</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46212.65655465278</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.87699585648</v>
+        <v>46212.656557256945</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -7461,7 +7467,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46162.76398071759</v>
+        <v>46212.65657465278</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>268</v>
@@ -7509,8 +7515,8 @@
       <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="U99" s="11" t="s">
-        <v>101</v>
+      <c r="U99" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46213.5406209375</v>
+        <v>46216.169047187504</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>271</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46213.54021552083</v>
+        <v>46216.169049386575</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>166</v>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46213.54021490741</v>
+        <v>46216.16906072917</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>166</v>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46213.540214305554</v>
+        <v>46216.16905091435</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>166</v>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46213.54021369213</v>
+        <v>46216.169052384255</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>166</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46213.540213078704</v>
+        <v>46216.16906208333</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>166</v>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46213.540212430555</v>
+        <v>46216.16905809028</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>166</v>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46213.54021180556</v>
+        <v>46216.16905946759</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>166</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46213.54021119213</v>
+        <v>46216.169053923615</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>166</v>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46213.54021056713</v>
+        <v>46216.16905537037</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>166</v>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46213.54020991898</v>
+        <v>46216.16905674768</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>166</v>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46162.76477166667</v>
+        <v>46216.18689434028</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>368</v>
@@ -10934,8 +10934,8 @@
       <c r="R160" s="5">
         <v>46223</v>
       </c>
-      <c r="S160" s="7" t="s">
-        <v>54</v>
+      <c r="S160" s="12" t="s">
+        <v>272</v>
       </c>
       <c r="T160" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -889,49 +889,49 @@
     <t>armado</t>
   </si>
   <si>
+    <t>1214977317011431</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,check planos</t>
+  </si>
+  <si>
+    <t>armado,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977396149628</t>
+  </si>
+  <si>
+    <t>1214977317021218</t>
+  </si>
+  <si>
+    <t>1214977317021238</t>
+  </si>
+  <si>
+    <t>1214977396150148</t>
+  </si>
+  <si>
+    <t>1214977396047659</t>
+  </si>
+  <si>
+    <t>1214977396047669</t>
+  </si>
+  <si>
+    <t>1214977317053262</t>
+  </si>
+  <si>
+    <t>1214977317053272</t>
+  </si>
+  <si>
+    <t>1214977317053282</t>
+  </si>
+  <si>
+    <t>1214977521454380</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977317011431</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,check planos</t>
-  </si>
-  <si>
-    <t>armado,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977396149628</t>
-  </si>
-  <si>
-    <t>1214977317021218</t>
-  </si>
-  <si>
-    <t>1214977317021238</t>
-  </si>
-  <si>
-    <t>1214977396150148</t>
-  </si>
-  <si>
-    <t>1214977396047659</t>
-  </si>
-  <si>
-    <t>1214977396047669</t>
-  </si>
-  <si>
-    <t>1214977317053262</t>
-  </si>
-  <si>
-    <t>1214977317053272</t>
-  </si>
-  <si>
-    <t>1214977317053282</t>
-  </si>
-  <si>
-    <t>1214977521454380</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
   </si>
   <si>
     <t>1214977396176646</t>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46216.169047187504</v>
+        <v>46217.20388689815</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>271</v>
@@ -7692,8 +7692,8 @@
       <c r="R100" s="5">
         <v>46216</v>
       </c>
-      <c r="S100" s="12" t="s">
-        <v>272</v>
+      <c r="S100" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B101" s="9">
         <v>46162.681718935186</v>
@@ -7744,10 +7744,10 @@
         <v>271</v>
       </c>
       <c r="O101" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="P101" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7757,7 +7757,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B102" s="5">
         <v>46162.68172515046</v>
@@ -7797,10 +7797,10 @@
         <v>271</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B103" s="9">
         <v>46162.68173074074</v>
@@ -7850,10 +7850,10 @@
         <v>271</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>274</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>275</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B104" s="5">
         <v>46162.68173619213</v>
@@ -7903,10 +7903,10 @@
         <v>271</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B105" s="9">
         <v>46162.681741747685</v>
@@ -7959,7 +7959,7 @@
         <v>166</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B106" s="5">
         <v>46162.68178277778</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B107" s="9">
         <v>46162.68178671296</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>46162.68178976852</v>
@@ -8128,7 +8128,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B109" s="9">
         <v>46162.68179300926</v>
@@ -8181,7 +8181,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B110" s="5">
         <v>46162.68179625</v>
@@ -8234,17 +8234,17 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B111" s="9">
         <v>46162.681806875</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46213.540445</v>
+        <v>46217.16851451389</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8286,7 +8286,7 @@
         <v>46217</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="T111" s="10">
         <v>0</v>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46198.79656256945</v>
+        <v>46217.16850799769</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>166</v>
@@ -8334,10 +8334,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>288</v>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46198.79657365741</v>
+        <v>46217.168509375</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>166</v>
@@ -8387,10 +8387,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>288</v>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46198.79657413195</v>
+        <v>46217.16852262731</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>166</v>
@@ -8440,10 +8440,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>291</v>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46198.79657465278</v>
+        <v>46217.168524085646</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>166</v>
@@ -8493,10 +8493,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>291</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.763785347226</v>
+        <v>46217.16852547454</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>166</v>
@@ -8546,7 +8546,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>166</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46162.763782152775</v>
+        <v>46217.16850363426</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>166</v>
@@ -8599,7 +8599,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>166</v>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46162.76377949074</v>
+        <v>46217.168505208334</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>166</v>
@@ -8652,7 +8652,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>297</v>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46162.76377262731</v>
+        <v>46217.16850662037</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>166</v>
@@ -8705,7 +8705,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>166</v>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46162.76377197917</v>
+        <v>46217.16851664352</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>166</v>
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>166</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46162.7637712963</v>
+        <v>46217.16851827546</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>166</v>
@@ -8811,7 +8811,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>166</v>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46209.72420574074</v>
+        <v>46217.17476969908</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>316</v>
@@ -9155,8 +9155,8 @@
       <c r="R127" s="9">
         <v>46224</v>
       </c>
-      <c r="S127" s="7" t="s">
-        <v>54</v>
+      <c r="S127" s="12" t="s">
+        <v>286</v>
       </c>
       <c r="T127" s="10">
         <v>0</v>
@@ -9749,7 +9749,7 @@
         <v>46219</v>
       </c>
       <c r="S138" s="12" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="T138" s="6">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         <v>46220</v>
       </c>
       <c r="S149" s="12" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="T149" s="10">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         <v>46223</v>
       </c>
       <c r="S160" s="12" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="T160" s="6">
         <v>0</v>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46162.76494858797</v>
+        <v>46217.17476969908</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>388</v>
@@ -11527,8 +11527,8 @@
       <c r="R171" s="9">
         <v>46224</v>
       </c>
-      <c r="S171" s="7" t="s">
-        <v>54</v>
+      <c r="S171" s="12" t="s">
+        <v>286</v>
       </c>
       <c r="T171" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -706,6 +706,9 @@
     <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214977177405357</t>
   </si>
   <si>
@@ -929,9 +932,6 @@
   </si>
   <si>
     <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214977396176646</t>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.76230295139</v>
+        <v>46218.19777840278</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>207</v>
@@ -6066,8 +6066,8 @@
       <c r="R70" s="5">
         <v>46225</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>54</v>
+      <c r="S70" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B71" s="9">
         <v>46162.68153354166</v>
@@ -6119,7 +6119,7 @@
         <v>166</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B72" s="5">
         <v>46162.68153736111</v>
@@ -6170,7 +6170,7 @@
         <v>166</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B73" s="9">
         <v>46162.68154143519</v>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" s="5">
         <v>46162.68154440972</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B75" s="9">
         <v>46162.68154740741</v>
@@ -6333,7 +6333,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B76" s="5">
         <v>46162.68155047453</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B77" s="9">
         <v>46162.681552766204</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B78" s="5">
         <v>46162.68155516204</v>
@@ -6486,7 +6486,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B79" s="9">
         <v>46162.6815574537</v>
@@ -6537,7 +6537,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B80" s="5">
         <v>46162.68155952546</v>
@@ -6588,7 +6588,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B81" s="9">
         <v>46162.681598807874</v>
@@ -6598,7 +6598,7 @@
         <v>46162.707360960645</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>25</v>
@@ -6622,7 +6622,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>26</v>
@@ -6635,7 +6635,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B82" s="5">
         <v>46162.681602743054</v>
@@ -6645,16 +6645,16 @@
         <v>46209.81557859953</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6670,13 +6670,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q82" s="5">
         <v>46203</v>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B83" s="9">
         <v>46162.68160836806</v>
@@ -6706,16 +6706,16 @@
         <v>46205.173878229165</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6731,13 +6731,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q83" s="9">
         <v>46204</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B84" s="5">
         <v>46162.681615208334</v>
@@ -6767,16 +6767,16 @@
         <v>46209.81632625</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6792,13 +6792,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46203</v>
@@ -6818,7 +6818,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B85" s="9">
         <v>46162.68162069445</v>
@@ -6828,16 +6828,16 @@
         <v>46205.173878472226</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6853,13 +6853,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q85" s="9">
         <v>46204</v>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B86" s="5">
         <v>46162.681625983794</v>
@@ -6889,16 +6889,16 @@
         <v>46209.81705302083</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6914,13 +6914,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>152</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q86" s="5">
         <v>46203</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B87" s="9">
         <v>46162.68163075231</v>
@@ -6950,16 +6950,16 @@
         <v>46205.17387842592</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6975,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q87" s="9">
         <v>46204</v>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B88" s="5">
         <v>46162.68163611111</v>
@@ -7011,7 +7011,7 @@
         <v>46213.540516967594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -7035,7 +7035,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B89" s="9">
         <v>46162.6816390162</v>
@@ -7058,16 +7058,16 @@
         <v>46213.5405346412</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I89" s="9">
         <v>46205</v>
@@ -7085,13 +7085,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q89" s="9">
         <v>46205</v>
@@ -7111,7 +7111,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B90" s="5">
         <v>46162.68164390046</v>
@@ -7127,10 +7127,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I90" s="5">
         <v>46205</v>
@@ -7148,13 +7148,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B91" s="9">
         <v>46162.681651203704</v>
@@ -7180,10 +7180,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I91" s="9">
         <v>46205</v>
@@ -7201,13 +7201,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B92" s="5">
         <v>46162.68165733796</v>
@@ -7233,10 +7233,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I92" s="5">
         <v>46205</v>
@@ -7254,13 +7254,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B93" s="9">
         <v>46162.68166336806</v>
@@ -7286,10 +7286,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I93" s="9">
         <v>46205</v>
@@ -7307,13 +7307,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7323,7 +7323,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B94" s="5">
         <v>46162.68166935185</v>
@@ -7339,10 +7339,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I94" s="5">
         <v>46205</v>
@@ -7360,13 +7360,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7376,7 +7376,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B95" s="9">
         <v>46162.68167571759</v>
@@ -7392,10 +7392,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I95" s="9">
         <v>46205</v>
@@ -7413,10 +7413,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>166</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B96" s="5">
         <v>46162.68168109954</v>
@@ -7445,10 +7445,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I96" s="5">
         <v>46205</v>
@@ -7466,10 +7466,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>166</v>
@@ -7482,7 +7482,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B97" s="9">
         <v>46162.68168630787</v>
@@ -7498,10 +7498,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I97" s="9">
         <v>46205</v>
@@ -7519,10 +7519,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>166</v>
@@ -7535,7 +7535,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B98" s="5">
         <v>46162.68169194444</v>
@@ -7551,10 +7551,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I98" s="5">
         <v>46205</v>
@@ -7572,10 +7572,10 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>166</v>
@@ -7588,7 +7588,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B99" s="9">
         <v>46162.681698229164</v>
@@ -7604,10 +7604,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I99" s="9">
         <v>46205</v>
@@ -7625,10 +7625,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>166</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B100" s="5">
         <v>46162.68171431713</v>
@@ -7651,16 +7651,16 @@
         <v>46217.20388689815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I100" s="5">
         <v>46210</v>
@@ -7678,13 +7678,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q100" s="5">
         <v>46210</v>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B101" s="9">
         <v>46162.681718935186</v>
@@ -7720,10 +7720,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I101" s="9">
         <v>46210</v>
@@ -7741,13 +7741,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7757,7 +7757,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B102" s="5">
         <v>46162.68172515046</v>
@@ -7773,10 +7773,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I102" s="5">
         <v>46210</v>
@@ -7794,13 +7794,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7810,7 +7810,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B103" s="9">
         <v>46162.68173074074</v>
@@ -7826,10 +7826,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I103" s="9">
         <v>46210</v>
@@ -7847,13 +7847,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B104" s="5">
         <v>46162.68173619213</v>
@@ -7879,10 +7879,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I104" s="5">
         <v>46210</v>
@@ -7900,13 +7900,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B105" s="9">
         <v>46162.681741747685</v>
@@ -7932,10 +7932,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I105" s="9">
         <v>46210</v>
@@ -7953,13 +7953,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>166</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B106" s="5">
         <v>46162.68178277778</v>
@@ -7985,10 +7985,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I106" s="5">
         <v>46210</v>
@@ -8006,7 +8006,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>166</v>
@@ -8022,7 +8022,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B107" s="9">
         <v>46162.68178671296</v>
@@ -8038,10 +8038,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I107" s="9">
         <v>46210</v>
@@ -8059,7 +8059,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>166</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B108" s="5">
         <v>46162.68178976852</v>
@@ -8091,10 +8091,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I108" s="5">
         <v>46210</v>
@@ -8112,7 +8112,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>166</v>
@@ -8128,7 +8128,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B109" s="9">
         <v>46162.68179300926</v>
@@ -8144,10 +8144,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I109" s="9">
         <v>46210</v>
@@ -8165,7 +8165,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>166</v>
@@ -8181,7 +8181,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B110" s="5">
         <v>46162.68179625</v>
@@ -8197,10 +8197,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I110" s="5">
         <v>46210</v>
@@ -8218,7 +8218,7 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>166</v>
@@ -8234,26 +8234,26 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B111" s="9">
         <v>46162.681806875</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46217.16851451389</v>
+        <v>46218.194210347225</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I111" s="9">
         <v>46217</v>
@@ -8271,13 +8271,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q111" s="9">
         <v>46217</v>
@@ -8285,8 +8285,8 @@
       <c r="R111" s="9">
         <v>46217</v>
       </c>
-      <c r="S111" s="12" t="s">
-        <v>286</v>
+      <c r="S111" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T111" s="10">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I112" s="5">
         <v>46217</v>
@@ -8334,10 +8334,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>288</v>
@@ -8366,10 +8366,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I113" s="9">
         <v>46217</v>
@@ -8387,10 +8387,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>288</v>
@@ -8419,10 +8419,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I114" s="5">
         <v>46217</v>
@@ -8440,10 +8440,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>291</v>
@@ -8472,10 +8472,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I115" s="9">
         <v>46217</v>
@@ -8493,10 +8493,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>291</v>
@@ -8525,10 +8525,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I116" s="5">
         <v>46217</v>
@@ -8546,7 +8546,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>166</v>
@@ -8578,10 +8578,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I117" s="9">
         <v>46217</v>
@@ -8599,7 +8599,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>166</v>
@@ -8631,10 +8631,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8652,7 +8652,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>297</v>
@@ -8684,10 +8684,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I119" s="9">
         <v>46217</v>
@@ -8705,7 +8705,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>166</v>
@@ -8737,10 +8737,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>166</v>
@@ -8790,10 +8790,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I121" s="9">
         <v>46217</v>
@@ -8811,7 +8811,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>166</v>
@@ -8837,7 +8837,7 @@
         <v>46162.708598171295</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>25</v>
@@ -8890,10 +8890,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
@@ -8909,7 +8909,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>113</v>
@@ -8951,10 +8951,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8970,7 +8970,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>104</v>
@@ -9012,10 +9012,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I125" s="10"/>
       <c r="J125" s="9">
@@ -9031,7 +9031,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>122</v>
@@ -9144,7 +9144,7 @@
         <v>313</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>313</v>
@@ -9156,7 +9156,7 @@
         <v>46224</v>
       </c>
       <c r="S127" s="12" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="T127" s="10">
         <v>0</v>
@@ -9737,7 +9737,7 @@
         <v>313</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>313</v>
@@ -9749,7 +9749,7 @@
         <v>46219</v>
       </c>
       <c r="S138" s="12" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="T138" s="6">
         <v>0</v>
@@ -10330,7 +10330,7 @@
         <v>313</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>313</v>
@@ -10342,7 +10342,7 @@
         <v>46220</v>
       </c>
       <c r="S149" s="12" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="T149" s="10">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>313</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>313</v>
@@ -10935,7 +10935,7 @@
         <v>46223</v>
       </c>
       <c r="S160" s="12" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="T160" s="6">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>313</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>313</v>
@@ -11528,7 +11528,7 @@
         <v>46224</v>
       </c>
       <c r="S171" s="12" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="T171" s="10">
         <v>0</v>
@@ -12109,7 +12109,7 @@
         <v>313</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>403</v>
@@ -13322,7 +13322,7 @@
         <v>417</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P205" s="10" t="s">
         <v>417</v>
@@ -13891,10 +13891,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I216" s="5">
         <v>46231</v>
@@ -13915,7 +13915,7 @@
         <v>417</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>417</v>
@@ -13954,10 +13954,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I217" s="9">
         <v>46231</v>
@@ -14007,10 +14007,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I218" s="5">
         <v>46231</v>
@@ -14060,10 +14060,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I219" s="9">
         <v>46231</v>
@@ -14113,10 +14113,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I220" s="5">
         <v>46231</v>
@@ -14166,10 +14166,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14219,10 +14219,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I222" s="5">
         <v>46231</v>
@@ -14272,10 +14272,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I223" s="9">
         <v>46231</v>
@@ -14325,10 +14325,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I224" s="5">
         <v>46231</v>
@@ -14378,10 +14378,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I225" s="9">
         <v>46231</v>
@@ -14431,10 +14431,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I226" s="5">
         <v>46231</v>
@@ -14484,10 +14484,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I227" s="9">
         <v>46232</v>
@@ -14508,7 +14508,7 @@
         <v>417</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P227" s="10" t="s">
         <v>467</v>
@@ -14547,10 +14547,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I228" s="5">
         <v>46232</v>
@@ -14600,10 +14600,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I229" s="9">
         <v>46232</v>
@@ -14653,10 +14653,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I230" s="5">
         <v>46232</v>
@@ -14706,10 +14706,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I231" s="9">
         <v>46232</v>
@@ -14759,10 +14759,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I232" s="5">
         <v>46232</v>
@@ -14812,10 +14812,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I233" s="9">
         <v>46232</v>
@@ -14865,10 +14865,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14918,10 +14918,10 @@
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H235" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14971,10 +14971,10 @@
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -15024,10 +15024,10 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H237" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46162.7651559838</v>
+        <v>46219.19163878472</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>399</v>
@@ -11989,8 +11989,8 @@
       <c r="R182" s="5">
         <v>46226</v>
       </c>
-      <c r="S182" s="7" t="s">
-        <v>54</v>
+      <c r="S182" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="T182" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46212.189656875</v>
+        <v>46220.19967811342</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>327</v>
@@ -9705,8 +9705,8 @@
       <c r="R138" s="5">
         <v>46219</v>
       </c>
-      <c r="S138" s="12" t="s">
-        <v>208</v>
+      <c r="S138" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T138" s="6">
         <v>0</v>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46162.76537538195</v>
+        <v>46220.17480689815</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>417</v>
@@ -12589,8 +12589,8 @@
       <c r="R194" s="5">
         <v>46227</v>
       </c>
-      <c r="S194" s="7" t="s">
-        <v>54</v>
+      <c r="S194" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="T194" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46213.17565130787</v>
+        <v>46221.18939354167</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>346</v>
@@ -10276,8 +10276,8 @@
       <c r="R149" s="9">
         <v>46220</v>
       </c>
-      <c r="S149" s="12" t="s">
-        <v>208</v>
+      <c r="S149" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T149" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2740" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="485">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46223.20048721065</v>
+        <v>46223.83588414352</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>435</v>
@@ -13292,9 +13292,11 @@
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H205" s="10"/>
+        <v>74</v>
+      </c>
+      <c r="H205" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="I205" s="9">
         <v>46230</v>
       </c>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -9105,7 +9105,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46223.57819331018</v>
+        <v>46224.250435208334</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>314</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46223.57707488426</v>
+        <v>46224.25041532407</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>165</v>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46223.577074189816</v>
+        <v>46224.2504165625</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>165</v>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46223.57707353009</v>
+        <v>46224.25041792824</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>165</v>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46223.57707289352</v>
+        <v>46224.25041925926</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>165</v>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46223.577072280095</v>
+        <v>46224.25043248842</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>165</v>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46223.57707167824</v>
+        <v>46224.25043388889</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>165</v>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46223.57707101852</v>
+        <v>46224.25042052083</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>165</v>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46223.577070405096</v>
+        <v>46224.25042207176</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>165</v>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46223.57706981481</v>
+        <v>46224.25042332176</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>165</v>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46223.57706916667</v>
+        <v>46224.25042453704</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>165</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46223.57819107639</v>
+        <v>46224.20299456018</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>366</v>
@@ -10928,8 +10928,8 @@
       <c r="R160" s="5">
         <v>46223</v>
       </c>
-      <c r="S160" s="12" t="s">
-        <v>157</v>
+      <c r="S160" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T160" s="6">
         <v>0</v>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46223.57819018519</v>
+        <v>46224.25040923611</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>386</v>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46223.577957974536</v>
+        <v>46224.25041123843</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>165</v>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46223.5779572801</v>
+        <v>46224.250425844904</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>165</v>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46223.577956608795</v>
+        <v>46224.2504271412</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>165</v>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46223.57795594908</v>
+        <v>46224.25041263889</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>165</v>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46223.57795528935</v>
+        <v>46224.25041399305</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>165</v>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46223.57795460648</v>
+        <v>46224.25042840278</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>165</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46223.57795395833</v>
+        <v>46224.250429583335</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>165</v>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46223.577953252316</v>
+        <v>46224.2504365162</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>165</v>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46223.57795261574</v>
+        <v>46224.25043774306</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>165</v>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46223.57795194445</v>
+        <v>46224.25043097222</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>165</v>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46162.76653042824</v>
+        <v>46224.188705671295</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>449</v>
@@ -13920,8 +13920,8 @@
       <c r="R216" s="5">
         <v>46231</v>
       </c>
-      <c r="S216" s="7" t="s">
-        <v>54</v>
+      <c r="S216" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="T216" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -8616,7 +8616,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46217.168505208334</v>
+        <v>46224.87647668982</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>165</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -6018,7 +6018,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46218.19777840278</v>
+        <v>46225.168406944445</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>206</v>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46162.76229798611</v>
+        <v>46225.16840908564</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>165</v>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46162.76229449074</v>
+        <v>46225.168410370374</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>165</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46162.76229145833</v>
+        <v>46225.168411516206</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>165</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46162.76228877315</v>
+        <v>46225.168412743056</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>165</v>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46162.76228596065</v>
+        <v>46225.16841392361</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>165</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46162.762282870375</v>
+        <v>46225.16841503472</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>165</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46162.76227917824</v>
+        <v>46225.168416203705</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>165</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46162.76227634259</v>
+        <v>46225.168417361114</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>165</v>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46162.7622690162</v>
+        <v>46225.16841868055</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>165</v>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46162.762268391205</v>
+        <v>46225.16842006944</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>165</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46224.250435208334</v>
+        <v>46225.16960298611</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>314</v>
@@ -9149,8 +9149,8 @@
       <c r="R127" s="9">
         <v>46224</v>
       </c>
-      <c r="S127" s="12" t="s">
-        <v>157</v>
+      <c r="S127" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T127" s="10">
         <v>0</v>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46224.25040923611</v>
+        <v>46225.16960282407</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>386</v>
@@ -11521,8 +11521,8 @@
       <c r="R171" s="9">
         <v>46224</v>
       </c>
-      <c r="S171" s="12" t="s">
-        <v>157</v>
+      <c r="S171" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T171" s="10">
         <v>0</v>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46162.76671087963</v>
+        <v>46225.178812060185</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>464</v>
@@ -14513,8 +14513,8 @@
       <c r="R227" s="9">
         <v>46232</v>
       </c>
-      <c r="S227" s="7" t="s">
-        <v>54</v>
+      <c r="S227" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="T227" s="10">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -6021,7 +6021,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.168406944445</v>
+        <v>46226.17749263889</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>207</v>
@@ -6063,8 +6063,8 @@
       <c r="R70" s="5">
         <v>46225</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>158</v>
+      <c r="S70" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46223.578189594904</v>
+        <v>46226.16815858796</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>401</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46223.57811456019</v>
+        <v>46226.168160671295</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>166</v>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46223.57811398148</v>
+        <v>46226.16816204861</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>166</v>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46223.57811340278</v>
+        <v>46226.16816368056</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>166</v>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46223.578112766205</v>
+        <v>46226.16816538194</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>166</v>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46223.578112187504</v>
+        <v>46226.16816987269</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>166</v>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46223.57811162037</v>
+        <v>46226.16815111111</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>166</v>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46223.57811101852</v>
+        <v>46226.168152708335</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>166</v>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46223.57811043982</v>
+        <v>46226.16815416666</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>166</v>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46223.57810986111</v>
+        <v>46226.16815575231</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>166</v>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46223.5781092824</v>
+        <v>46226.16815724537</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>166</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46223.20048630787</v>
+        <v>46230.17140546296</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4552,9 +4552,11 @@
       <c r="B43" s="9">
         <v>46213.54075649305</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9">
+        <v>46227.62044760417</v>
+      </c>
       <c r="D43" s="9">
-        <v>46213.54953929398</v>
+        <v>46227.62045023148</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4605,9 +4607,11 @@
       <c r="B44" s="5">
         <v>46213.54081322916</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46227.62052016203</v>
+      </c>
       <c r="D44" s="5">
-        <v>46213.54592954861</v>
+        <v>46227.620521689816</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4660,7 +4664,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46213.54651274305</v>
+        <v>46227.62045711806</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>166</v>
@@ -4713,7 +4717,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46213.54664486111</v>
+        <v>46227.620457893514</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4766,7 +4770,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46213.54677894676</v>
+        <v>46227.620458634265</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>166</v>
@@ -4819,7 +4823,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46213.5469336574</v>
+        <v>46227.62045965278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>166</v>
@@ -4872,7 +4876,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46213.54740284722</v>
+        <v>46227.62046045139</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>166</v>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46213.547545891204</v>
+        <v>46227.6204612037</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>166</v>
@@ -4978,7 +4982,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46213.547717118054</v>
+        <v>46227.62046199074</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>166</v>
@@ -5031,7 +5035,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46213.54787296296</v>
+        <v>46227.62046280093</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>166</v>
@@ -5084,7 +5088,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46213.54802452546</v>
+        <v>46227.62046361111</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>166</v>
@@ -5137,7 +5141,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46213.54814745371</v>
+        <v>46227.62046460648</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>166</v>
@@ -5190,7 +5194,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46213.548271990745</v>
+        <v>46227.62046534722</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>177</v>
@@ -5243,7 +5247,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46213.54841328703</v>
+        <v>46227.62046612268</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>177</v>
@@ -5296,7 +5300,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46213.54856065972</v>
+        <v>46227.62046690972</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>180</v>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46213.54868125</v>
+        <v>46227.620467870365</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -5402,7 +5406,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46213.548798958334</v>
+        <v>46227.6204687037</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>177</v>
@@ -5455,7 +5459,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46213.54894163195</v>
+        <v>46227.62046957176</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>177</v>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46213.54907178241</v>
+        <v>46227.620470381946</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>177</v>
@@ -5561,7 +5565,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46213.54930521991</v>
+        <v>46227.6204712037</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>177</v>
@@ -5614,7 +5618,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46213.54943423611</v>
+        <v>46227.620472002316</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>177</v>
@@ -5667,7 +5671,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46213.54953907407</v>
+        <v>46227.620472951385</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>177</v>
@@ -5720,7 +5724,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46213.543864907406</v>
+        <v>46230.17140723379</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>189</v>
@@ -12073,7 +12077,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46226.16815858796</v>
+        <v>46227.198019351854</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>401</v>
@@ -12117,8 +12121,8 @@
       <c r="R182" s="5">
         <v>46226</v>
       </c>
-      <c r="S182" s="12" t="s">
-        <v>158</v>
+      <c r="S182" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T182" s="6">
         <v>0</v>
@@ -12693,7 +12697,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46220.17480689815</v>
+        <v>46228.19797770833</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>419</v>
@@ -12737,8 +12741,8 @@
       <c r="R194" s="5">
         <v>46227</v>
       </c>
-      <c r="S194" s="12" t="s">
-        <v>158</v>
+      <c r="S194" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T194" s="6">
         <v>0</v>
@@ -12756,7 +12760,7 @@
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46162.76536123843</v>
+        <v>46227.168892430556</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>166</v>
@@ -12809,7 +12813,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46162.76535802083</v>
+        <v>46227.16883238426</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>166</v>
@@ -12862,7 +12866,7 @@
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46162.76535458333</v>
+        <v>46227.16883634259</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>166</v>
@@ -12915,7 +12919,7 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46162.76535162037</v>
+        <v>46227.16883768518</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>166</v>
@@ -12968,7 +12972,7 @@
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46162.765348796296</v>
+        <v>46227.16884165509</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>166</v>
@@ -13021,7 +13025,7 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46162.765344976855</v>
+        <v>46227.16884313658</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>166</v>
@@ -13074,7 +13078,7 @@
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46162.765340763886</v>
+        <v>46227.16888855324</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>166</v>
@@ -13127,7 +13131,7 @@
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46162.765337488425</v>
+        <v>46227.168889884255</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>166</v>
@@ -13180,7 +13184,7 @@
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46162.76533056713</v>
+        <v>46227.16889119213</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>166</v>
@@ -13233,7 +13237,7 @@
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46162.76532990741</v>
+        <v>46227.16884428241</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>166</v>
@@ -13286,7 +13290,7 @@
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46223.83588414352</v>
+        <v>46230.168793634264</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>436</v>
@@ -13349,7 +13353,7 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46223.578334363425</v>
+        <v>46230.168786319446</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>166</v>
@@ -13402,7 +13406,7 @@
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46223.57833366898</v>
+        <v>46230.168788043986</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>166</v>
@@ -13455,7 +13459,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46223.578333020836</v>
+        <v>46230.1687662037</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>166</v>
@@ -13508,7 +13512,7 @@
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46223.57833239583</v>
+        <v>46230.16876739584</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>166</v>
@@ -13561,7 +13565,7 @@
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46223.57833175926</v>
+        <v>46230.1687893287</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>166</v>
@@ -13614,7 +13618,7 @@
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46223.578331122684</v>
+        <v>46230.168790578704</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>166</v>
@@ -13667,7 +13671,7 @@
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46223.57833042824</v>
+        <v>46230.16876855324</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>166</v>
@@ -13720,7 +13724,7 @@
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46223.57832976852</v>
+        <v>46230.16876962963</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>166</v>
@@ -13773,7 +13777,7 @@
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46223.5783290625</v>
+        <v>46230.16877107639</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>166</v>
@@ -13826,7 +13830,7 @@
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46223.57832832176</v>
+        <v>46230.16876494213</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>166</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -547,883 +547,883 @@
     <t xml:space="preserve">Generación OC ,ARMADO,CONTROL DE CALIDAD </t>
   </si>
   <si>
+    <t>1216451278926598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC </t>
+  </si>
+  <si>
+    <t>Fabricación externa,ARMADO,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLAOT ,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA</t>
+  </si>
+  <si>
+    <t>1216451278926599</t>
+  </si>
+  <si>
+    <t>ARMADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa,CONTROL DE CALIDAD </t>
+  </si>
+  <si>
+    <t>1216451278926616</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1216451278926617</t>
+  </si>
+  <si>
+    <t>1216451278926618</t>
+  </si>
+  <si>
+    <t>1216451278926620</t>
+  </si>
+  <si>
+    <t>1216451278926619</t>
+  </si>
+  <si>
+    <t>1216451278926621</t>
+  </si>
+  <si>
+    <t>1216451278926622</t>
+  </si>
+  <si>
+    <t>1216451278926623</t>
+  </si>
+  <si>
+    <t>1216451278926624</t>
+  </si>
+  <si>
+    <t>1216451278926625</t>
+  </si>
+  <si>
+    <t>1216451278926637</t>
+  </si>
+  <si>
+    <t>OT 4327- CONDUNTO REJILLA</t>
+  </si>
+  <si>
+    <t>1216451278926638</t>
+  </si>
+  <si>
+    <t>1216451278926639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4327- CONDUNTO REJILLAOT </t>
+  </si>
+  <si>
+    <t>1216451278926640</t>
+  </si>
+  <si>
+    <t>1216451278926641</t>
+  </si>
+  <si>
+    <t>1216451278926642</t>
+  </si>
+  <si>
+    <t>1216451278926643</t>
+  </si>
+  <si>
+    <t>1216451278926644</t>
+  </si>
+  <si>
+    <t>1216451278926645</t>
+  </si>
+  <si>
+    <t>1216451278926646</t>
+  </si>
+  <si>
+    <t>1216451278926600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL DE CALIDAD </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214969047720960</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977075856742</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214977521258828</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT4327</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214977521270201</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Propuesta Mecanizado OT4327,Propuesta Fabricación externa  OT4327,propuesta Corte Laser OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405347</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405357</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177405367</t>
+  </si>
+  <si>
+    <t>1214977316866399</t>
+  </si>
+  <si>
+    <t>1214977316866404</t>
+  </si>
+  <si>
+    <t>1214977316866409</t>
+  </si>
+  <si>
+    <t>1214977316866414</t>
+  </si>
+  <si>
+    <t>1214977316866419</t>
+  </si>
+  <si>
+    <t>1214977316884296</t>
+  </si>
+  <si>
+    <t>1214977316884301</t>
+  </si>
+  <si>
+    <t>1214977316884306</t>
+  </si>
+  <si>
+    <t>1214977316832250</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214977316832260</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214977075952529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177463236</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214977177463256</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977534119621</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214977534119636</t>
+  </si>
+  <si>
+    <t>1214977521366438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldereria </t>
+  </si>
+  <si>
+    <t>armado,Control de calidad Armado,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1214977521366448</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977534136624</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1214977534136649</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214977521376017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparacion materiales,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177507310</t>
+  </si>
+  <si>
+    <t>1214977177507495</t>
+  </si>
+  <si>
+    <t>1214977177507520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214977316993231</t>
+  </si>
+  <si>
+    <t>1214977521406360</t>
+  </si>
+  <si>
+    <t>1214977521406380</t>
+  </si>
+  <si>
+    <t>1214977521432284</t>
+  </si>
+  <si>
+    <t>1214977317011416</t>
+  </si>
+  <si>
+    <t>armado</t>
+  </si>
+  <si>
+    <t>1214977317011431</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,check planos</t>
+  </si>
+  <si>
+    <t>armado,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977396149628</t>
+  </si>
+  <si>
+    <t>1214977317021218</t>
+  </si>
+  <si>
+    <t>1214977317021238</t>
+  </si>
+  <si>
+    <t>1214977396150148</t>
+  </si>
+  <si>
+    <t>1214977396047659</t>
+  </si>
+  <si>
+    <t>1214977396047669</t>
+  </si>
+  <si>
+    <t>1214977317053262</t>
+  </si>
+  <si>
+    <t>1214977317053272</t>
+  </si>
+  <si>
+    <t>1214977317053282</t>
+  </si>
+  <si>
+    <t>1214977521454380</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214977396176646</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Control de calidad Armado,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214977396176666</t>
+  </si>
+  <si>
+    <t>1214977534255453</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214977534263794</t>
+  </si>
+  <si>
+    <t>1214977534263814</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4327- ZVN 2-9-103/2,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214977317069415</t>
+  </si>
+  <si>
+    <t>1214977317069425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214977317069435</t>
+  </si>
+  <si>
+    <t>1214977521509527</t>
+  </si>
+  <si>
+    <t>1214977521509537</t>
+  </si>
+  <si>
+    <t>1214977396208180</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214977396208190</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977396208468</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317091106</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977534318855</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje Alabe,Revestimiento,Montaje Rodete,Montaje motor,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214977534318865</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>1214977317097556</t>
+  </si>
+  <si>
+    <t>1214977396236831</t>
+  </si>
+  <si>
+    <t>1214977396236846</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977396236861</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214977521557062</t>
+  </si>
+  <si>
+    <t>1214977521557072</t>
+  </si>
+  <si>
+    <t>1214977396248241</t>
+  </si>
+  <si>
+    <t>1214977396248251</t>
+  </si>
+  <si>
+    <t>1214977396248261</t>
+  </si>
+  <si>
+    <t>1214977396248271</t>
+  </si>
+  <si>
+    <t>1214977317089826</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214977317089841</t>
+  </si>
+  <si>
+    <t>check planos,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214977534427350</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>1214977521630165</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,OT 4327- ZVN 2-9-103/2,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977521630190</t>
+  </si>
+  <si>
+    <t>1214977177729562</t>
+  </si>
+  <si>
+    <t>1214977317163223</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>1214977317163243</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214977317163423</t>
+  </si>
+  <si>
+    <t>1214977396359668</t>
+  </si>
+  <si>
+    <t>1214977396359688</t>
+  </si>
+  <si>
+    <t>1214977317191535</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214977317191550</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,check planos,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317199936</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214977521698437</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214977177785853</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177785878</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177787037</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214977177787052</t>
+  </si>
+  <si>
+    <t>1214977521723607</t>
+  </si>
+  <si>
+    <t>1214977521723622</t>
+  </si>
+  <si>
+    <t>1214977521739323</t>
+  </si>
+  <si>
+    <t>1214977317209893</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214977317209908</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Montaje motor</t>
+  </si>
+  <si>
+    <t>1214977521756155</t>
+  </si>
+  <si>
+    <t>1214977396431180</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214977396431205</t>
+  </si>
+  <si>
+    <t>check planos,OT 4327- ZVN 2-9-103/2,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214977317199967</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317199982</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Recepcion motor</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977534622331</t>
+  </si>
+  <si>
+    <t>1214977521818921</t>
+  </si>
+  <si>
+    <t>1214977521818941</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317325436</t>
+  </si>
+  <si>
+    <t>1214977177893872</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214977177893887</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977396504992</t>
+  </si>
+  <si>
+    <t>1214977396505012</t>
+  </si>
+  <si>
+    <t>1214977177904480</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214977177904500</t>
+  </si>
+  <si>
+    <t>1214977396507229</t>
+  </si>
+  <si>
+    <t>1214977396507239</t>
+  </si>
+  <si>
+    <t>1214977534658490</t>
+  </si>
+  <si>
+    <t>1214977534658500</t>
+  </si>
+  <si>
+    <t>1214977396532079</t>
+  </si>
+  <si>
+    <t>1214977521842444</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
+    <t>1214977521842459</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214977521865482</t>
+  </si>
+  <si>
+    <t>1214977521865497</t>
+  </si>
+  <si>
+    <t>1214977521865512</t>
+  </si>
+  <si>
+    <t>1214977534681571</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977177909228</t>
+  </si>
+  <si>
+    <t>1214977177909238</t>
+  </si>
+  <si>
+    <t>1214977177909248</t>
+  </si>
+  <si>
+    <t>1214977396586693</t>
+  </si>
+  <si>
+    <t>1214977396586703</t>
+  </si>
+  <si>
+    <t>1214977396590869</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,PACKING LIST,Despacho,Embalaje</t>
+  </si>
+  <si>
+    <t>1214977396590879</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317463499</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317463514</t>
+  </si>
+  <si>
+    <t>1214977396631142</t>
+  </si>
+  <si>
+    <t>1214977396631157</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214977534721000</t>
+  </si>
+  <si>
+    <t>1214977534721015</t>
+  </si>
+  <si>
+    <t>1214977178000429</t>
+  </si>
+  <si>
+    <t>1214977178000439</t>
+  </si>
+  <si>
+    <t>1214977178000449</t>
+  </si>
+  <si>
+    <t>1214977534731518</t>
+  </si>
+  <si>
+    <t>1214977534731548</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>1214977521967452</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977521967467</t>
+  </si>
+  <si>
+    <t>1214977396652350</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,Embalaje</t>
+  </si>
+  <si>
+    <t>1214977396652365</t>
+  </si>
+  <si>
+    <t>1214977521980129</t>
+  </si>
+  <si>
+    <t>1214977521980144</t>
+  </si>
+  <si>
+    <t>1214977396668053</t>
+  </si>
+  <si>
+    <t>1214977396668063</t>
+  </si>
+  <si>
+    <t>1214977396668073</t>
+  </si>
+  <si>
+    <t>1214977317525369</t>
+  </si>
+  <si>
+    <t>1214977317525399</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216451278926598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC </t>
-  </si>
-  <si>
-    <t>Fabricación externa,ARMADO,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLAOT ,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA,OT 4327- CONDUNTO REJILLA</t>
-  </si>
-  <si>
-    <t>1216451278926599</t>
-  </si>
-  <si>
-    <t>ARMADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa,CONTROL DE CALIDAD </t>
-  </si>
-  <si>
-    <t>1216451278926616</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1216451278926617</t>
-  </si>
-  <si>
-    <t>1216451278926618</t>
-  </si>
-  <si>
-    <t>1216451278926620</t>
-  </si>
-  <si>
-    <t>1216451278926619</t>
-  </si>
-  <si>
-    <t>1216451278926621</t>
-  </si>
-  <si>
-    <t>1216451278926622</t>
-  </si>
-  <si>
-    <t>1216451278926623</t>
-  </si>
-  <si>
-    <t>1216451278926624</t>
-  </si>
-  <si>
-    <t>1216451278926625</t>
-  </si>
-  <si>
-    <t>1216451278926637</t>
-  </si>
-  <si>
-    <t>OT 4327- CONDUNTO REJILLA</t>
-  </si>
-  <si>
-    <t>1216451278926638</t>
-  </si>
-  <si>
-    <t>1216451278926639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4327- CONDUNTO REJILLAOT </t>
-  </si>
-  <si>
-    <t>1216451278926640</t>
-  </si>
-  <si>
-    <t>1216451278926641</t>
-  </si>
-  <si>
-    <t>1216451278926642</t>
-  </si>
-  <si>
-    <t>1216451278926643</t>
-  </si>
-  <si>
-    <t>1216451278926644</t>
-  </si>
-  <si>
-    <t>1216451278926645</t>
-  </si>
-  <si>
-    <t>1216451278926646</t>
-  </si>
-  <si>
-    <t>1216451278926600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL DE CALIDAD </t>
-  </si>
-  <si>
-    <t>1214969047720960</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977075856742</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214977521258828</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT4327</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214977521270201</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Propuesta Mecanizado OT4327,Propuesta Fabricación externa  OT4327,propuesta Corte Laser OT4327,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405347</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405357</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177405367</t>
-  </si>
-  <si>
-    <t>1214977316866399</t>
-  </si>
-  <si>
-    <t>1214977316866404</t>
-  </si>
-  <si>
-    <t>1214977316866409</t>
-  </si>
-  <si>
-    <t>1214977316866414</t>
-  </si>
-  <si>
-    <t>1214977316866419</t>
-  </si>
-  <si>
-    <t>1214977316884296</t>
-  </si>
-  <si>
-    <t>1214977316884301</t>
-  </si>
-  <si>
-    <t>1214977316884306</t>
-  </si>
-  <si>
-    <t>1214977316832250</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214977316832260</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214977075952529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177463236</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214977177463256</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977534119621</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214977534119636</t>
-  </si>
-  <si>
-    <t>1214977521366438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldereria </t>
-  </si>
-  <si>
-    <t>armado,Control de calidad Armado,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1214977521366448</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977534136624</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1214977534136649</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214977521376017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparacion materiales,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177507310</t>
-  </si>
-  <si>
-    <t>1214977177507495</t>
-  </si>
-  <si>
-    <t>1214977177507520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214977316993231</t>
-  </si>
-  <si>
-    <t>1214977521406360</t>
-  </si>
-  <si>
-    <t>1214977521406380</t>
-  </si>
-  <si>
-    <t>1214977521432284</t>
-  </si>
-  <si>
-    <t>1214977317011416</t>
-  </si>
-  <si>
-    <t>armado</t>
-  </si>
-  <si>
-    <t>1214977317011431</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,check planos</t>
-  </si>
-  <si>
-    <t>armado,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977396149628</t>
-  </si>
-  <si>
-    <t>1214977317021218</t>
-  </si>
-  <si>
-    <t>1214977317021238</t>
-  </si>
-  <si>
-    <t>1214977396150148</t>
-  </si>
-  <si>
-    <t>1214977396047659</t>
-  </si>
-  <si>
-    <t>1214977396047669</t>
-  </si>
-  <si>
-    <t>1214977317053262</t>
-  </si>
-  <si>
-    <t>1214977317053272</t>
-  </si>
-  <si>
-    <t>1214977317053282</t>
-  </si>
-  <si>
-    <t>1214977521454380</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214977396176646</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Control de calidad Armado,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214977396176666</t>
-  </si>
-  <si>
-    <t>1214977534255453</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214977534263794</t>
-  </si>
-  <si>
-    <t>1214977534263814</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4327- ZVN 2-9-103/2,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214977317069415</t>
-  </si>
-  <si>
-    <t>1214977317069425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT7 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214977317069435</t>
-  </si>
-  <si>
-    <t>1214977521509527</t>
-  </si>
-  <si>
-    <t>1214977521509537</t>
-  </si>
-  <si>
-    <t>1214977396208180</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214977396208190</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977396208468</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317091106</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977534318855</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje Alabe,Revestimiento,Montaje Rodete,Montaje motor,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214977534318865</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>1214977317097556</t>
-  </si>
-  <si>
-    <t>1214977396236831</t>
-  </si>
-  <si>
-    <t>1214977396236846</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977396236861</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214977521557062</t>
-  </si>
-  <si>
-    <t>1214977521557072</t>
-  </si>
-  <si>
-    <t>1214977396248241</t>
-  </si>
-  <si>
-    <t>1214977396248251</t>
-  </si>
-  <si>
-    <t>1214977396248261</t>
-  </si>
-  <si>
-    <t>1214977396248271</t>
-  </si>
-  <si>
-    <t>1214977317089826</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214977317089841</t>
-  </si>
-  <si>
-    <t>check planos,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214977534427350</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>1214977521630165</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,OT 4327- ZVN 2-9-103/2,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977521630190</t>
-  </si>
-  <si>
-    <t>1214977177729562</t>
-  </si>
-  <si>
-    <t>1214977317163223</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>1214977317163243</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214977317163423</t>
-  </si>
-  <si>
-    <t>1214977396359668</t>
-  </si>
-  <si>
-    <t>1214977396359688</t>
-  </si>
-  <si>
-    <t>1214977317191535</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214977317191550</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,check planos,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317199936</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214977521698437</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214977177785853</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177785878</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177787037</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214977177787052</t>
-  </si>
-  <si>
-    <t>1214977521723607</t>
-  </si>
-  <si>
-    <t>1214977521723622</t>
-  </si>
-  <si>
-    <t>1214977521739323</t>
-  </si>
-  <si>
-    <t>1214977317209893</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214977317209908</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Montaje motor</t>
-  </si>
-  <si>
-    <t>1214977521756155</t>
-  </si>
-  <si>
-    <t>1214977396431180</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214977396431205</t>
-  </si>
-  <si>
-    <t>check planos,OT 4327- ZVN 2-9-103/2,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214977317199967</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317199982</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Recepcion motor</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977534622331</t>
-  </si>
-  <si>
-    <t>1214977521818921</t>
-  </si>
-  <si>
-    <t>1214977521818941</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317325436</t>
-  </si>
-  <si>
-    <t>1214977177893872</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214977177893887</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977396504992</t>
-  </si>
-  <si>
-    <t>1214977396505012</t>
-  </si>
-  <si>
-    <t>1214977177904480</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214977177904500</t>
-  </si>
-  <si>
-    <t>1214977396507229</t>
-  </si>
-  <si>
-    <t>1214977396507239</t>
-  </si>
-  <si>
-    <t>1214977534658490</t>
-  </si>
-  <si>
-    <t>1214977534658500</t>
-  </si>
-  <si>
-    <t>1214977396532079</t>
-  </si>
-  <si>
-    <t>1214977521842444</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
-  </si>
-  <si>
-    <t>1214977521842459</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214977521865482</t>
-  </si>
-  <si>
-    <t>1214977521865497</t>
-  </si>
-  <si>
-    <t>1214977521865512</t>
-  </si>
-  <si>
-    <t>1214977534681571</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977177909228</t>
-  </si>
-  <si>
-    <t>1214977177909238</t>
-  </si>
-  <si>
-    <t>1214977177909248</t>
-  </si>
-  <si>
-    <t>1214977396586693</t>
-  </si>
-  <si>
-    <t>1214977396586703</t>
-  </si>
-  <si>
-    <t>1214977396590869</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,PACKING LIST,Despacho,Embalaje</t>
-  </si>
-  <si>
-    <t>1214977396590879</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317463499</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317463514</t>
-  </si>
-  <si>
-    <t>1214977396631142</t>
-  </si>
-  <si>
-    <t>1214977396631157</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214977534721000</t>
-  </si>
-  <si>
-    <t>1214977534721015</t>
-  </si>
-  <si>
-    <t>1214977178000429</t>
-  </si>
-  <si>
-    <t>1214977178000439</t>
-  </si>
-  <si>
-    <t>1214977178000449</t>
-  </si>
-  <si>
-    <t>1214977534731518</t>
-  </si>
-  <si>
-    <t>1214977534731548</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>1214977521967452</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977521967467</t>
-  </si>
-  <si>
-    <t>1214977396652350</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,Embalaje</t>
-  </si>
-  <si>
-    <t>1214977396652365</t>
-  </si>
-  <si>
-    <t>1214977521980129</t>
-  </si>
-  <si>
-    <t>1214977521980144</t>
-  </si>
-  <si>
-    <t>1214977396668053</t>
-  </si>
-  <si>
-    <t>1214977396668063</t>
-  </si>
-  <si>
-    <t>1214977396668073</t>
-  </si>
-  <si>
-    <t>1214977317525369</t>
-  </si>
-  <si>
-    <t>1214977317525399</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>1214977534728344</t>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46230.17140546296</v>
+        <v>46231.20820982639</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4535,8 +4535,8 @@
       <c r="R42" s="5">
         <v>46230</v>
       </c>
-      <c r="S42" s="12" t="s">
-        <v>158</v>
+      <c r="S42" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46213.54075649305</v>
@@ -4559,7 +4559,7 @@
         <v>46227.62045023148</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4592,7 +4592,7 @@
         <v>26</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46213.54081322916</v>
@@ -4614,7 +4614,7 @@
         <v>46227.620521689816</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4644,10 +4644,10 @@
         <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4657,17 +4657,19 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46213.54449835648</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46231.63149971065</v>
+      </c>
       <c r="D45" s="9">
-        <v>46227.62045711806</v>
+        <v>46231.63150133102</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4694,10 +4696,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4710,17 +4712,19 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46213.544511342596</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46231.63150725694</v>
+      </c>
       <c r="D46" s="5">
-        <v>46227.620457893514</v>
+        <v>46231.631508923616</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4747,10 +4751,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4763,17 +4767,19 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="9">
         <v>46213.54452657407</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46231.631512314816</v>
+      </c>
       <c r="D47" s="9">
-        <v>46227.620458634265</v>
+        <v>46231.631513263885</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4800,10 +4806,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4816,17 +4822,19 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46213.54455305556</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46231.63152594907</v>
+      </c>
       <c r="D48" s="5">
-        <v>46227.62045965278</v>
+        <v>46231.631526909725</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4853,10 +4861,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4869,17 +4877,19 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="9">
         <v>46213.54453994213</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46231.6315846412</v>
+      </c>
       <c r="D49" s="9">
-        <v>46227.62046045139</v>
+        <v>46231.631585995376</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4906,10 +4916,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4922,17 +4932,19 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46213.5445649537</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46231.63161847222</v>
+      </c>
       <c r="D50" s="5">
-        <v>46227.6204612037</v>
+        <v>46231.63161953704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4959,10 +4971,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4975,17 +4987,19 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B51" s="9">
         <v>46213.54459085648</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46231.63160039352</v>
+      </c>
       <c r="D51" s="9">
-        <v>46227.62046199074</v>
+        <v>46231.631601851856</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -5012,10 +5026,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -5028,17 +5042,19 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B52" s="5">
         <v>46213.544605601855</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46231.63163682871</v>
+      </c>
       <c r="D52" s="5">
-        <v>46227.62046280093</v>
+        <v>46231.63163773148</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -5065,10 +5081,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5081,17 +5097,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B53" s="9">
         <v>46213.54463689815</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46231.63164260417</v>
+      </c>
       <c r="D53" s="9">
-        <v>46227.62046361111</v>
+        <v>46231.63164357639</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -5118,10 +5136,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5134,17 +5152,19 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B54" s="5">
         <v>46213.54464902778</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46231.63166644676</v>
+      </c>
       <c r="D54" s="5">
-        <v>46227.62046460648</v>
+        <v>46231.631670358795</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5171,10 +5191,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5187,17 +5207,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" s="9">
         <v>46213.54538011574</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46231.63173143518</v>
+      </c>
       <c r="D55" s="9">
-        <v>46227.62046534722</v>
+        <v>46231.63173241898</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -5224,10 +5246,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -5240,17 +5262,19 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B56" s="5">
         <v>46213.545488993055</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46231.63184952547</v>
+      </c>
       <c r="D56" s="5">
-        <v>46227.62046612268</v>
+        <v>46231.63185048611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5277,10 +5301,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5293,17 +5317,19 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B57" s="9">
         <v>46213.5454980787</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46231.631857685185</v>
+      </c>
       <c r="D57" s="9">
-        <v>46227.62046690972</v>
+        <v>46231.6318593287</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5330,10 +5356,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5346,17 +5372,19 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B58" s="5">
         <v>46213.545549849536</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46231.63186469907</v>
+      </c>
       <c r="D58" s="5">
-        <v>46227.620467870365</v>
+        <v>46231.63186645834</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5383,10 +5411,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5399,17 +5427,19 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B59" s="9">
         <v>46213.545558611106</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46231.6319061574</v>
+      </c>
       <c r="D59" s="9">
-        <v>46227.6204687037</v>
+        <v>46231.631907303235</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5436,10 +5466,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5452,17 +5482,19 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B60" s="5">
         <v>46213.54557347222</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46231.6319168287</v>
+      </c>
       <c r="D60" s="5">
-        <v>46227.62046957176</v>
+        <v>46231.63191810185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5489,10 +5521,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5505,17 +5537,19 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B61" s="9">
         <v>46213.54558582176</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46231.63192273148</v>
+      </c>
       <c r="D61" s="9">
-        <v>46227.620470381946</v>
+        <v>46231.63192396991</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5542,10 +5576,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5558,17 +5592,19 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B62" s="5">
         <v>46213.5455965625</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46231.63193590278</v>
+      </c>
       <c r="D62" s="5">
-        <v>46227.6204712037</v>
+        <v>46231.631937094906</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5595,10 +5631,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5611,17 +5647,19 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B63" s="9">
         <v>46213.545607962966</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46231.63194760417</v>
+      </c>
       <c r="D63" s="9">
-        <v>46227.620472002316</v>
+        <v>46231.6319487037</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5648,10 +5686,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5664,17 +5702,19 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B64" s="5">
         <v>46213.545619537035</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46231.63195206018</v>
+      </c>
       <c r="D64" s="5">
-        <v>46227.620472951385</v>
+        <v>46231.6319533912</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5701,10 +5741,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5717,26 +5757,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B65" s="9">
         <v>46213.54088876158</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46230.17140723379</v>
+        <v>46231.63246866898</v>
       </c>
       <c r="E65" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="H65" s="10" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="I65" s="9">
         <v>46227</v>
@@ -5757,7 +5797,7 @@
         <v>154</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>154</v>
@@ -5770,7 +5810,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B66" s="5">
         <v>46162.68117938658</v>
@@ -5782,7 +5822,7 @@
         <v>46210.52928206019</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5806,7 +5846,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5823,7 +5863,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="9">
         <v>46162.68150506944</v>
@@ -5835,16 +5875,16 @@
         <v>46197.703074074074</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I67" s="9">
         <v>46160</v>
@@ -5862,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q67" s="9">
         <v>46160</v>
@@ -5888,7 +5928,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B68" s="5">
         <v>46162.68151027778</v>
@@ -5900,16 +5940,16 @@
         <v>46198.796512534725</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I68" s="5">
         <v>46176</v>
@@ -5927,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68" s="5">
         <v>46176</v>
@@ -5953,7 +5993,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B69" s="9">
         <v>46162.6815165625</v>
@@ -5971,10 +6011,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I69" s="9">
         <v>46185</v>
@@ -5992,13 +6032,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q69" s="9">
         <v>46185</v>
@@ -6018,7 +6058,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B70" s="5">
         <v>46162.68153015046</v>
@@ -6028,16 +6068,16 @@
         <v>46226.17749263889</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6053,10 +6093,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6079,7 +6119,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B71" s="9">
         <v>46162.68153354166</v>
@@ -6089,16 +6129,16 @@
         <v>46225.16840908564</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I71" s="10"/>
       <c r="J71" s="9">
@@ -6114,13 +6154,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -6130,7 +6170,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B72" s="5">
         <v>46162.68153736111</v>
@@ -6140,16 +6180,16 @@
         <v>46225.168410370374</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6165,13 +6205,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6181,7 +6221,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B73" s="9">
         <v>46162.68154143519</v>
@@ -6191,16 +6231,16 @@
         <v>46225.168411516206</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I73" s="10"/>
       <c r="J73" s="9">
@@ -6216,13 +6256,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6232,7 +6272,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" s="5">
         <v>46162.68154440972</v>
@@ -6242,16 +6282,16 @@
         <v>46225.168412743056</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -6267,13 +6307,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6283,7 +6323,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B75" s="9">
         <v>46162.68154740741</v>
@@ -6293,16 +6333,16 @@
         <v>46225.16841392361</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6318,13 +6358,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6334,7 +6374,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B76" s="5">
         <v>46162.68155047453</v>
@@ -6344,16 +6384,16 @@
         <v>46225.16841503472</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6369,10 +6409,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6385,7 +6425,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B77" s="9">
         <v>46162.681552766204</v>
@@ -6395,16 +6435,16 @@
         <v>46225.168416203705</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6420,13 +6460,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6436,7 +6476,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B78" s="5">
         <v>46162.68155516204</v>
@@ -6446,16 +6486,16 @@
         <v>46225.168417361114</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6471,13 +6511,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6487,7 +6527,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B79" s="9">
         <v>46162.6815574537</v>
@@ -6497,16 +6537,16 @@
         <v>46225.16841868055</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6522,10 +6562,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6538,7 +6578,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B80" s="5">
         <v>46162.68155952546</v>
@@ -6548,16 +6588,16 @@
         <v>46225.16842006944</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6573,10 +6613,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6589,7 +6629,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B81" s="9">
         <v>46162.681598807874</v>
@@ -6599,7 +6639,7 @@
         <v>46162.707360960645</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>25</v>
@@ -6623,7 +6663,7 @@
         <v>26</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>26</v>
@@ -6636,7 +6676,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B82" s="5">
         <v>46162.681602743054</v>
@@ -6646,16 +6686,16 @@
         <v>46209.81557859953</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6671,13 +6711,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q82" s="5">
         <v>46203</v>
@@ -6697,7 +6737,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B83" s="9">
         <v>46162.68160836806</v>
@@ -6707,16 +6747,16 @@
         <v>46205.173878229165</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6732,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="Q83" s="9">
         <v>46204</v>
@@ -6758,7 +6798,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B84" s="5">
         <v>46162.681615208334</v>
@@ -6768,16 +6808,16 @@
         <v>46209.81632625</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6793,13 +6833,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q84" s="5">
         <v>46203</v>
@@ -6819,7 +6859,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B85" s="9">
         <v>46162.68162069445</v>
@@ -6829,16 +6869,16 @@
         <v>46205.173878472226</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6854,13 +6894,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q85" s="9">
         <v>46204</v>
@@ -6880,7 +6920,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B86" s="5">
         <v>46162.681625983794</v>
@@ -6890,16 +6930,16 @@
         <v>46209.81705302083</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6915,13 +6955,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>151</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q86" s="5">
         <v>46203</v>
@@ -6941,7 +6981,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B87" s="9">
         <v>46162.68163075231</v>
@@ -6951,16 +6991,16 @@
         <v>46205.17387842592</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6976,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q87" s="9">
         <v>46204</v>
@@ -7002,7 +7042,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B88" s="5">
         <v>46162.68163611111</v>
@@ -7012,7 +7052,7 @@
         <v>46213.540516967594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -7036,7 +7076,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -7049,7 +7089,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B89" s="9">
         <v>46162.6816390162</v>
@@ -7059,16 +7099,16 @@
         <v>46213.5405346412</v>
       </c>
       <c r="E89" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="10" t="s">
+      <c r="H89" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I89" s="9">
         <v>46205</v>
@@ -7086,13 +7126,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q89" s="9">
         <v>46205</v>
@@ -7112,7 +7152,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B90" s="5">
         <v>46162.68164390046</v>
@@ -7122,16 +7162,16 @@
         <v>46213.54003409723</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I90" s="5">
         <v>46205</v>
@@ -7149,13 +7189,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7165,7 +7205,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B91" s="9">
         <v>46162.681651203704</v>
@@ -7175,16 +7215,16 @@
         <v>46213.54003350694</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I91" s="9">
         <v>46205</v>
@@ -7202,13 +7242,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7218,7 +7258,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B92" s="5">
         <v>46162.68165733796</v>
@@ -7228,16 +7268,16 @@
         <v>46213.540032881945</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I92" s="5">
         <v>46205</v>
@@ -7255,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O92" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7271,7 +7311,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B93" s="9">
         <v>46162.68166336806</v>
@@ -7281,16 +7321,16 @@
         <v>46213.54003226852</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I93" s="9">
         <v>46205</v>
@@ -7308,13 +7348,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7324,7 +7364,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B94" s="5">
         <v>46162.68166935185</v>
@@ -7334,16 +7374,16 @@
         <v>46213.5400315625</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I94" s="5">
         <v>46205</v>
@@ -7361,13 +7401,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7377,7 +7417,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B95" s="9">
         <v>46162.68167571759</v>
@@ -7387,16 +7427,16 @@
         <v>46213.54003097222</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I95" s="9">
         <v>46205</v>
@@ -7414,13 +7454,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7430,7 +7470,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B96" s="5">
         <v>46162.68168109954</v>
@@ -7440,16 +7480,16 @@
         <v>46213.54003015046</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I96" s="5">
         <v>46205</v>
@@ -7467,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7483,7 +7523,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B97" s="9">
         <v>46162.68168630787</v>
@@ -7493,16 +7533,16 @@
         <v>46213.54002954861</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I97" s="9">
         <v>46205</v>
@@ -7520,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7536,7 +7576,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B98" s="5">
         <v>46162.68169194444</v>
@@ -7546,16 +7586,16 @@
         <v>46213.54002893518</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I98" s="5">
         <v>46205</v>
@@ -7573,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7589,7 +7629,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B99" s="9">
         <v>46162.681698229164</v>
@@ -7599,16 +7639,16 @@
         <v>46213.54002833333</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I99" s="9">
         <v>46205</v>
@@ -7626,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7642,7 +7682,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B100" s="5">
         <v>46162.68171431713</v>
@@ -7652,16 +7692,16 @@
         <v>46217.20388689815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I100" s="5">
         <v>46210</v>
@@ -7679,13 +7719,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q100" s="5">
         <v>46210</v>
@@ -7705,7 +7745,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B101" s="9">
         <v>46162.681718935186</v>
@@ -7715,16 +7755,16 @@
         <v>46216.169049386575</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I101" s="9">
         <v>46210</v>
@@ -7742,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="P101" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7758,7 +7798,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B102" s="5">
         <v>46162.68172515046</v>
@@ -7768,16 +7808,16 @@
         <v>46216.16906072917</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I102" s="5">
         <v>46210</v>
@@ -7795,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7811,7 +7851,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B103" s="9">
         <v>46162.68173074074</v>
@@ -7821,16 +7861,16 @@
         <v>46216.16905091435</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I103" s="9">
         <v>46210</v>
@@ -7848,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7864,7 +7904,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B104" s="5">
         <v>46162.68173619213</v>
@@ -7874,16 +7914,16 @@
         <v>46216.169052384255</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I104" s="5">
         <v>46210</v>
@@ -7901,13 +7941,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7917,7 +7957,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B105" s="9">
         <v>46162.681741747685</v>
@@ -7927,16 +7967,16 @@
         <v>46216.16906208333</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I105" s="9">
         <v>46210</v>
@@ -7954,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7970,7 +8010,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B106" s="5">
         <v>46162.68178277778</v>
@@ -7980,16 +8020,16 @@
         <v>46216.16905809028</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I106" s="5">
         <v>46210</v>
@@ -8007,13 +8047,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8023,7 +8063,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B107" s="9">
         <v>46162.68178671296</v>
@@ -8033,16 +8073,16 @@
         <v>46216.16905946759</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I107" s="9">
         <v>46210</v>
@@ -8060,10 +8100,10 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>26</v>
@@ -8076,7 +8116,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B108" s="5">
         <v>46162.68178976852</v>
@@ -8086,16 +8126,16 @@
         <v>46216.169053923615</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I108" s="5">
         <v>46210</v>
@@ -8113,13 +8153,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8129,7 +8169,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B109" s="9">
         <v>46162.68179300926</v>
@@ -8139,16 +8179,16 @@
         <v>46216.16905537037</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I109" s="9">
         <v>46210</v>
@@ -8166,13 +8206,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8182,7 +8222,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B110" s="5">
         <v>46162.68179625</v>
@@ -8192,16 +8232,16 @@
         <v>46216.16905674768</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I110" s="5">
         <v>46210</v>
@@ -8219,13 +8259,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8235,7 +8275,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B111" s="9">
         <v>46162.681806875</v>
@@ -8245,16 +8285,16 @@
         <v>46218.194210347225</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I111" s="9">
         <v>46217</v>
@@ -8272,13 +8312,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q111" s="9">
         <v>46217</v>
@@ -8298,7 +8338,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B112" s="5">
         <v>46162.68181175926</v>
@@ -8308,16 +8348,16 @@
         <v>46217.16850799769</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I112" s="5">
         <v>46217</v>
@@ -8335,13 +8375,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8351,7 +8391,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B113" s="9">
         <v>46162.68181751158</v>
@@ -8361,16 +8401,16 @@
         <v>46217.168509375</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I113" s="9">
         <v>46217</v>
@@ -8388,13 +8428,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8404,7 +8444,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B114" s="5">
         <v>46162.681823032406</v>
@@ -8414,16 +8454,16 @@
         <v>46217.16852262731</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I114" s="5">
         <v>46217</v>
@@ -8441,13 +8481,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8457,7 +8497,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B115" s="9">
         <v>46162.681828368055</v>
@@ -8467,16 +8507,16 @@
         <v>46217.168524085646</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I115" s="9">
         <v>46217</v>
@@ -8494,13 +8534,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8510,7 +8550,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B116" s="5">
         <v>46162.68183400463</v>
@@ -8520,16 +8560,16 @@
         <v>46217.16852547454</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I116" s="5">
         <v>46217</v>
@@ -8547,13 +8587,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8563,7 +8603,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B117" s="9">
         <v>46162.6818390625</v>
@@ -8573,16 +8613,16 @@
         <v>46217.16850363426</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I117" s="9">
         <v>46217</v>
@@ -8600,13 +8640,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8616,7 +8656,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B118" s="5">
         <v>46162.68184208333</v>
@@ -8626,16 +8666,16 @@
         <v>46224.87647668982</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8653,13 +8693,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8669,7 +8709,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B119" s="9">
         <v>46162.6818458912</v>
@@ -8679,16 +8719,16 @@
         <v>46217.16850662037</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I119" s="9">
         <v>46217</v>
@@ -8706,13 +8746,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8722,7 +8762,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B120" s="5">
         <v>46162.681849375</v>
@@ -8732,16 +8772,16 @@
         <v>46217.16851664352</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8759,13 +8799,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8775,7 +8815,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B121" s="9">
         <v>46162.68185259259</v>
@@ -8785,16 +8825,16 @@
         <v>46217.16851827546</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="I121" s="9">
         <v>46217</v>
@@ -8812,13 +8852,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8828,7 +8868,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B122" s="5">
         <v>46162.681862557874</v>
@@ -8838,7 +8878,7 @@
         <v>46162.708598171295</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>25</v>
@@ -8862,7 +8902,7 @@
         <v>26</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>26</v>
@@ -8875,7 +8915,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B123" s="9">
         <v>46162.68186600694</v>
@@ -8885,16 +8925,16 @@
         <v>46212.65657465278</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="9">
@@ -8910,13 +8950,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q123" s="9">
         <v>46161</v>
@@ -8936,7 +8976,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B124" s="5">
         <v>46162.681872870366</v>
@@ -8946,16 +8986,16 @@
         <v>46198.685305949075</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8971,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q124" s="5">
         <v>46161</v>
@@ -8997,7 +9037,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B125" s="9">
         <v>46162.681879930555</v>
@@ -9007,16 +9047,16 @@
         <v>46197.17676240741</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I125" s="10"/>
       <c r="J125" s="9">
@@ -9032,13 +9072,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>121</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q125" s="9">
         <v>46196</v>
@@ -9058,7 +9098,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B126" s="5">
         <v>46162.68189086806</v>
@@ -9068,7 +9108,7 @@
         <v>46162.710864479166</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9092,7 +9132,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9105,7 +9145,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B127" s="9">
         <v>46162.681893761575</v>
@@ -9115,7 +9155,7 @@
         <v>46225.16960298611</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9142,13 +9182,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q127" s="9">
         <v>46218</v>
@@ -9168,7 +9208,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B128" s="5">
         <v>46162.68190694445</v>
@@ -9178,7 +9218,7 @@
         <v>46224.25041532407</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9205,10 +9245,10 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9221,7 +9261,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B129" s="9">
         <v>46162.68191104167</v>
@@ -9231,7 +9271,7 @@
         <v>46224.2504165625</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9258,10 +9298,10 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>26</v>
@@ -9274,7 +9314,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B130" s="5">
         <v>46162.68191516204</v>
@@ -9284,7 +9324,7 @@
         <v>46224.25041792824</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9311,13 +9351,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9327,7 +9367,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B131" s="9">
         <v>46162.68191947917</v>
@@ -9337,7 +9377,7 @@
         <v>46224.25041925926</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9364,13 +9404,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9380,7 +9420,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B132" s="5">
         <v>46162.68192371528</v>
@@ -9390,7 +9430,7 @@
         <v>46224.25043248842</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9417,13 +9457,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9433,7 +9473,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B133" s="9">
         <v>46162.68192716435</v>
@@ -9443,7 +9483,7 @@
         <v>46224.25043388889</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9470,13 +9510,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9486,7 +9526,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B134" s="5">
         <v>46162.6819303588</v>
@@ -9496,7 +9536,7 @@
         <v>46224.25042052083</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9523,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9539,7 +9579,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B135" s="9">
         <v>46162.6819334375</v>
@@ -9549,7 +9589,7 @@
         <v>46224.25042207176</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9576,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9592,7 +9632,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B136" s="5">
         <v>46162.68193662037</v>
@@ -9602,7 +9642,7 @@
         <v>46224.25042332176</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9629,13 +9669,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9645,7 +9685,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B137" s="9">
         <v>46162.68193976852</v>
@@ -9655,7 +9695,7 @@
         <v>46224.25042453704</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9682,13 +9722,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9698,7 +9738,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B138" s="5">
         <v>46162.68199361111</v>
@@ -9708,7 +9748,7 @@
         <v>46223.57819246528</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9735,13 +9775,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q138" s="5">
         <v>46219</v>
@@ -9761,7 +9801,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B139" s="9">
         <v>46162.68199872685</v>
@@ -9771,7 +9811,7 @@
         <v>46223.57719570602</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9798,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="P139" s="10" t="s">
         <v>331</v>
-      </c>
-      <c r="P139" s="10" t="s">
-        <v>332</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9814,7 +9854,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B140" s="5">
         <v>46162.6820043287</v>
@@ -9824,7 +9864,7 @@
         <v>46223.57719509259</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9851,13 +9891,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9867,7 +9907,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B141" s="9">
         <v>46162.68200945602</v>
@@ -9877,7 +9917,7 @@
         <v>46223.57719428241</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9904,13 +9944,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O141" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="P141" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="P141" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9920,7 +9960,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B142" s="5">
         <v>46162.68201590278</v>
@@ -9930,7 +9970,7 @@
         <v>46223.57719365741</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9957,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O142" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="P142" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9973,7 +10013,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B143" s="9">
         <v>46162.682022175926</v>
@@ -9983,7 +10023,7 @@
         <v>46223.57719302083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10010,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10026,7 +10066,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B144" s="5">
         <v>46162.68202664352</v>
@@ -10036,7 +10076,7 @@
         <v>46223.57719239584</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10063,13 +10103,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10079,7 +10119,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B145" s="9">
         <v>46162.682031874996</v>
@@ -10089,7 +10129,7 @@
         <v>46223.5771917824</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10116,13 +10156,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10132,7 +10172,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B146" s="5">
         <v>46162.682037129634</v>
@@ -10142,7 +10182,7 @@
         <v>46223.57719092593</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10169,13 +10209,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10185,7 +10225,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B147" s="9">
         <v>46162.68204233796</v>
@@ -10195,7 +10235,7 @@
         <v>46223.5771903125</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10222,13 +10262,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10238,7 +10278,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B148" s="5">
         <v>46162.68204753472</v>
@@ -10248,7 +10288,7 @@
         <v>46223.577189675925</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10275,13 +10315,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10291,7 +10331,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B149" s="9">
         <v>46162.68206118056</v>
@@ -10301,7 +10341,7 @@
         <v>46223.57819173612</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10328,13 +10368,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q149" s="9">
         <v>46220</v>
@@ -10354,7 +10394,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B150" s="5">
         <v>46162.68206542824</v>
@@ -10364,7 +10404,7 @@
         <v>46223.577558969904</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10391,13 +10431,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10407,7 +10447,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B151" s="9">
         <v>46162.68207142361</v>
@@ -10417,7 +10457,7 @@
         <v>46223.577558379635</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10444,13 +10484,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10460,7 +10500,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B152" s="5">
         <v>46162.682082997686</v>
@@ -10470,7 +10510,7 @@
         <v>46223.577557743054</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10497,13 +10537,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10513,7 +10553,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B153" s="9">
         <v>46162.682089317124</v>
@@ -10523,7 +10563,7 @@
         <v>46223.57755715278</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10550,13 +10590,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O153" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="P153" s="10" t="s">
         <v>356</v>
-      </c>
-      <c r="P153" s="10" t="s">
-        <v>357</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10566,7 +10606,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B154" s="5">
         <v>46162.68209565972</v>
@@ -10576,7 +10616,7 @@
         <v>46223.57755659722</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10603,13 +10643,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10619,7 +10659,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B155" s="9">
         <v>46162.68209994213</v>
@@ -10629,7 +10669,7 @@
         <v>46223.57755598379</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10656,13 +10696,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10672,7 +10712,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B156" s="5">
         <v>46162.682104189815</v>
@@ -10682,7 +10722,7 @@
         <v>46223.57755538194</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10709,13 +10749,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10725,7 +10765,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B157" s="9">
         <v>46162.68210733796</v>
@@ -10735,7 +10775,7 @@
         <v>46223.57755479167</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10762,13 +10802,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10778,7 +10818,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B158" s="5">
         <v>46162.68211155092</v>
@@ -10788,7 +10828,7 @@
         <v>46223.577554097224</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10815,13 +10855,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10831,7 +10871,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B159" s="9">
         <v>46162.68211587963</v>
@@ -10841,7 +10881,7 @@
         <v>46223.57755349537</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10868,13 +10908,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10884,7 +10924,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B160" s="5">
         <v>46162.68212817129</v>
@@ -10894,7 +10934,7 @@
         <v>46224.20299456018</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10921,13 +10961,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q160" s="5">
         <v>46223</v>
@@ -10947,7 +10987,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B161" s="9">
         <v>46162.68213233796</v>
@@ -10957,7 +10997,7 @@
         <v>46223.5777274537</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10984,13 +11024,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O161" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="P161" s="10" t="s">
         <v>369</v>
-      </c>
-      <c r="P161" s="10" t="s">
-        <v>370</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11000,7 +11040,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B162" s="5">
         <v>46162.682137881944</v>
@@ -11010,7 +11050,7 @@
         <v>46223.57772681713</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11037,13 +11077,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O162" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P162" s="6" t="s">
         <v>369</v>
-      </c>
-      <c r="P162" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11053,7 +11093,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B163" s="9">
         <v>46162.682143275466</v>
@@ -11063,7 +11103,7 @@
         <v>46223.57772619213</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11090,13 +11130,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11106,7 +11146,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B164" s="5">
         <v>46162.68214959491</v>
@@ -11116,7 +11156,7 @@
         <v>46223.57772559028</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11143,13 +11183,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11159,7 +11199,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B165" s="9">
         <v>46162.6821980324</v>
@@ -11169,7 +11209,7 @@
         <v>46223.57772497685</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11196,13 +11236,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11212,7 +11252,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B166" s="5">
         <v>46162.68220454861</v>
@@ -11222,7 +11262,7 @@
         <v>46223.5777243287</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11249,13 +11289,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O166" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="P166" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="P166" s="6" t="s">
-        <v>380</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11265,7 +11305,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B167" s="9">
         <v>46162.6822112963</v>
@@ -11275,7 +11315,7 @@
         <v>46223.577723738425</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
@@ -11302,13 +11342,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -11318,7 +11358,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B168" s="5">
         <v>46162.68221605324</v>
@@ -11328,7 +11368,7 @@
         <v>46223.577723055554</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11355,13 +11395,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11371,7 +11411,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B169" s="9">
         <v>46162.68222200232</v>
@@ -11381,7 +11421,7 @@
         <v>46223.57772240741</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11408,13 +11448,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11424,7 +11464,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B170" s="5">
         <v>46162.68222814814</v>
@@ -11434,7 +11474,7 @@
         <v>46223.57772177084</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11461,13 +11501,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11477,7 +11517,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B171" s="9">
         <v>46162.68224497685</v>
@@ -11487,7 +11527,7 @@
         <v>46225.16960282407</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11514,13 +11554,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q171" s="9">
         <v>46224</v>
@@ -11540,7 +11580,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B172" s="5">
         <v>46162.68224997685</v>
@@ -11550,7 +11590,7 @@
         <v>46224.25041123843</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11577,13 +11617,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11593,7 +11633,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B173" s="9">
         <v>46162.682255844906</v>
@@ -11603,7 +11643,7 @@
         <v>46224.250425844904</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11630,13 +11670,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11646,7 +11686,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B174" s="5">
         <v>46162.682261354166</v>
@@ -11656,7 +11696,7 @@
         <v>46224.2504271412</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11683,13 +11723,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11699,7 +11739,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B175" s="9">
         <v>46162.68226693287</v>
@@ -11709,7 +11749,7 @@
         <v>46224.25041263889</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11736,13 +11776,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11752,7 +11792,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B176" s="5">
         <v>46162.68227229167</v>
@@ -11762,7 +11802,7 @@
         <v>46224.25041399305</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11789,13 +11829,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11805,7 +11845,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B177" s="9">
         <v>46162.68227762732</v>
@@ -11815,7 +11855,7 @@
         <v>46224.25042840278</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11842,10 +11882,10 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P177" s="10" t="s">
         <v>26</v>
@@ -11858,7 +11898,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B178" s="5">
         <v>46162.68228032408</v>
@@ -11868,7 +11908,7 @@
         <v>46224.250429583335</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11895,13 +11935,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11911,7 +11951,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B179" s="9">
         <v>46162.68228446759</v>
@@ -11921,7 +11961,7 @@
         <v>46224.2504365162</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11948,10 +11988,10 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P179" s="10" t="s">
         <v>26</v>
@@ -11964,7 +12004,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B180" s="5">
         <v>46162.68228719907</v>
@@ -11974,7 +12014,7 @@
         <v>46224.25043774306</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12001,10 +12041,10 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>26</v>
@@ -12017,7 +12057,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B181" s="9">
         <v>46162.68229016203</v>
@@ -12027,7 +12067,7 @@
         <v>46224.25043097222</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12054,10 +12094,10 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P181" s="10" t="s">
         <v>26</v>
@@ -12070,7 +12110,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B182" s="5">
         <v>46162.68230002315</v>
@@ -12080,7 +12120,7 @@
         <v>46227.198019351854</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12107,13 +12147,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q182" s="5">
         <v>46226</v>
@@ -12133,7 +12173,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B183" s="9">
         <v>46162.682309502314</v>
@@ -12143,7 +12183,7 @@
         <v>46226.168160671295</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12168,13 +12208,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12184,7 +12224,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B184" s="5">
         <v>46162.68231375</v>
@@ -12194,7 +12234,7 @@
         <v>46226.16816204861</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12219,13 +12259,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12235,7 +12275,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B185" s="9">
         <v>46162.682318101855</v>
@@ -12245,7 +12285,7 @@
         <v>46226.16816368056</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12270,13 +12310,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12286,7 +12326,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B186" s="5">
         <v>46162.682322430555</v>
@@ -12296,7 +12336,7 @@
         <v>46226.16816538194</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12321,13 +12361,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12337,7 +12377,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B187" s="9">
         <v>46162.682326759255</v>
@@ -12347,7 +12387,7 @@
         <v>46226.16816987269</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12372,13 +12412,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12388,7 +12428,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B188" s="5">
         <v>46162.68236239583</v>
@@ -12398,7 +12438,7 @@
         <v>46226.16815111111</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12423,10 +12463,10 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>26</v>
@@ -12439,7 +12479,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B189" s="9">
         <v>46162.682365960645</v>
@@ -12449,7 +12489,7 @@
         <v>46226.168152708335</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12474,13 +12514,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12490,7 +12530,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B190" s="5">
         <v>46162.68236944445</v>
@@ -12500,7 +12540,7 @@
         <v>46226.16815416666</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12525,13 +12565,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12541,7 +12581,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B191" s="9">
         <v>46162.68237259259</v>
@@ -12551,7 +12591,7 @@
         <v>46226.16815575231</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12576,13 +12616,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12592,7 +12632,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B192" s="5">
         <v>46162.682375902776</v>
@@ -12602,7 +12642,7 @@
         <v>46226.16815724537</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12627,13 +12667,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12643,7 +12683,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B193" s="9">
         <v>46162.682386099536</v>
@@ -12653,7 +12693,7 @@
         <v>46162.711784837964</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>25</v>
@@ -12677,7 +12717,7 @@
         <v>26</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P193" s="10" t="s">
         <v>26</v>
@@ -12690,7 +12730,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B194" s="5">
         <v>46162.68238924768</v>
@@ -12700,16 +12740,16 @@
         <v>46228.19797770833</v>
       </c>
       <c r="E194" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G194" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="F194" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G194" s="6" t="s">
+      <c r="H194" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I194" s="5">
         <v>46227</v>
@@ -12727,13 +12767,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q194" s="5">
         <v>46227</v>
@@ -12753,7 +12793,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B195" s="9">
         <v>46162.682394664356</v>
@@ -12763,16 +12803,16 @@
         <v>46227.168892430556</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H195" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I195" s="9">
         <v>46227</v>
@@ -12790,13 +12830,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12806,7 +12846,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B196" s="5">
         <v>46162.68239902778</v>
@@ -12816,16 +12856,16 @@
         <v>46227.16883238426</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I196" s="5">
         <v>46227</v>
@@ -12843,13 +12883,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12859,7 +12899,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B197" s="9">
         <v>46162.682403321756</v>
@@ -12869,16 +12909,16 @@
         <v>46227.16883634259</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I197" s="9">
         <v>46227</v>
@@ -12896,13 +12936,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12912,7 +12952,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B198" s="5">
         <v>46162.68240755787</v>
@@ -12922,16 +12962,16 @@
         <v>46227.16883768518</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I198" s="5">
         <v>46227</v>
@@ -12949,13 +12989,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12965,7 +13005,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B199" s="9">
         <v>46162.68241208333</v>
@@ -12975,16 +13015,16 @@
         <v>46227.16884165509</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I199" s="9">
         <v>46227</v>
@@ -13002,13 +13042,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13018,7 +13058,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B200" s="5">
         <v>46162.682416400465</v>
@@ -13028,16 +13068,16 @@
         <v>46227.16884313658</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I200" s="5">
         <v>46227</v>
@@ -13055,13 +13095,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13071,7 +13111,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B201" s="9">
         <v>46162.68241952546</v>
@@ -13081,16 +13121,16 @@
         <v>46227.16888855324</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I201" s="9">
         <v>46227</v>
@@ -13108,10 +13148,10 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P201" s="10" t="s">
         <v>26</v>
@@ -13124,7 +13164,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B202" s="5">
         <v>46162.6824222338</v>
@@ -13134,16 +13174,16 @@
         <v>46227.168889884255</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I202" s="5">
         <v>46227</v>
@@ -13161,13 +13201,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13177,7 +13217,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B203" s="9">
         <v>46162.68242513889</v>
@@ -13187,16 +13227,16 @@
         <v>46227.16889119213</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>420</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>421</v>
       </c>
       <c r="I203" s="9">
         <v>46227</v>
@@ -13214,13 +13254,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13230,7 +13270,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B204" s="5">
         <v>46162.682428125</v>
@@ -13240,16 +13280,16 @@
         <v>46227.16884428241</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="I204" s="5">
         <v>46227</v>
@@ -13267,13 +13307,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13283,17 +13323,17 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B205" s="9">
         <v>46162.68243688658</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46230.168793634264</v>
+        <v>46231.20820982639</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13320,13 +13360,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q205" s="9">
         <v>46230</v>
@@ -13334,8 +13374,8 @@
       <c r="R205" s="9">
         <v>46230</v>
       </c>
-      <c r="S205" s="12" t="s">
-        <v>158</v>
+      <c r="S205" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T205" s="10">
         <v>0</v>
@@ -13346,7 +13386,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B206" s="5">
         <v>46162.68244069444</v>
@@ -13356,7 +13396,7 @@
         <v>46230.168786319446</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13383,13 +13423,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13399,7 +13439,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B207" s="9">
         <v>46162.68244457176</v>
@@ -13409,7 +13449,7 @@
         <v>46230.168788043986</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13436,13 +13476,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13452,7 +13492,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B208" s="5">
         <v>46162.68244844908</v>
@@ -13462,7 +13502,7 @@
         <v>46230.1687662037</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13489,13 +13529,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13505,7 +13545,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B209" s="9">
         <v>46162.68245221065</v>
@@ -13515,7 +13555,7 @@
         <v>46230.16876739584</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13542,13 +13582,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13558,7 +13598,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B210" s="5">
         <v>46162.68245652778</v>
@@ -13568,7 +13608,7 @@
         <v>46230.1687893287</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13595,13 +13635,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13611,7 +13651,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B211" s="9">
         <v>46162.68246049769</v>
@@ -13621,7 +13661,7 @@
         <v>46230.168790578704</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13648,10 +13688,10 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P211" s="10" t="s">
         <v>26</v>
@@ -13664,7 +13704,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B212" s="5">
         <v>46162.68246318287</v>
@@ -13674,7 +13714,7 @@
         <v>46230.16876855324</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13701,13 +13741,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13717,7 +13757,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B213" s="9">
         <v>46162.68246601852</v>
@@ -13727,7 +13767,7 @@
         <v>46230.16876962963</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13754,13 +13794,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13770,7 +13810,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B214" s="5">
         <v>46162.68246881945</v>
@@ -13780,7 +13820,7 @@
         <v>46230.16877107639</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13807,13 +13847,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13823,7 +13863,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B215" s="9">
         <v>46162.68247158565</v>
@@ -13833,7 +13873,7 @@
         <v>46230.16876494213</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13860,13 +13900,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13876,26 +13916,26 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B216" s="5">
         <v>46162.68248012732</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46224.188705671295</v>
+        <v>46231.168264340275</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I216" s="5">
         <v>46231</v>
@@ -13913,13 +13953,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q216" s="5">
         <v>46231</v>
@@ -13928,7 +13968,7 @@
         <v>46231</v>
       </c>
       <c r="S216" s="12" t="s">
-        <v>158</v>
+        <v>450</v>
       </c>
       <c r="T216" s="6">
         <v>0</v>
@@ -13946,19 +13986,19 @@
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46162.766515462965</v>
+        <v>46231.16828158565</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I217" s="9">
         <v>46231</v>
@@ -13976,10 +14016,10 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>452</v>
@@ -13999,19 +14039,19 @@
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46162.76651282408</v>
+        <v>46231.168282847226</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I218" s="5">
         <v>46231</v>
@@ -14029,10 +14069,10 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>452</v>
@@ -14052,19 +14092,19 @@
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46162.76651023148</v>
+        <v>46231.16828413194</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I219" s="9">
         <v>46231</v>
@@ -14082,10 +14122,10 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>455</v>
@@ -14105,19 +14145,19 @@
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46162.76650773148</v>
+        <v>46231.16826653935</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I220" s="5">
         <v>46231</v>
@@ -14135,10 +14175,10 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>455</v>
@@ -14158,19 +14198,19 @@
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46162.76650408565</v>
+        <v>46231.168267800924</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I221" s="9">
         <v>46231</v>
@@ -14188,10 +14228,10 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>458</v>
@@ -14211,19 +14251,19 @@
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46162.76650106482</v>
+        <v>46231.168273194446</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I222" s="5">
         <v>46231</v>
@@ -14241,13 +14281,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14264,19 +14304,19 @@
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46162.76649841435</v>
+        <v>46231.16827447916</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I223" s="9">
         <v>46231</v>
@@ -14294,13 +14334,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P223" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q223" s="10"/>
       <c r="R223" s="10"/>
@@ -14317,19 +14357,19 @@
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46162.76649456019</v>
+        <v>46231.16827571759</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I224" s="5">
         <v>46231</v>
@@ -14347,13 +14387,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14370,19 +14410,19 @@
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46162.766489050926</v>
+        <v>46231.16827678241</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I225" s="9">
         <v>46231</v>
@@ -14400,13 +14440,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P225" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q225" s="10"/>
       <c r="R225" s="10"/>
@@ -14423,19 +14463,19 @@
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46162.76648839121</v>
+        <v>46231.16827799768</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I226" s="5">
         <v>46231</v>
@@ -14453,13 +14493,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14485,10 +14525,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I227" s="9">
         <v>46232</v>
@@ -14506,10 +14546,10 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P227" s="10" t="s">
         <v>466</v>
@@ -14521,7 +14561,7 @@
         <v>46232</v>
       </c>
       <c r="S227" s="12" t="s">
-        <v>158</v>
+        <v>450</v>
       </c>
       <c r="T227" s="10">
         <v>0</v>
@@ -14542,16 +14582,16 @@
         <v>46162.76670017361</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I228" s="5">
         <v>46232</v>
@@ -14572,7 +14612,7 @@
         <v>465</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>465</v>
@@ -14595,16 +14635,16 @@
         <v>46162.76669680556</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I229" s="9">
         <v>46232</v>
@@ -14625,7 +14665,7 @@
         <v>465</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P229" s="10" t="s">
         <v>465</v>
@@ -14648,16 +14688,16 @@
         <v>46162.76669409723</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I230" s="5">
         <v>46232</v>
@@ -14678,7 +14718,7 @@
         <v>465</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>465</v>
@@ -14701,16 +14741,16 @@
         <v>46162.766691377314</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I231" s="9">
         <v>46232</v>
@@ -14731,7 +14771,7 @@
         <v>465</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>465</v>
@@ -14754,16 +14794,16 @@
         <v>46162.766687662035</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I232" s="5">
         <v>46232</v>
@@ -14784,7 +14824,7 @@
         <v>465</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P232" s="6" t="s">
         <v>465</v>
@@ -14807,16 +14847,16 @@
         <v>46162.76668472222</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I233" s="9">
         <v>46232</v>
@@ -14837,7 +14877,7 @@
         <v>465</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P233" s="10" t="s">
         <v>26</v>
@@ -14860,16 +14900,16 @@
         <v>46162.76668173611</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I234" s="5">
         <v>46232</v>
@@ -14890,7 +14930,7 @@
         <v>465</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>26</v>
@@ -14913,16 +14953,16 @@
         <v>46162.76667282407</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G235" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H235" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H235" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I235" s="9">
         <v>46232</v>
@@ -14943,7 +14983,7 @@
         <v>465</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -14966,16 +15006,16 @@
         <v>46162.76667212963</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H236" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I236" s="5">
         <v>46232</v>
@@ -14996,7 +15036,7 @@
         <v>465</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P236" s="6" t="s">
         <v>26</v>
@@ -15019,16 +15059,16 @@
         <v>46162.76667141204</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H237" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H237" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I237" s="9">
         <v>46232</v>
@@ -15049,7 +15089,7 @@
         <v>465</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P237" s="10" t="s">
         <v>26</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -1423,55 +1423,55 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1214977534728344</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,PACKING LIST,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1214977534807907</t>
+  </si>
+  <si>
+    <t>1214977534807927</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4327- ZVN 2-9-103/2</t>
+  </si>
+  <si>
+    <t>1214977317598088</t>
+  </si>
+  <si>
+    <t>1214977317598103</t>
+  </si>
+  <si>
+    <t>OT 4327- ZVN 2-9-103/2,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1214977522051960</t>
+  </si>
+  <si>
+    <t>1214977522051970</t>
+  </si>
+  <si>
+    <t>1214977522051980</t>
+  </si>
+  <si>
+    <t>1214977522054268</t>
+  </si>
+  <si>
+    <t>1214977522054278</t>
+  </si>
+  <si>
+    <t>1214977396743897</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214977534728344</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,PACKING LIST,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1214977534807907</t>
-  </si>
-  <si>
-    <t>1214977534807927</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4327- ZVN 2-9-103/2</t>
-  </si>
-  <si>
-    <t>1214977317598088</t>
-  </si>
-  <si>
-    <t>1214977317598103</t>
-  </si>
-  <si>
-    <t>OT 4327- ZVN 2-9-103/2,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1214977522051960</t>
-  </si>
-  <si>
-    <t>1214977522051970</t>
-  </si>
-  <si>
-    <t>1214977522051980</t>
-  </si>
-  <si>
-    <t>1214977522054268</t>
-  </si>
-  <si>
-    <t>1214977522054278</t>
-  </si>
-  <si>
-    <t>1214977396743897</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1214977178148305</t>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46231.168264340275</v>
+        <v>46232.16892658565</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>449</v>
@@ -13967,8 +13967,8 @@
       <c r="R216" s="5">
         <v>46231</v>
       </c>
-      <c r="S216" s="12" t="s">
-        <v>450</v>
+      <c r="S216" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T216" s="6">
         <v>0</v>
@@ -13979,7 +13979,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B217" s="9">
         <v>46162.682524502314</v>
@@ -14022,7 +14022,7 @@
         <v>165</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -14032,7 +14032,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B218" s="5">
         <v>46162.682533032406</v>
@@ -14075,7 +14075,7 @@
         <v>165</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -14085,7 +14085,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B219" s="9">
         <v>46162.68253883102</v>
@@ -14128,7 +14128,7 @@
         <v>165</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14138,7 +14138,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B220" s="5">
         <v>46162.68254368055</v>
@@ -14181,7 +14181,7 @@
         <v>165</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14191,7 +14191,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B221" s="9">
         <v>46162.68255409722</v>
@@ -14234,7 +14234,7 @@
         <v>165</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B222" s="5">
         <v>46162.6825590625</v>
@@ -14297,7 +14297,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B223" s="9">
         <v>46162.68256261574</v>
@@ -14350,7 +14350,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B224" s="5">
         <v>46162.682566006944</v>
@@ -14403,7 +14403,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B225" s="9">
         <v>46162.682569386576</v>
@@ -14456,7 +14456,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B226" s="5">
         <v>46162.68257278935</v>
@@ -14509,17 +14509,17 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B227" s="9">
         <v>46162.68258331019</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46225.178812060185</v>
+        <v>46232.168232094904</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14552,7 +14552,7 @@
         <v>252</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q227" s="9">
         <v>46232</v>
@@ -14561,7 +14561,7 @@
         <v>46232</v>
       </c>
       <c r="S227" s="12" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="T227" s="10">
         <v>0</v>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46162.76670017361</v>
+        <v>46232.16822225694</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>165</v>
@@ -14609,13 +14609,13 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P228" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46162.76669680556</v>
+        <v>46232.16822356482</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>165</v>
@@ -14662,13 +14662,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>165</v>
       </c>
       <c r="P229" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q229" s="10"/>
       <c r="R229" s="10"/>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46162.76669409723</v>
+        <v>46232.1682255787</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>165</v>
@@ -14715,13 +14715,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q230" s="6"/>
       <c r="R230" s="6"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46162.766691377314</v>
+        <v>46232.16822944445</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>165</v>
@@ -14768,13 +14768,13 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>165</v>
       </c>
       <c r="P231" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q231" s="10"/>
       <c r="R231" s="10"/>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46162.766687662035</v>
+        <v>46232.168230868054</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>165</v>
@@ -14821,13 +14821,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q232" s="6"/>
       <c r="R232" s="6"/>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46162.76668472222</v>
+        <v>46232.16823401621</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>165</v>
@@ -14874,7 +14874,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>165</v>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46162.76668173611</v>
+        <v>46232.1682353588</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>165</v>
@@ -14927,7 +14927,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>165</v>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46162.76667282407</v>
+        <v>46232.16823686342</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>165</v>
@@ -14980,7 +14980,7 @@
         <v>26</v>
       </c>
       <c r="N235" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O235" s="10" t="s">
         <v>165</v>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46162.76667212963</v>
+        <v>46232.168226932874</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>165</v>
@@ -15033,7 +15033,7 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O236" s="6" t="s">
         <v>165</v>
@@ -15056,7 +15056,7 @@
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46162.76667141204</v>
+        <v>46232.16822815972</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>165</v>
@@ -15086,7 +15086,7 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O237" s="10" t="s">
         <v>165</v>
@@ -15189,7 +15189,7 @@
         <v>478</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P239" s="10" t="s">
         <v>478</v>
@@ -15252,7 +15252,7 @@
         <v>478</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P240" s="6" t="s">
         <v>478</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="485">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -1469,9 +1469,6 @@
   </si>
   <si>
     <t>Logistica:,Gestion,Costos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214977178148305</t>
@@ -14516,7 +14513,7 @@
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46232.168232094904</v>
+        <v>46233.17843454861</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>464</v>
@@ -14560,8 +14557,8 @@
       <c r="R227" s="9">
         <v>46232</v>
       </c>
-      <c r="S227" s="12" t="s">
-        <v>466</v>
+      <c r="S227" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T227" s="10">
         <v>0</v>
@@ -14572,7 +14569,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B228" s="5">
         <v>46162.6825891551</v>
@@ -14625,7 +14622,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B229" s="9">
         <v>46162.68259327546</v>
@@ -14678,7 +14675,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B230" s="5">
         <v>46162.682597499996</v>
@@ -14731,7 +14728,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B231" s="9">
         <v>46162.68260168981</v>
@@ -14784,7 +14781,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B232" s="5">
         <v>46162.68260615741</v>
@@ -14837,7 +14834,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B233" s="9">
         <v>46162.68261056713</v>
@@ -14890,7 +14887,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B234" s="5">
         <v>46162.682613564815</v>
@@ -14943,7 +14940,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B235" s="9">
         <v>46162.682616666665</v>
@@ -14996,7 +14993,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B236" s="5">
         <v>46162.682619583335</v>
@@ -15049,7 +15046,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B237" s="9">
         <v>46162.68262266203</v>
@@ -15102,7 +15099,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B238" s="5">
         <v>46162.682665625005</v>
@@ -15112,7 +15109,7 @@
         <v>46162.76005167824</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15136,7 +15133,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15149,7 +15146,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B239" s="9">
         <v>46162.68266950232</v>
@@ -15159,16 +15156,16 @@
         <v>46162.76676789352</v>
       </c>
       <c r="E239" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F239" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G239" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="F239" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G239" s="10" t="s">
+      <c r="H239" s="10" t="s">
         <v>482</v>
-      </c>
-      <c r="H239" s="10" t="s">
-        <v>483</v>
       </c>
       <c r="I239" s="9">
         <v>46233</v>
@@ -15186,13 +15183,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O239" s="10" t="s">
         <v>464</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q239" s="9">
         <v>46233</v>
@@ -15212,7 +15209,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B240" s="5">
         <v>46162.68267490741</v>
@@ -15222,7 +15219,7 @@
         <v>46197.777038217595</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15249,13 +15246,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O240" s="6" t="s">
         <v>464</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q240" s="5">
         <v>46233</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="486">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -1520,6 +1520,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214977534966124</t>
@@ -15153,7 +15156,7 @@
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46162.76676789352</v>
+        <v>46234.207251134256</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>480</v>
@@ -15197,8 +15200,8 @@
       <c r="R239" s="9">
         <v>46241</v>
       </c>
-      <c r="S239" s="7" t="s">
-        <v>54</v>
+      <c r="S239" s="12" t="s">
+        <v>483</v>
       </c>
       <c r="T239" s="10">
         <v>0</v>
@@ -15209,17 +15212,17 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B240" s="5">
         <v>46162.68267490741</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46197.777038217595</v>
+        <v>46234.20725118056</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15260,8 +15263,8 @@
       <c r="R240" s="5">
         <v>46241</v>
       </c>
-      <c r="S240" s="7" t="s">
-        <v>54</v>
+      <c r="S240" s="12" t="s">
+        <v>483</v>
       </c>
       <c r="T240" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46234.207251134256</v>
+        <v>46241.1686374537</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>480</v>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46234.20725118056</v>
+        <v>46241.16863947916</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>485</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2741" uniqueCount="485">
   <si>
     <t>50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4327</t>
   </si>
@@ -1520,9 +1520,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214977534966124</t>
@@ -15156,7 +15153,7 @@
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46241.1686374537</v>
+        <v>46242.190387581024</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>480</v>
@@ -15200,8 +15197,8 @@
       <c r="R239" s="9">
         <v>46241</v>
       </c>
-      <c r="S239" s="12" t="s">
-        <v>483</v>
+      <c r="S239" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T239" s="10">
         <v>0</v>
@@ -15212,17 +15209,17 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B240" s="5">
         <v>46162.68267490741</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46241.16863947916</v>
+        <v>46242.19038837963</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15263,8 +15260,8 @@
       <c r="R240" s="5">
         <v>46241</v>
       </c>
-      <c r="S240" s="12" t="s">
-        <v>483</v>
+      <c r="S240" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T240" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2276,7 +2276,7 @@
         <v>46175.87787261574</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.767692511574</v>
+        <v>46248.930263912036</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46226.17749263889</v>
+        <v>46249.04768783565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>208</v>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46213.540516967594</v>
+        <v>46249.06894548611</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>246</v>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46213.5405346412</v>
+        <v>46249.04037365741</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>249</v>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46217.20388689815</v>
+        <v>46249.04044701389</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>270</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46218.194210347225</v>
+        <v>46249.04049478009</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>284</v>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46162.708598171295</v>
+        <v>46249.04035597222</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>224</v>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46225.16960298611</v>
+        <v>46249.04080386574</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>314</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46223.57819246528</v>
+        <v>46249.04286884259</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>328</v>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46223.57819173612</v>
+        <v>46249.04289667824</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>347</v>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46224.20299456018</v>
+        <v>46249.04296068287</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>366</v>
@@ -11521,7 +11521,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46225.16960282407</v>
+        <v>46249.04298155093</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>386</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46227.198019351854</v>
+        <v>46249.04302650463</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>400</v>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46228.19797770833</v>
+        <v>46249.04307560185</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>418</v>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46231.20820982639</v>
+        <v>46249.04313600695</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>435</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46232.16892658565</v>
+        <v>46249.04350951389</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>449</v>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46233.17843454861</v>
+        <v>46249.04364065972</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>464</v>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46162.76005167824</v>
+        <v>46249.06790976852</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>477</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -2536,7 +2536,7 @@
         <v>46198.68205895834</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.68207692129</v>
+        <v>46264.299901516206</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -3290,7 +3290,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46213.54066168981</v>
+        <v>46271.64556232639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46249.04035597222</v>
+        <v>46271.64561790509</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>224</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4327.xlsx
@@ -4608,7 +4608,7 @@
         <v>46227.62052016203</v>
       </c>
       <c r="D44" s="5">
-        <v>46227.620521689816</v>
+        <v>46276.99749231481</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46249.06894548611</v>
+        <v>46276.98858347222</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>246</v>
